--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,1147 +429,1147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>entityid</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>teamid</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>shortname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rowid</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>teamabbreviation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>secondsplayed</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gamesplayed</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>plusminus</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>offposs</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>defposs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffposs</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>penaltydefposs</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>secondchanceoffposs</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>totalposs</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>atrimfgm</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>atrimfga</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfgm</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfga</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfgm</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfga</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefgm</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefga</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefgm</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefga</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>corner3fgm</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>corner3fga</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3fgm</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3fga</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3fgm</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3fga</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>arc3fgm</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>arc3fga</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3fgm</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3fga</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3fgm</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3fga</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>fg2m</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>fg2a</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>fg3m</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fg3a</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ftpoints</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>opponentpoints</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2m</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2a</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3m</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3a</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>secondchanceftpoints</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>secondchancepoints</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2m</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2a</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3m</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3a</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>penaltyftpoints</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>penaltypoints</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ptsassisted2s</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ptsunassisted2s</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ptsassisted3s</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>ptsunassisted3s</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ptsputbacks</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3fga</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3fgm</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>fg2ablocked</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>fg3ablocked</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>twoptassists</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>threeptassists</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>assists</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>arc3assists</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>corner3assists</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>atrimassists</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangeassists</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>longmidrangeassists</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>assistpoints</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>offthreeptrebounds</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>offtwoptrebounds</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>ftoffrebounds</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>defthreeptrebounds</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>deftwoptrebounds</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>ftdefrebounds</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>defrebounds</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>offrebounds</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>rebounds</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>selforeb</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>steals</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>badpasssteals</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>lostballsteals</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>liveballturnovers</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>badpassoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>badpassturnovers</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>deadballturnovers</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>lostballoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>lostballturnovers</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>stepoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>travels</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>turnovers</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>secondchanceturnovers</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>penaltyturnovers</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>shootingfouls</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>fouls</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>charge fouls</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>loose ball fouls</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>offensive fouls</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>foulsdrawn</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>charge fouls drawn</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>loose ball fouls drawn</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>offensive fouls drawn</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>fta</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>2pt and 1 free throw trips</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>3pt and 1 free throw trips</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>technical free throw trips</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>twoptshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>threeptshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>nonshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>blocked2s</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>blocked3s</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>blockedarc3</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>blockedatrim</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>blockedlongmidrange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>blockedshortmidrange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>blocks</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>recoveredblocks</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>defensivegoaltends</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>defensive 3 seconds violations</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>firstchancepoints</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>penaltypointsexcludingtakefouls</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffpossexcludingtakefouls</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>nonshootingpenaltynontakefouls</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>nonshootingpenaltynontakefoulsdrawn</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>assisted2spct</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>nonputbacksassisted2spct</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>assisted3spct</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>fg3pct</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3pct</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3pct</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>nonheavefg3pct</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>fg2pct</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2pct</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2pct</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>efgpct</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>secondchanceefgpct</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>penaltyefgpct</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>tspct</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>secondchancetspct</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>penaltytspct</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>fg3apct</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>fg3apctblocked</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>fg2apctblocked</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>atrimpctblocked</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangepctblocked</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>longmidrangepctblocked</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>arc3pctblocked</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>liveballturnoverpct</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>defftreboundpct</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>offftreboundpct</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>deftwoptreboundpct</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>offtwoptreboundpct</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>defthreeptreboundpct</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>offthreeptreboundpct</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>deffgreboundpct</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>offfgreboundpct</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>offatrimreboundpct</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>offshortmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>offlongmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>offarc3reboundpct</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>offcorner3reboundpct</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>defatrimreboundpct</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>defshortmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>deflongmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>defarc3reboundpct</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>defcorner3reboundpct</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>selforebpct</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>pace</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>blocksrecoveredpct</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>secondsperpossoff</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>secondsperpossdef</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>secondsexcludingorebsperpossoff</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>secondsexcludingorebsperpossdef</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>atrimfrequency</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>atrimaccuracy</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>unblockedatrimaccuracy</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>atrimpctassisted</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefrequency</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>unblockedshortmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangepctassisted</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefrequency</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>longmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>unblockedlongmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>longmidrangepctassisted</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>corner3frequency</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>corner3accuracy</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>unblockedcorner3accuracy</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>corner3pctassisted</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>arc3frequency</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>arc3accuracy</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>unblockedarc3accuracy</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>arc3pctassisted</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfrequency</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimaccuracy</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimpctassisted</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3frequency</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3accuracy</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3pctassisted</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3frequency</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3accuracy</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3pctassisted</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfrequency</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimaccuracy</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3frequency</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3accuracy</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3frequency</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3accuracy</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>atrimfg3afrequency</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3accuracy</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>shotqualityavg</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>secondchanceshotqualityavg</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>penaltyshotqualityavg</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>shootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>twoptshootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>threeptshootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>secondchancepointspct</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>penaltypointspct</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>avg2ptshotdistance</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>avg3ptshotdistance</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffposspct</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>blockedcorner3</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>offensivegoaltends</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>corner3pctblocked</t>
         </is>
@@ -2987,331 +2999,331 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38040</v>
+        <v>40920</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>-9</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>1242</v>
+        <v>1341</v>
       </c>
       <c r="K4" t="n">
-        <v>1251</v>
+        <v>1350</v>
       </c>
       <c r="L4" t="n">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="M4" t="n">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="N4" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="O4" t="n">
-        <v>2493</v>
+        <v>2691</v>
       </c>
       <c r="P4" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="Q4" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S4" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="T4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="V4" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="W4" t="n">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
         <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AF4" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="AG4" t="n">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AK4" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="AL4" t="n">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="AM4" t="n">
-        <v>575</v>
+        <v>626</v>
       </c>
       <c r="AN4" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="AO4" t="n">
-        <v>491</v>
+        <v>526</v>
       </c>
       <c r="AP4" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1420</v>
+        <v>1545</v>
       </c>
       <c r="AR4" t="n">
-        <v>1429</v>
+        <v>1523</v>
       </c>
       <c r="AS4" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AT4" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AU4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AW4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="AY4" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="AZ4" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="BA4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB4" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="BC4" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="BD4" t="n">
-        <v>469</v>
+        <v>535</v>
       </c>
       <c r="BE4" t="n">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="BF4" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="BG4" t="n">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="BH4" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="BI4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="BJ4" t="n">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="BK4" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="BL4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BM4" t="n">
         <v>7</v>
       </c>
       <c r="BN4" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="BO4" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="BP4" t="n">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="BQ4" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="BR4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>677</v>
+        <v>748</v>
       </c>
       <c r="BW4" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="BX4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="CA4" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="CB4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CC4" t="n">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="CD4" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="CE4" t="n">
-        <v>611</v>
+        <v>672</v>
       </c>
       <c r="CF4" t="n">
+        <v>26</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>111</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>74</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>37</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>133</v>
+      </c>
+      <c r="CK4" t="n">
         <v>21</v>
       </c>
-      <c r="CG4" t="n">
-        <v>101</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>69</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>32</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>126</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>20</v>
-      </c>
       <c r="CL4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="CM4" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="CN4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CO4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="CP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CQ4" t="n">
         <v>8</v>
       </c>
       <c r="CR4" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="CS4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CT4" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="CU4" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="CV4" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="CW4" t="n">
         <v>2</v>
       </c>
       <c r="CX4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="CY4" t="n">
         <v>19</v>
       </c>
       <c r="CZ4" t="n">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="DA4" t="n">
         <v>3</v>
       </c>
       <c r="DB4" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>27</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>405</v>
+      </c>
+      <c r="DE4" t="n">
         <v>22</v>
       </c>
-      <c r="DC4" t="n">
-        <v>25</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>361</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>19</v>
-      </c>
       <c r="DF4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DG4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="DI4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DJ4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="DK4" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="DL4" t="n">
         <v>3</v>
@@ -3320,50 +3332,50 @@
         <v>3</v>
       </c>
       <c r="DN4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="DQ4" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="DR4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="DS4" t="inlineStr"/>
       <c r="DT4" t="n">
         <v>2</v>
       </c>
       <c r="DU4" t="n">
-        <v>1231</v>
+        <v>1338</v>
       </c>
       <c r="DV4" t="n">
-        <v>468</v>
+        <v>534</v>
       </c>
       <c r="DW4" t="n">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="DX4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="DY4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.4845679012345679</v>
+        <v>0.5028089887640449</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.5340136054421769</v>
+        <v>0.5524691358024691</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.7289156626506024</v>
+        <v>0.7344632768361582</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.3380855397148676</v>
+        <v>0.3365019011406844</v>
       </c>
       <c r="ED4" t="n">
         <v>0.25</v>
@@ -3372,282 +3384,282 @@
         <v>0.3125</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.3380855397148676</v>
+        <v>0.3365019011406844</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.5634782608695652</v>
+        <v>0.5686900958466453</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.6022727272727273</v>
+        <v>0.5894736842105263</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5431472081218274</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.5375234521575984</v>
+        <v>0.5394965277777778</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.5064516129032258</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.4971181556195965</v>
+        <v>0.506426735218509</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.5768292682926829</v>
+        <v>0.5774700598802395</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.5570071258907363</v>
+        <v>0.5632911392405063</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4606003752345216</v>
+        <v>0.4565972222222222</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01425661914460285</v>
+        <v>0.01330798479087452</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.111304347826087</v>
+        <v>0.110223642172524</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.09665427509293681</v>
+        <v>0.09642857142857143</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1330798479087452</v>
+        <v>0.1291390728476821</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.06976744186046512</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.01081081081081081</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.5753424657534246</v>
+        <v>0.5732758620689655</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.169811320754717</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.6242937853107344</v>
+        <v>0.6335078534031413</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.4048582995951417</v>
+        <v>0.4135338345864661</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.6943231441048034</v>
+        <v>0.6980392156862745</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.3003194888178914</v>
+        <v>0.3065476190476191</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.6518010291595198</v>
+        <v>0.6593406593406593</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.3464285714285714</v>
+        <v>0.3538205980066445</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.308641975308642</v>
+        <v>0.3294117647058823</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.4929577464788732</v>
+        <v>0.4904458598726115</v>
       </c>
       <c r="FH4" t="n">
         <v>0.2083333333333333</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.2966101694915254</v>
+        <v>0.3070866141732284</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.3116883116883117</v>
+        <v>0.3048780487804878</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.5522388059701493</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.6395348837209303</v>
+        <v>0.65625</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.7168674698795181</v>
+        <v>0.7219251336898396</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.6349206349206349</v>
+        <v>0.6323529411764706</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.04276985743380855</v>
+        <v>0.04924242424242424</v>
       </c>
       <c r="FQ4" t="n">
-        <v>94.37223974763407</v>
+        <v>94.69794721407625</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.4507042253521127</v>
+        <v>0.48</v>
       </c>
       <c r="FS4" t="n">
-        <v>15.50378421900161</v>
+        <v>15.42371364653244</v>
       </c>
       <c r="FT4" t="n">
-        <v>15.0154276578737</v>
+        <v>14.99022222222222</v>
       </c>
       <c r="FU4" t="n">
-        <v>14.66682769726248</v>
+        <v>14.60984340044743</v>
       </c>
       <c r="FV4" t="n">
-        <v>14.30535571542766</v>
+        <v>14.28088888888889</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2523452157598499</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.6951672862453532</v>
+        <v>0.6928571428571428</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.7695473251028807</v>
+        <v>0.766798418972332</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.5401069518716578</v>
+        <v>0.5412371134020618</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.2467166979362101</v>
+        <v>0.2621527777777778</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.4486692015209126</v>
+        <v>0.4701986754966888</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.5175438596491229</v>
+        <v>0.5399239543726235</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.423728813559322</v>
+        <v>0.4718309859154929</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.04033771106941839</v>
+        <v>0.03819444444444445</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.475</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.35</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.1135084427767355</v>
+        <v>0.1128472222222222</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3728813559322034</v>
+        <v>0.3779527559055118</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.875</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3470919324577861</v>
+        <v>0.34375</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3297297297297297</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3290816326530612</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.680327868852459</v>
+        <v>0.6821705426356589</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.375</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.08387096774193549</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="GV4" t="n">
         <v>0.25</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3032258064516129</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2340425531914894</v>
       </c>
       <c r="GY4" t="n">
         <v>1</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.239193083573487</v>
+        <v>0.2287917737789203</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.1239193083573487</v>
+        <v>0.1259640102827763</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3832853025936599</v>
+        <v>0.3676092544987147</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.2706766917293233</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.7129455909943715</v>
+        <v>0.6996527777777778</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3297297297297297</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.5485029328287606</v>
+        <v>0.5445112182296231</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.5477011111111112</v>
+        <v>0.54629375</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.5443826470588236</v>
+        <v>0.5391089238845144</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.1204717775905644</v>
+        <v>0.1244167962674961</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.190684133915575</v>
+        <v>0.1957390146471371</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.024</v>
+        <v>0.02429906542056075</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.1330985915492958</v>
+        <v>0.1339805825242718</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3302816901408451</v>
+        <v>0.3462783171521036</v>
       </c>
       <c r="HP4" t="n">
-        <v>5.666434782608695</v>
+        <v>5.670287539936102</v>
       </c>
       <c r="HQ4" t="n">
-        <v>25.61131687242798</v>
+        <v>25.6675</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.321256038647343</v>
+        <v>0.3348247576435496</v>
       </c>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
       <c r="HU4" t="n">
-        <v>0.02479338842975207</v>
+        <v>0.02307692307692308</v>
       </c>
     </row>
     <row r="5">
@@ -11952,67 +11964,67 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>37740</v>
+        <v>40620</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>1219</v>
+        <v>1317</v>
       </c>
       <c r="K17" t="n">
-        <v>1228</v>
+        <v>1328</v>
       </c>
       <c r="L17" t="n">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="M17" t="n">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="N17" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="O17" t="n">
-        <v>2447</v>
+        <v>2645</v>
       </c>
       <c r="P17" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="Q17" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="R17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S17" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="T17" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="V17" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="W17" t="n">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="X17" t="n">
         <v>39</v>
       </c>
       <c r="Y17" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Z17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA17" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AB17" t="n">
         <v>6</v>
@@ -12021,196 +12033,196 @@
         <v>14</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AG17" t="n">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="AH17" t="n">
         <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK17" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AL17" t="n">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="AM17" t="n">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="AN17" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AO17" t="n">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="AP17" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1375</v>
+        <v>1469</v>
       </c>
       <c r="AR17" t="n">
-        <v>1321</v>
+        <v>1446</v>
       </c>
       <c r="AS17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="AT17" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AU17" t="n">
         <v>21</v>
       </c>
       <c r="AV17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AW17" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AX17" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="AY17" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="AZ17" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB17" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="BC17" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="BD17" t="n">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="BE17" t="n">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="BF17" t="n">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="BG17" t="n">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="BH17" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="BI17" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="BJ17" t="n">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="BK17" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="BL17" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BM17" t="n">
         <v>4</v>
       </c>
       <c r="BN17" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="BO17" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="BP17" t="n">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="BQ17" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="BR17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="BS17" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="BT17" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BU17" t="n">
         <v>13</v>
       </c>
       <c r="BV17" t="n">
-        <v>698</v>
+        <v>750</v>
       </c>
       <c r="BW17" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="BX17" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>227</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>201</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>46</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>474</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>227</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>701</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>15</v>
+      </c>
+      <c r="CG17" t="n">
         <v>122</v>
       </c>
-      <c r="BY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>213</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>192</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>38</v>
-      </c>
-      <c r="CC17" t="n">
-        <v>443</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>212</v>
-      </c>
-      <c r="CE17" t="n">
-        <v>655</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>11</v>
-      </c>
-      <c r="CG17" t="n">
-        <v>115</v>
-      </c>
       <c r="CH17" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="CI17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CJ17" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="CK17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CL17" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="CM17" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="CN17" t="n">
         <v>11</v>
       </c>
       <c r="CO17" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="CP17" t="n">
         <v>7</v>
@@ -12219,64 +12231,64 @@
         <v>5</v>
       </c>
       <c r="CR17" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="CS17" t="n">
         <v>23</v>
       </c>
       <c r="CT17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="CU17" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="CV17" t="n">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="CW17" t="n">
         <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="CY17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CZ17" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="DA17" t="n">
         <v>1</v>
       </c>
       <c r="DB17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="DC17" t="n">
         <v>13</v>
       </c>
       <c r="DD17" t="n">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="DE17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DH17" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="DI17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DJ17" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="DK17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="DL17" t="n">
         <v>2</v>
@@ -12285,19 +12297,19 @@
         <v>1</v>
       </c>
       <c r="DN17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DO17" t="n">
         <v>3</v>
       </c>
       <c r="DP17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="DQ17" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="DR17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="DS17" t="n">
         <v>4</v>
@@ -12306,236 +12318,236 @@
         <v>3</v>
       </c>
       <c r="DU17" t="n">
-        <v>1163</v>
+        <v>1246</v>
       </c>
       <c r="DV17" t="n">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="DW17" t="n">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="DX17" t="n">
+        <v>46</v>
+      </c>
+      <c r="DY17" t="n">
         <v>40</v>
       </c>
-      <c r="DY17" t="n">
-        <v>37</v>
-      </c>
       <c r="DZ17" t="n">
-        <v>0.5</v>
+        <v>0.5053475935828877</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.5545171339563862</v>
+        <v>0.5625</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.3612565445026178</v>
+        <v>0.3562945368171022</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.3559322033898305</v>
+        <v>0.35</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.2545454545454545</v>
+        <v>0.2635658914728682</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.3612565445026178</v>
+        <v>0.3562945368171022</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.5049645390070922</v>
+        <v>0.4980026631158455</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.5370370370370371</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4622222222222222</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.5179392824287029</v>
+        <v>0.5110921501706485</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.5359281437125748</v>
+        <v>0.5223463687150838</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.444794952681388</v>
+        <v>0.4378531073446328</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.5582722086389568</v>
+        <v>0.5520754716981132</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.5698924731182796</v>
+        <v>0.554726368159204</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.5116279069767442</v>
+        <v>0.5057870370370371</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.3514259429622815</v>
+        <v>0.3592150170648464</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.01047120418848168</v>
+        <v>0.009501187648456057</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.1078014184397163</v>
+        <v>0.1065246338215712</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.1059602649006623</v>
+        <v>0.1041009463722398</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1394658753709199</v>
       </c>
       <c r="EU17" t="inlineStr"/>
       <c r="EV17" t="n">
-        <v>0.007168458781362007</v>
+        <v>0.006430868167202572</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.5502392344497608</v>
+        <v>0.5580357142857143</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.2702702702702703</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6222910216718266</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.3556851311953353</v>
+        <v>0.3477088948787062</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.726962457337884</v>
+        <v>0.7183544303797469</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.3319502074688797</v>
+        <v>0.3258426966292135</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.678391959798995</v>
+        <v>0.6697965571205008</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.3458904109589041</v>
+        <v>0.3385579937304075</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.375</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.3497267759562842</v>
+        <v>0.3349753694581281</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.3085714285714286</v>
+        <v>0.3010204081632653</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3943661971830986</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.6185567010309279</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.6162790697674418</v>
+        <v>0.6096256684491979</v>
       </c>
       <c r="FM17" t="n">
         <v>0.7428571428571429</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.7543859649122807</v>
+        <v>0.7398373983739838</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.6307692307692307</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.02173913043478261</v>
+        <v>0.02697841726618705</v>
       </c>
       <c r="FQ17" t="n">
-        <v>93.36724960254372</v>
+        <v>93.76661742983752</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.5567010309278351</v>
+        <v>0.5392156862745098</v>
       </c>
       <c r="FS17" t="n">
-        <v>15.6369155045119</v>
+        <v>15.57623386484434</v>
       </c>
       <c r="FT17" t="n">
-        <v>15.21058631921824</v>
+        <v>15.14013554216867</v>
       </c>
       <c r="FU17" t="n">
-        <v>14.78728465955701</v>
+        <v>14.73720577069096</v>
       </c>
       <c r="FV17" t="n">
-        <v>14.38029315960912</v>
+        <v>14.33328313253012</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.2778288868445262</v>
+        <v>0.2704778156996587</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.6490066225165563</v>
+        <v>0.6466876971608833</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.725925925925926</v>
+        <v>0.721830985915493</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.5459183673469388</v>
+        <v>0.5463414634146342</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.2833486660533578</v>
+        <v>0.287542662116041</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3857566765578635</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.4793388429752066</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.08739650413983441</v>
+        <v>0.08276450511945392</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.4105263157894737</v>
+        <v>0.4020618556701031</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.4105263157894737</v>
+        <v>0.4020618556701031</v>
       </c>
       <c r="GH17" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="GI17" t="n">
-        <v>0.09475620975160993</v>
+        <v>0.09385665529010238</v>
       </c>
       <c r="GJ17" t="n">
+        <v>0.3545454545454546</v>
+      </c>
+      <c r="GK17" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="GL17" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="GM17" t="n">
+        <v>0.265358361774744</v>
+      </c>
+      <c r="GN17" t="n">
+        <v>0.3569131832797428</v>
+      </c>
+      <c r="GO17" t="n">
         <v>0.3592233009708738</v>
       </c>
-      <c r="GK17" t="n">
-        <v>0.3663366336633663</v>
-      </c>
-      <c r="GL17" t="n">
-        <v>0.9459459459459459</v>
-      </c>
-      <c r="GM17" t="n">
-        <v>0.2566697332106715</v>
-      </c>
-      <c r="GN17" t="n">
-        <v>0.3620071684587813</v>
-      </c>
-      <c r="GO17" t="n">
-        <v>0.3646209386281589</v>
-      </c>
       <c r="GP17" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="GQ17" t="n">
-        <v>0.407185628742515</v>
+        <v>0.4134078212290503</v>
       </c>
       <c r="GR17" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="GS17" t="n">
-        <v>0.2</v>
+        <v>0.2045454545454546</v>
       </c>
       <c r="GT17" t="n">
-        <v>0.08383233532934131</v>
+        <v>0.0782122905027933</v>
       </c>
       <c r="GU17" t="n">
         <v>0.4285714285714285</v>
@@ -12544,77 +12556,79 @@
         <v>1</v>
       </c>
       <c r="GW17" t="n">
-        <v>0.2694610778443114</v>
+        <v>0.2569832402234637</v>
       </c>
       <c r="GX17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="GY17" t="n">
         <v>0.8</v>
       </c>
       <c r="GZ17" t="n">
-        <v>0.2996845425867508</v>
+        <v>0.2824858757062147</v>
       </c>
       <c r="HA17" t="n">
-        <v>0.6105263157894737</v>
+        <v>0.61</v>
       </c>
       <c r="HB17" t="n">
-        <v>0.0946372239747634</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="HC17" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="HD17" t="n">
-        <v>0.2523659305993691</v>
+        <v>0.2627118644067797</v>
       </c>
       <c r="HE17" t="n">
-        <v>0.25</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="HF17" t="n">
-        <v>0.6292548298068077</v>
+        <v>0.6296928327645052</v>
       </c>
       <c r="HG17" t="n">
-        <v>0.3620071684587813</v>
+        <v>0.3569131832797428</v>
       </c>
       <c r="HH17" t="n">
-        <v>0.5304233856088562</v>
+        <v>0.5276072284003421</v>
       </c>
       <c r="HI17" t="n">
-        <v>0.5332949541284404</v>
+        <v>0.5310884615384616</v>
       </c>
       <c r="HJ17" t="n">
-        <v>0.5195680952380952</v>
+        <v>0.5153485795454545</v>
       </c>
       <c r="HK17" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1107644305772231</v>
       </c>
       <c r="HL17" t="n">
-        <v>0.1583541147132169</v>
+        <v>0.1588785046728972</v>
       </c>
       <c r="HM17" t="n">
-        <v>0.01295336787564767</v>
+        <v>0.01408450704225352</v>
       </c>
       <c r="HN17" t="n">
-        <v>0.1541818181818182</v>
+        <v>0.1518039482641252</v>
       </c>
       <c r="HO17" t="n">
-        <v>0.2887272727272727</v>
+        <v>0.2988427501701838</v>
       </c>
       <c r="HP17" t="n">
-        <v>6.564255319148937</v>
+        <v>6.556191744340879</v>
       </c>
       <c r="HQ17" t="n">
-        <v>25.66833773087071</v>
+        <v>25.7578947368421</v>
       </c>
       <c r="HR17" t="n">
-        <v>0.3018867924528302</v>
+        <v>0.3120728929384966</v>
       </c>
       <c r="HS17" t="n">
         <v>1</v>
       </c>
-      <c r="HT17" t="inlineStr"/>
+      <c r="HT17" t="n">
+        <v>1</v>
+      </c>
       <c r="HU17" t="n">
-        <v>0.01941747572815534</v>
+        <v>0.01818181818181818</v>
       </c>
     </row>
   </sheetData>

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,311 +7135,311 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>31680</v>
+        <v>35160</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J10" t="n">
-        <v>1086</v>
+        <v>1198</v>
       </c>
       <c r="K10" t="n">
-        <v>1096</v>
+        <v>1209</v>
       </c>
       <c r="L10" t="n">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="M10" t="n">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="N10" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="O10" t="n">
-        <v>2182</v>
+        <v>2407</v>
       </c>
       <c r="P10" t="n">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="Q10" t="n">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="R10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="S10" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="U10" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="V10" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="W10" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="AG10" t="n">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AL10" t="n">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="AM10" t="n">
-        <v>587</v>
+        <v>640</v>
       </c>
       <c r="AN10" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="AO10" t="n">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="AP10" t="n">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1286</v>
+        <v>1408</v>
       </c>
       <c r="AR10" t="n">
-        <v>1127</v>
+        <v>1242</v>
       </c>
       <c r="AS10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AT10" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AU10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AW10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="AY10" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AZ10" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="BA10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="BB10" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="BC10" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="BD10" t="n">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="BE10" t="n">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="BF10" t="n">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="BG10" t="n">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="BH10" t="n">
         <v>42</v>
       </c>
       <c r="BI10" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="BJ10" t="n">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="BK10" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="BL10" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="BM10" t="n">
         <v>4</v>
       </c>
       <c r="BN10" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="BO10" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="BP10" t="n">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="BQ10" t="n">
+        <v>98</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>114</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>43</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>742</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX10" t="n">
         <v>89</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>104</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>679</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>81</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="CA10" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="CB10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CC10" t="n">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="CD10" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="CE10" t="n">
-        <v>584</v>
+        <v>652</v>
       </c>
       <c r="CF10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CG10" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="CH10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="CI10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="CJ10" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="CK10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CL10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="CM10" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="CN10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CO10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="CP10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CR10" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="CS10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CT10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CU10" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="CV10" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="CW10" t="n">
         <v>9</v>
       </c>
       <c r="CX10" t="n">
+        <v>29</v>
+      </c>
+      <c r="CY10" t="n">
         <v>26</v>
       </c>
-      <c r="CY10" t="n">
-        <v>24</v>
-      </c>
       <c r="CZ10" t="n">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DC10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DD10" t="n">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="DE10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -7448,37 +7448,37 @@
         <v>5</v>
       </c>
       <c r="DH10" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="DI10" t="n">
         <v>5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="DK10" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="DL10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DM10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DN10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="DO10" t="n">
         <v>1</v>
       </c>
       <c r="DP10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="DQ10" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="DR10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="DS10" t="n">
         <v>5</v>
@@ -7487,310 +7487,310 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1123</v>
+        <v>1232</v>
       </c>
       <c r="DV10" t="n">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="DW10" t="n">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="DX10" t="n">
         <v>28</v>
       </c>
       <c r="DY10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4754601226993865</v>
+        <v>0.4717514124293785</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5236486486486487</v>
+        <v>0.521875</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8978102189781022</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3816155988857939</v>
+        <v>0.373134328358209</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.5</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3904761904761905</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3816155988857939</v>
+        <v>0.373134328358209</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.555366269165247</v>
+        <v>0.553125</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5529411764705883</v>
+        <v>0.5257731958762887</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5</v>
+        <v>0.5023923444976076</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5618393234672304</v>
+        <v>0.5556621880998081</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.6043478260869565</v>
+        <v>0.5725190839694656</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5299003322259136</v>
+        <v>0.5340557275541795</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5990654205607476</v>
+        <v>0.5954198473282443</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6417322834645669</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5821917808219178</v>
+        <v>0.5888324873096447</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.379492600422833</v>
+        <v>0.3857965451055662</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01114206128133705</v>
+        <v>0.009950248756218905</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.06984667802385008</v>
+        <v>0.07656250000000001</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.08169934640522876</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06698564593301436</v>
+        <v>0.06787330316742081</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.003831417624521073</v>
+        <v>0.003472222222222222</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.4720496894409938</v>
+        <v>0.4891304347826087</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1</v>
+        <v>0.09375</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6467065868263473</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3115384615384615</v>
+        <v>0.3133802816901409</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7587548638132295</v>
+        <v>0.7649122807017544</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2752293577981652</v>
+        <v>0.2874493927125506</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6954314720812182</v>
+        <v>0.7046153846153846</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.294979079497908</v>
+        <v>0.3013182674199623</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3603603603603603</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3097345132743363</v>
+        <v>0.3057851239669421</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.24</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2923976608187134</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.25</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6107382550335571</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7569060773480663</v>
+        <v>0.76</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.03695150115473441</v>
+        <v>0.04175365344467641</v>
       </c>
       <c r="FQ10" t="n">
-        <v>99.18181818181819</v>
+        <v>98.580204778157</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.34014732965009</v>
+        <v>14.54641068447412</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.69580291970803</v>
+        <v>14.66782464846981</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.76418047882136</v>
+        <v>13.96001669449082</v>
       </c>
       <c r="FV10" t="n">
-        <v>13.91970802919708</v>
+        <v>13.90885028949545</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3234672304439746</v>
+        <v>0.3301343570057582</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6830065359477124</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7437722419928826</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.4976076555023923</v>
+        <v>0.4913793103448276</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2209302325581395</v>
+        <v>0.2120921305182342</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4479638009049774</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.4805825242718447</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4421052631578947</v>
+        <v>0.4343434343434344</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07610993657505286</v>
+        <v>0.07197696737044146</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3066666666666666</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.3150684931506849</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1035940803382664</v>
+        <v>0.109404990403071</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3578947368421053</v>
+        <v>0.3423423423423423</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2758985200845666</v>
+        <v>0.2763915547024952</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3946360153256705</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3961538461538461</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8640776699029126</v>
+        <v>0.875</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.4695652173913044</v>
+        <v>0.4885496183206107</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.578125</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1351351351351351</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06956521739130435</v>
+        <v>0.07633587786259542</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.191304347826087</v>
+        <v>0.183206106870229</v>
       </c>
       <c r="GX10" t="n">
         <v>0.5</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3355481727574751</v>
+        <v>0.3405572755417957</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.594059405940594</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.07641196013289037</v>
+        <v>0.08359133126934984</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2724252491694352</v>
+        <v>0.2693498452012384</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.4024390243902439</v>
+        <v>0.3908045977011494</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7029598308668076</v>
+        <v>0.7159309021113244</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3946360153256705</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.565665906680806</v>
+        <v>0.5645760827718961</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.542178</v>
+        <v>0.5414744047619047</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5565254180602007</v>
+        <v>0.5545506230529595</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.118042226487524</v>
+        <v>0.1184668989547038</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1762114537444934</v>
+        <v>0.1787634408602151</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.008310249307479225</v>
+        <v>0.007425742574257425</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1267496111975117</v>
+        <v>0.125</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3312597200622084</v>
+        <v>0.3302556818181818</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.927427597955707</v>
+        <v>5.7603125</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.27787114845939</v>
+        <v>25.30425</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3406998158379374</v>
+        <v>0.3347245409015025</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.03061224489795918</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="11">
@@ -11271,73 +11271,73 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>23040</v>
+        <v>26520</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J16" t="n">
-        <v>756</v>
+        <v>868</v>
       </c>
       <c r="K16" t="n">
-        <v>763</v>
+        <v>876</v>
       </c>
       <c r="L16" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M16" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="N16" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="O16" t="n">
-        <v>1519</v>
+        <v>1744</v>
       </c>
       <c r="P16" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="Q16" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="R16" t="n">
         <v>23</v>
       </c>
       <c r="S16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="W16" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="X16" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Y16" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD16" t="n">
         <v>9</v>
@@ -11346,238 +11346,238 @@
         <v>26</v>
       </c>
       <c r="AF16" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AG16" t="n">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AL16" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="AM16" t="n">
-        <v>406</v>
+        <v>462</v>
       </c>
       <c r="AN16" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="AO16" t="n">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="AP16" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="AQ16" t="n">
-        <v>970</v>
+        <v>1085</v>
       </c>
       <c r="AR16" t="n">
-        <v>837</v>
+        <v>959</v>
       </c>
       <c r="AS16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT16" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AU16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AW16" t="n">
         <v>20</v>
       </c>
       <c r="AX16" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="AY16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AZ16" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BB16" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BC16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BD16" t="n">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="BE16" t="n">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="BF16" t="n">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="BG16" t="n">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="BH16" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="BI16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BJ16" t="n">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="BK16" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="BL16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BM16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN16" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="BO16" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="BP16" t="n">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="BQ16" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="BR16" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="BS16" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="BT16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BU16" t="n">
         <v>5</v>
       </c>
       <c r="BV16" t="n">
-        <v>511</v>
+        <v>577</v>
       </c>
       <c r="BW16" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="BX16" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="CA16" t="n">
+        <v>143</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>16</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>294</v>
+      </c>
+      <c r="CD16" t="n">
         <v>127</v>
       </c>
-      <c r="CB16" t="n">
-        <v>14</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>258</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>115</v>
-      </c>
       <c r="CE16" t="n">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="CF16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CG16" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="CH16" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="CI16" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="CJ16" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="CK16" t="n">
         <v>7</v>
       </c>
       <c r="CL16" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="CM16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CN16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CO16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CP16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CQ16" t="n">
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="CS16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CT16" t="n">
         <v>26</v>
       </c>
       <c r="CU16" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="CV16" t="n">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CY16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CZ16" t="n">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="DA16" t="n">
         <v>6</v>
       </c>
       <c r="DB16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="DC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>190</v>
+      </c>
+      <c r="DE16" t="n">
         <v>15</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>171</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>13</v>
       </c>
       <c r="DF16" t="n">
         <v>2</v>
@@ -11586,16 +11586,16 @@
         <v>4</v>
       </c>
       <c r="DH16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="DI16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ16" t="n">
         <v>25</v>
       </c>
       <c r="DK16" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="DL16" t="n">
         <v>1</v>
@@ -11604,329 +11604,329 @@
         <v>1</v>
       </c>
       <c r="DN16" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="DO16" t="n">
         <v>3</v>
       </c>
       <c r="DP16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="DR16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="DS16" t="inlineStr"/>
       <c r="DT16" t="n">
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>838</v>
+        <v>945</v>
       </c>
       <c r="DV16" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="DW16" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="DX16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="DY16" t="n">
         <v>21</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4508196721311475</v>
+        <v>0.4440298507462687</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.4867256637168141</v>
+        <v>0.4779116465863454</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.8660714285714286</v>
+        <v>0.875968992248062</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.3796610169491526</v>
+        <v>0.3794117647058823</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="EE16" t="n">
+        <v>0.3775510204081632</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0.3794117647058823</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0.5800865800865801</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0.5508474576271186</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0.5754364089775561</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0.5578703703703703</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0.6100451467268623</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0.6091269841269841</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0.4239401496259352</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0.01176470588235294</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0.05194805194805195</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0.05945945945945946</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0.02531645569620253</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0.01619433198380567</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0.5181818181818182</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0.6713615023474179</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0.3193717277486911</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.6852791878172588</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0.2980769230769231</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0.6780487804878049</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0.3082706766917293</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0.4038461538461539</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.1956521739130435</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0.3376623376623377</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0.569620253164557</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0.7191011235955056</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0.678082191780822</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0.02964959568733154</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>94.69683257918552</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>14.74953917050691</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>15.65913242009132</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>14.12569124423963</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>14.9953196347032</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0.2468827930174564</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0.7323232323232324</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0.7754010695187166</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0.5241379310344828</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0.2306733167082294</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0.4864864864864865</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0.4222222222222222</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0.09850374064837905</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0.4177215189873418</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="GH16" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="GI16" t="n">
+        <v>0.1159600997506234</v>
+      </c>
+      <c r="GJ16" t="n">
+        <v>0.4086021505376344</v>
+      </c>
+      <c r="GK16" t="n">
+        <v>0.4086021505376344</v>
+      </c>
+      <c r="GL16" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="GM16" t="n">
+        <v>0.3079800498753117</v>
+      </c>
+      <c r="GN16" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="GO16" t="n">
+        <v>0.3744855967078189</v>
+      </c>
+      <c r="GP16" t="n">
+        <v>0.8351648351648352</v>
+      </c>
+      <c r="GQ16" t="n">
         <v>0.375</v>
       </c>
-      <c r="EF16" t="n">
-        <v>0.3796610169491526</v>
-      </c>
-      <c r="EG16" t="n">
-        <v>0.6009852216748769</v>
-      </c>
-      <c r="EH16" t="n">
-        <v>0.6274509803921569</v>
-      </c>
-      <c r="EI16" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="EJ16" t="n">
-        <v>0.5877318116975749</v>
-      </c>
-      <c r="EK16" t="n">
-        <v>0.6436781609195402</v>
-      </c>
-      <c r="EL16" t="n">
-        <v>0.5533980582524272</v>
-      </c>
-      <c r="EM16" t="n">
-        <v>0.6216216216216216</v>
-      </c>
-      <c r="EN16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="EO16" t="n">
-        <v>0.6058091286307054</v>
-      </c>
-      <c r="EP16" t="n">
-        <v>0.4208273894436519</v>
-      </c>
-      <c r="EQ16" t="n">
-        <v>0.01016949152542373</v>
-      </c>
-      <c r="ER16" t="n">
-        <v>0.04433497536945813</v>
-      </c>
-      <c r="ES16" t="n">
-        <v>0.04117647058823529</v>
-      </c>
-      <c r="ET16" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="EU16" t="n">
-        <v>0.02702702702702703</v>
-      </c>
-      <c r="EV16" t="n">
-        <v>0.0136986301369863</v>
-      </c>
-      <c r="EW16" t="n">
-        <v>0.4842105263157895</v>
-      </c>
-      <c r="EX16" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="EY16" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="EZ16" t="n">
-        <v>0.671957671957672</v>
-      </c>
-      <c r="FA16" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="FB16" t="n">
-        <v>0.6964285714285714</v>
-      </c>
-      <c r="FC16" t="n">
-        <v>0.3166666666666667</v>
-      </c>
-      <c r="FD16" t="n">
-        <v>0.6834733893557423</v>
-      </c>
-      <c r="FE16" t="n">
-        <v>0.3264705882352941</v>
-      </c>
-      <c r="FF16" t="n">
-        <v>0.4146341463414634</v>
-      </c>
-      <c r="FG16" t="n">
-        <v>0.3733333333333334</v>
-      </c>
-      <c r="FH16" t="n">
-        <v>0.2045454545454546</v>
-      </c>
-      <c r="FI16" t="n">
-        <v>0.3555555555555556</v>
-      </c>
-      <c r="FJ16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="FK16" t="n">
-        <v>0.5692307692307692</v>
-      </c>
-      <c r="FL16" t="n">
-        <v>0.7160493827160493</v>
-      </c>
-      <c r="FM16" t="n">
-        <v>0.7441860465116279</v>
-      </c>
-      <c r="FN16" t="n">
-        <v>0.6821705426356589</v>
-      </c>
-      <c r="FO16" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="FP16" t="n">
-        <v>0.03134796238244514</v>
-      </c>
-      <c r="FQ16" t="n">
-        <v>94.9375</v>
-      </c>
-      <c r="FR16" t="n">
-        <v>0.5526315789473685</v>
-      </c>
-      <c r="FS16" t="n">
-        <v>14.78280423280423</v>
-      </c>
-      <c r="FT16" t="n">
-        <v>15.54941022280472</v>
-      </c>
-      <c r="FU16" t="n">
-        <v>14.15515873015873</v>
-      </c>
-      <c r="FV16" t="n">
-        <v>14.88820445609437</v>
-      </c>
-      <c r="FW16" t="n">
-        <v>0.2425106990014265</v>
-      </c>
-      <c r="FX16" t="n">
-        <v>0.7588235294117647</v>
-      </c>
-      <c r="FY16" t="n">
-        <v>0.7914110429447853</v>
-      </c>
-      <c r="FZ16" t="n">
-        <v>0.5271317829457365</v>
-      </c>
-      <c r="GA16" t="n">
-        <v>0.2310984308131241</v>
-      </c>
-      <c r="GB16" t="n">
-        <v>0.5246913580246914</v>
-      </c>
-      <c r="GC16" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="GD16" t="n">
-        <v>0.4352941176470588</v>
-      </c>
-      <c r="GE16" t="n">
-        <v>0.1055634807417974</v>
-      </c>
-      <c r="GF16" t="n">
-        <v>0.4054054054054054</v>
-      </c>
-      <c r="GG16" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="GH16" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="GI16" t="n">
-        <v>0.108416547788873</v>
-      </c>
-      <c r="GJ16" t="n">
-        <v>0.3947368421052632</v>
-      </c>
-      <c r="GK16" t="n">
-        <v>0.3947368421052632</v>
-      </c>
-      <c r="GL16" t="n">
-        <v>0.9666666666666667</v>
-      </c>
-      <c r="GM16" t="n">
-        <v>0.3124108416547789</v>
-      </c>
-      <c r="GN16" t="n">
-        <v>0.3744292237442922</v>
-      </c>
-      <c r="GO16" t="n">
-        <v>0.3796296296296297</v>
-      </c>
-      <c r="GP16" t="n">
-        <v>0.8292682926829268</v>
-      </c>
-      <c r="GQ16" t="n">
-        <v>0.367816091954023</v>
-      </c>
       <c r="GR16" t="n">
-        <v>0.71875</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="GS16" t="n">
         <v>0.1739130434782609</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.04597701149425287</v>
+        <v>0.0625</v>
       </c>
       <c r="GU16" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="GV16" t="n">
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.367816091954023</v>
+        <v>0.34375</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.46875</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="GY16" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.2524271844660194</v>
+        <v>0.2546296296296297</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.1262135922330097</v>
+        <v>0.1203703703703704</v>
       </c>
       <c r="HC16" t="n">
         <v>0.3461538461538461</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.3398058252427185</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3857142857142857</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6633380884450785</v>
+        <v>0.6708229426433915</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3744292237442922</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.5392381805157593</v>
+        <v>0.5400105757196496</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5361462962962963</v>
+        <v>0.5265270491803279</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.538030637254902</v>
+        <v>0.5360640186915887</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.08776595744680851</v>
+        <v>0.08826945412311266</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1400437636761488</v>
+        <v>0.1403846153846154</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.006779661016949152</v>
+        <v>0.008797653958944282</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.1360824742268041</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.3030927835051546</v>
+        <v>0.2847926267281106</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.281034482758621</v>
+        <v>7.187445887445887</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.48253424657534</v>
+        <v>25.38902077151335</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.3042328042328042</v>
+        <v>0.2764976958525346</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -2999,331 +2999,331 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>40920</v>
+        <v>44100</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>1341</v>
+        <v>1447</v>
       </c>
       <c r="K4" t="n">
-        <v>1350</v>
+        <v>1458</v>
       </c>
       <c r="L4" t="n">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="M4" t="n">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="N4" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="O4" t="n">
-        <v>2691</v>
+        <v>2905</v>
       </c>
       <c r="P4" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="R4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U4" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="V4" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="W4" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="AG4" t="n">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="AH4" t="n">
         <v>11</v>
       </c>
       <c r="AI4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AK4" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="AL4" t="n">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="AM4" t="n">
-        <v>626</v>
+        <v>666</v>
       </c>
       <c r="AN4" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="AO4" t="n">
-        <v>526</v>
+        <v>577</v>
       </c>
       <c r="AP4" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1545</v>
+        <v>1649</v>
       </c>
       <c r="AR4" t="n">
-        <v>1523</v>
+        <v>1638</v>
       </c>
       <c r="AS4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AT4" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AX4" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="AY4" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AZ4" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="BA4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="BB4" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="BC4" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="BD4" t="n">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="BE4" t="n">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="BF4" t="n">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="BG4" t="n">
-        <v>390</v>
+        <v>435</v>
       </c>
       <c r="BH4" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="BI4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BJ4" t="n">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="BK4" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="BL4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM4" t="n">
         <v>7</v>
       </c>
       <c r="BN4" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="BO4" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="BP4" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="BQ4" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="BR4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BS4" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="BT4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="BU4" t="n">
         <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>748</v>
+        <v>809</v>
       </c>
       <c r="BW4" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="BX4" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BY4" t="n">
         <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="CA4" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="CB4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CC4" t="n">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="CD4" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="CE4" t="n">
-        <v>672</v>
+        <v>721</v>
       </c>
       <c r="CF4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CG4" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="CH4" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="CI4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="CJ4" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="CK4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CL4" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="CM4" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="CN4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CO4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="CP4" t="n">
         <v>9</v>
       </c>
       <c r="CQ4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CR4" t="n">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="CS4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CT4" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="CU4" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="CV4" t="n">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="CW4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="CY4" t="n">
         <v>19</v>
       </c>
       <c r="CZ4" t="n">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="DA4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DB4" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC4" t="n">
         <v>29</v>
       </c>
-      <c r="DC4" t="n">
-        <v>27</v>
-      </c>
       <c r="DD4" t="n">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="DE4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DF4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DG4" t="n">
         <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="DI4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="DK4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="DL4" t="n">
         <v>3</v>
@@ -3332,334 +3332,334 @@
         <v>3</v>
       </c>
       <c r="DN4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="DQ4" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="DR4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="DS4" t="inlineStr"/>
       <c r="DT4" t="n">
         <v>2</v>
       </c>
       <c r="DU4" t="n">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="DV4" t="n">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="DW4" t="n">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="DX4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="DY4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.5028089887640449</v>
+        <v>0.4973404255319149</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.5524691358024691</v>
+        <v>0.5451895043731778</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.7344632768361582</v>
+        <v>0.7512953367875648</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.3365019011406844</v>
+        <v>0.3344887348353553</v>
       </c>
       <c r="ED4" t="n">
         <v>0.25</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.3125</v>
+        <v>0.3106796116504854</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.3365019011406844</v>
+        <v>0.3344887348353553</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.5686900958466453</v>
+        <v>0.5645645645645646</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.5894736842105263</v>
+        <v>0.594059405940594</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.5431472081218274</v>
+        <v>0.5288461538461539</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.5394965277777778</v>
+        <v>0.5353982300884956</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.5064516129032258</v>
+        <v>0.509090909090909</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.506426735218509</v>
+        <v>0.4975845410628019</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.5774700598802395</v>
+        <v>0.5730688935281837</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.5476190476190477</v>
+        <v>0.5497512437810945</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.5632911392405063</v>
+        <v>0.5536779324055666</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4565972222222222</v>
+        <v>0.4641995172968624</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01330798479087452</v>
+        <v>0.0121317157712305</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.110223642172524</v>
+        <v>0.1066066066066066</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.09642857142857143</v>
+        <v>0.09210526315789473</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1291390728476821</v>
+        <v>0.124203821656051</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0101010101010101</v>
+        <v>0.009280742459396751</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.5732758620689655</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.169811320754717</v>
+        <v>0.1636363636363636</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.6335078534031413</v>
+        <v>0.6305418719211823</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.4135338345864661</v>
+        <v>0.4020979020979021</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.6980392156862745</v>
+        <v>0.703971119133574</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.3065476190476191</v>
+        <v>0.3054054054054054</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.6593406593406593</v>
+        <v>0.6603221083455344</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.3538205980066445</v>
+        <v>0.3475609756097561</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.3294117647058823</v>
+        <v>0.3368421052631579</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.4904458598726115</v>
+        <v>0.4785276073619632</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.3070866141732284</v>
+        <v>0.3057553956834532</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.3048780487804878</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.5571428571428572</v>
+        <v>0.5657894736842105</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.65625</v>
+        <v>0.645</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.76</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.7219251336898396</v>
+        <v>0.7281553398058253</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.6323529411764706</v>
+        <v>0.6338028169014085</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.04924242424242424</v>
+        <v>0.04655172413793104</v>
       </c>
       <c r="FQ4" t="n">
-        <v>94.69794721407625</v>
+        <v>94.85714285714286</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.48</v>
+        <v>0.4938271604938271</v>
       </c>
       <c r="FS4" t="n">
-        <v>15.42371364653244</v>
+        <v>15.38887353144437</v>
       </c>
       <c r="FT4" t="n">
-        <v>14.99022222222222</v>
+        <v>14.9741426611797</v>
       </c>
       <c r="FU4" t="n">
-        <v>14.60984340044743</v>
+        <v>14.5852798894264</v>
       </c>
       <c r="FV4" t="n">
-        <v>14.28088888888889</v>
+        <v>14.24183813443073</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.2445695897023331</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.6928571428571428</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.766798418972332</v>
+        <v>0.7536231884057971</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.5412371134020618</v>
+        <v>0.5288461538461539</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.2621527777777778</v>
+        <v>0.252614641995173</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.4701986754966888</v>
+        <v>0.4713375796178344</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.5399239543726235</v>
+        <v>0.5381818181818182</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.4718309859154929</v>
+        <v>0.472972972972973</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.03819444444444445</v>
+        <v>0.03861625100563153</v>
       </c>
       <c r="GF4" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="GG4" t="n">
         <v>0.4545454545454545</v>
-      </c>
-      <c r="GG4" t="n">
-        <v>0.4878048780487805</v>
       </c>
       <c r="GH4" t="n">
         <v>0.35</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.1128472222222222</v>
+        <v>0.1174577634754626</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3779527559055118</v>
+        <v>0.3776223776223776</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.34375</v>
+        <v>0.3467417538213998</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3257575757575757</v>
+        <v>0.3225058004640371</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3290816326530612</v>
+        <v>0.3255269320843091</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.6821705426356589</v>
+        <v>0.697841726618705</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3878787878787879</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.65</v>
+        <v>0.640625</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.08387096774193549</v>
+        <v>0.08484848484848485</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3032258064516129</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.2340425531914894</v>
+        <v>0.22</v>
       </c>
       <c r="GY4" t="n">
         <v>1</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.2287917737789203</v>
+        <v>0.2270531400966184</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.6741573033707865</v>
+        <v>0.6595744680851063</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.1259640102827763</v>
+        <v>0.1207729468599034</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.42</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3676092544987147</v>
+        <v>0.3768115942028986</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2756410256410257</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.6996527777777778</v>
+        <v>0.7087691069991955</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3257575757575757</v>
+        <v>0.3225058004640371</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.5445112182296231</v>
+        <v>0.545791551584078</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.54629375</v>
+        <v>0.5445642156862744</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.5391089238845144</v>
+        <v>0.5365751851851852</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.1244167962674961</v>
+        <v>0.1234657039711191</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.1957390146471371</v>
+        <v>0.195244055068836</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.02429906542056075</v>
+        <v>0.02559726962457338</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.1339805825242718</v>
+        <v>0.134020618556701</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3462783171521036</v>
+        <v>0.3383869011522135</v>
       </c>
       <c r="HP4" t="n">
-        <v>5.670287539936102</v>
+        <v>5.614414414414414</v>
       </c>
       <c r="HQ4" t="n">
-        <v>25.6675</v>
+        <v>25.62771929824561</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.3348247576435496</v>
+        <v>0.331720801658604</v>
       </c>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
       <c r="HU4" t="n">
-        <v>0.02307692307692308</v>
+        <v>0.02054794520547945</v>
       </c>
     </row>
     <row r="5">
@@ -4377,310 +4377,310 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>28800</v>
+        <v>31980</v>
       </c>
       <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>205</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1059</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L6" t="n">
+        <v>322</v>
+      </c>
+      <c r="M6" t="n">
+        <v>312</v>
+      </c>
+      <c r="N6" t="n">
+        <v>135</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2129</v>
+      </c>
+      <c r="P6" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>333</v>
+      </c>
+      <c r="R6" t="n">
+        <v>39</v>
+      </c>
+      <c r="S6" t="n">
+        <v>58</v>
+      </c>
+      <c r="T6" t="n">
+        <v>57</v>
+      </c>
+      <c r="U6" t="n">
+        <v>89</v>
+      </c>
+      <c r="V6" t="n">
+        <v>90</v>
+      </c>
+      <c r="W6" t="n">
+        <v>186</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>99</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="n">
+      <c r="AD6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>101</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>258</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>86</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>334</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>572</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>141</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>357</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>228</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1319</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1114</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>54</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX6" t="n">
         <v>194</v>
       </c>
-      <c r="J6" t="n">
-        <v>951</v>
-      </c>
-      <c r="K6" t="n">
-        <v>964</v>
-      </c>
-      <c r="L6" t="n">
-        <v>291</v>
-      </c>
-      <c r="M6" t="n">
-        <v>281</v>
-      </c>
-      <c r="N6" t="n">
-        <v>119</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1915</v>
-      </c>
-      <c r="P6" t="n">
-        <v>203</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>301</v>
-      </c>
-      <c r="R6" t="n">
-        <v>38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>54</v>
-      </c>
-      <c r="T6" t="n">
-        <v>53</v>
-      </c>
-      <c r="U6" t="n">
-        <v>82</v>
-      </c>
-      <c r="V6" t="n">
-        <v>80</v>
-      </c>
-      <c r="W6" t="n">
-        <v>168</v>
-      </c>
-      <c r="X6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>47</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>92</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>232</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>302</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>516</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>131</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>324</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>207</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1204</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1010</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>52</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>82</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>177</v>
-      </c>
       <c r="AY6" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AZ6" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="BA6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB6" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="BC6" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="BD6" t="n">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="BE6" t="n">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="BF6" t="n">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="BG6" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="BH6" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="BI6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="BK6" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="BL6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="BM6" t="n">
         <v>3</v>
       </c>
       <c r="BN6" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="BO6" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="BP6" t="n">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="BQ6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="BT6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="BU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>678</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY6" t="n">
         <v>7</v>
       </c>
-      <c r="BV6" t="n">
-        <v>631</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>53</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>82</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>5</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="CA6" t="n">
+        <v>172</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>32</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>405</v>
+      </c>
+      <c r="CD6" t="n">
         <v>157</v>
       </c>
-      <c r="CB6" t="n">
-        <v>30</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>364</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>140</v>
-      </c>
       <c r="CE6" t="n">
-        <v>504</v>
+        <v>562</v>
       </c>
       <c r="CF6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CG6" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="CH6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="CI6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="CJ6" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="CK6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CL6" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="CM6" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="CN6" t="n">
         <v>8</v>
       </c>
       <c r="CO6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="CP6" t="n">
         <v>5</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CR6" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="CS6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CT6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="CU6" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="CV6" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="CW6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="CY6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CZ6" t="n">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="DA6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DB6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="DC6" t="n">
         <v>13</v>
       </c>
       <c r="DD6" t="n">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="DE6" t="n">
         <v>21</v>
@@ -4690,16 +4690,16 @@
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="DI6" t="n">
         <v>4</v>
       </c>
       <c r="DJ6" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="DK6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="DL6" t="n">
         <v>5</v>
@@ -4708,336 +4708,336 @@
         <v>3</v>
       </c>
       <c r="DN6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP6" t="n">
         <v>20</v>
       </c>
       <c r="DQ6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="DR6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DS6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1027</v>
+        <v>1125</v>
       </c>
       <c r="DV6" t="n">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="DW6" t="n">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="DX6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="DY6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5132450331125827</v>
+        <v>0.5029940119760479</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5636363636363636</v>
+        <v>0.5490196078431373</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.816793893129771</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.404320987654321</v>
+        <v>0.3949579831932773</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.59375</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4421052631578947</v>
+        <v>0.4368932038834951</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.404320987654321</v>
+        <v>0.3949579831932773</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5852713178294574</v>
+        <v>0.583916083916084</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.5460526315789473</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.593452380952381</v>
+        <v>0.5871905274488698</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.706140350877193</v>
+        <v>0.7137096774193549</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.597457627118644</v>
+        <v>0.5901960784313726</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6238293444328824</v>
+        <v>0.6163227016885553</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.708</v>
+        <v>0.708029197080292</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6402640264026402</v>
+        <v>0.6302395209580839</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3857142857142857</v>
+        <v>0.3842841765339075</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.008403361344537815</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0755813953488372</v>
+        <v>0.07867132867132867</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.08637873754152824</v>
+        <v>0.09009009009009009</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.008620689655172414</v>
+        <v>0.007751937984496124</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5328947368421053</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7235023041474654</v>
+        <v>0.7257383966244726</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.3923444976076555</v>
+        <v>0.3948497854077253</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.7375</v>
+        <v>0.7335766423357665</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2804232804232804</v>
+        <v>0.2748815165876777</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7308533916849015</v>
+        <v>0.7299412915851272</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3391959798994975</v>
+        <v>0.3378378378378378</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.358695652173913</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2481203007518797</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3559322033898305</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.7452830188679245</v>
+        <v>0.75</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7584269662921348</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.04213483146067416</v>
+        <v>0.04797979797979798</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.75</v>
+        <v>95.86491557223265</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.9</v>
+        <v>15.78508026440038</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.1899377593361</v>
+        <v>14.26504672897196</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.25531019978969</v>
+        <v>15.10217186024552</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.65321576763485</v>
+        <v>13.71476635514019</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.3584499461786868</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.6696696696696697</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.7381818181818182</v>
+        <v>0.735973597359736</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5566502463054187</v>
+        <v>0.547085201793722</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2</v>
+        <v>0.2002152852529602</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5232558139534884</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4375</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.05595238095238095</v>
+        <v>0.05705059203444564</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.4042553191489361</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.4038461538461539</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1095238095238095</v>
+        <v>0.1065662002152852</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.391304347826087</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.3956043956043956</v>
+        <v>0.4081632653061225</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.95</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2761904761904762</v>
+        <v>0.2777179763186222</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.4094827586206897</v>
+        <v>0.3914728682170542</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.39453125</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7684210526315789</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.7037037037037037</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2017543859649123</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3474576271186441</v>
+        <v>0.3490196078431372</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6463414634146342</v>
+        <v>0.6404494382022472</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.0635593220338983</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.3372549019607843</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.425</v>
+        <v>0.4069767441860465</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7440476190476191</v>
+        <v>0.7427341227125942</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.4094827586206897</v>
+        <v>0.3914728682170542</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5705364832535885</v>
+        <v>0.56926341991342</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5511891025641026</v>
+        <v>0.5514831395348837</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5539049568965517</v>
+        <v>0.5526806000000001</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.1058951965065502</v>
+        <v>0.1045364891518738</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1581632653061225</v>
+        <v>0.1562021439509954</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.01219512195121951</v>
+        <v>0.0110803324099723</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1470099667774086</v>
+        <v>0.1470811220621683</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3239202657807309</v>
+        <v>0.3206974981046247</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.226162790697674</v>
+        <v>5.243881118881119</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.20685358255452</v>
+        <v>25.21388101983003</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.305993690851735</v>
+        <v>0.3040604343720491</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.0108695652173913</v>
+        <v>0.0101010101010101</v>
       </c>
     </row>
     <row r="7">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,67 +7135,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>35160</v>
+        <v>38040</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J10" t="n">
-        <v>1198</v>
+        <v>1295</v>
       </c>
       <c r="K10" t="n">
-        <v>1209</v>
+        <v>1307</v>
       </c>
       <c r="L10" t="n">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="M10" t="n">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="N10" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="O10" t="n">
-        <v>2407</v>
+        <v>2602</v>
       </c>
       <c r="P10" t="n">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="Q10" t="n">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="U10" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="V10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="W10" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="X10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AA10" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
@@ -7204,196 +7204,196 @@
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>121</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>313</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI10" t="n">
         <v>27</v>
       </c>
-      <c r="AF10" t="n">
-        <v>112</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>288</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>24</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="n">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="AM10" t="n">
-        <v>640</v>
+        <v>684</v>
       </c>
       <c r="AN10" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="AO10" t="n">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="AP10" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1408</v>
+        <v>1521</v>
       </c>
       <c r="AR10" t="n">
-        <v>1242</v>
+        <v>1364</v>
       </c>
       <c r="AS10" t="n">
+        <v>57</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>106</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>37</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>198</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>113</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>228</v>
+      </c>
+      <c r="BA10" t="n">
         <v>51</v>
       </c>
-      <c r="AT10" t="n">
-        <v>97</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>176</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>105</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>209</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
+        <v>127</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>125</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>504</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>348</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>410</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>453</v>
+      </c>
+      <c r="BH10" t="n">
         <v>45</v>
       </c>
-      <c r="BB10" t="n">
-        <v>114</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>120</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>465</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>334</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>374</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>408</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>42</v>
-      </c>
       <c r="BI10" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="BJ10" t="n">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="BK10" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="BL10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="BM10" t="n">
         <v>4</v>
       </c>
       <c r="BN10" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="BO10" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="BP10" t="n">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="BQ10" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BS10" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="BT10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="BU10" t="n">
         <v>10</v>
       </c>
       <c r="BV10" t="n">
-        <v>742</v>
+        <v>801</v>
       </c>
       <c r="BW10" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="BX10" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="CA10" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="CB10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CC10" t="n">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="CD10" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="CE10" t="n">
-        <v>652</v>
+        <v>700</v>
       </c>
       <c r="CF10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="CG10" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="CH10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="CI10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="CJ10" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="CK10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CL10" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="CM10" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="CN10" t="n">
         <v>15</v>
       </c>
       <c r="CO10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
@@ -7402,44 +7402,44 @@
         <v>6</v>
       </c>
       <c r="CR10" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="CS10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CT10" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="CU10" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="CV10" t="n">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="CW10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CX10" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="CY10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CZ10" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DC10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DD10" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="DE10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -7448,37 +7448,37 @@
         <v>5</v>
       </c>
       <c r="DH10" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="DI10" t="n">
         <v>5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="DK10" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="DL10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DM10" t="n">
         <v>5</v>
       </c>
       <c r="DN10" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="DO10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
         <v>29</v>
       </c>
       <c r="DQ10" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="DR10" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="DS10" t="n">
         <v>5</v>
@@ -7487,238 +7487,238 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1232</v>
+        <v>1323</v>
       </c>
       <c r="DV10" t="n">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="DW10" t="n">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="DX10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="DY10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4717514124293785</v>
+        <v>0.4591029023746702</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.521875</v>
+        <v>0.5132743362831859</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9096385542168675</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.373134328358209</v>
+        <v>0.3755656108597285</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4015748031496063</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.373134328358209</v>
+        <v>0.3755656108597285</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.553125</v>
+        <v>0.554093567251462</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5257731958762887</v>
+        <v>0.5377358490566038</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5023923444976076</v>
+        <v>0.4956140350877193</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5556621880998081</v>
+        <v>0.5577264653641207</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5725190839694656</v>
+        <v>0.5874125874125874</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5340557275541795</v>
+        <v>0.5338028169014084</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5954198473282443</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6265822784810127</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5888324873096447</v>
+        <v>0.5862470862470862</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.3857965451055662</v>
+        <v>0.3925399644760213</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.009950248756218905</v>
+        <v>0.009049773755656109</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07656250000000001</v>
+        <v>0.07602339181286549</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09302325581395349</v>
+        <v>0.09358288770053476</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06787330316742081</v>
+        <v>0.06578947368421052</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.02439024390243903</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.003472222222222222</v>
+        <v>0.003194888178913738</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.4891304347826087</v>
+        <v>0.5073170731707317</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.09375</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6575342465753424</v>
+        <v>0.6624040920716112</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3133802816901409</v>
+        <v>0.33003300330033</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7649122807017544</v>
+        <v>0.7435064935064936</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2874493927125506</v>
+        <v>0.2841328413284133</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.7046153846153846</v>
+        <v>0.698140200286123</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3013182674199623</v>
+        <v>0.3083623693379791</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.3603603603603603</v>
+        <v>0.3801652892561984</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3057851239669421</v>
+        <v>0.3174603174603174</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.25</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2923976608187134</v>
+        <v>0.2887700534759358</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6107382550335571</v>
+        <v>0.6064516129032258</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6703910614525139</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.76</v>
+        <v>0.7230046948356808</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04175365344467641</v>
+        <v>0.05202312138728324</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.580204778157</v>
+        <v>98.49842271293376</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5876288659793815</v>
+        <v>0.5922330097087378</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.54641068447412</v>
+        <v>14.51876447876448</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.66782464846981</v>
+        <v>14.71935730680949</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.96001669449082</v>
+        <v>13.94779922779923</v>
       </c>
       <c r="FV10" t="n">
-        <v>13.90885028949545</v>
+        <v>13.94537107880643</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3301343570057582</v>
+        <v>0.3321492007104796</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.6737967914438503</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7433628318584071</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.4913793103448276</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2120921305182342</v>
+        <v>0.2024866785079929</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4479638009049774</v>
+        <v>0.4429824561403509</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4805825242718447</v>
+        <v>0.4741784037558686</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4343434343434344</v>
+        <v>0.4356435643564356</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07197696737044146</v>
+        <v>0.07282415630550622</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3150684931506849</v>
+        <v>0.325</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.109404990403071</v>
+        <v>0.1145648312611012</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3423423423423423</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2763915547024952</v>
+        <v>0.2779751332149201</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3865814696485623</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3878205128205128</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.875</v>
+        <v>0.8760330578512396</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.4885496183206107</v>
+        <v>0.5034965034965035</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.578125</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1351351351351351</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.07633587786259542</v>
+        <v>0.06993006993006994</v>
       </c>
       <c r="GU10" t="n">
         <v>0.4</v>
@@ -7727,79 +7727,79 @@
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.183206106870229</v>
+        <v>0.1888111888111888</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.5</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3405572755417957</v>
+        <v>0.3436619718309859</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.08359133126934984</v>
+        <v>0.09014084507042254</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.40625</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2693498452012384</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3908045977011494</v>
+        <v>0.4</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7159309021113244</v>
+        <v>0.7246891651865008</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3865814696485623</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5645760827718961</v>
+        <v>0.5647184772929653</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5414744047619047</v>
+        <v>0.5438000000000001</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5545506230529595</v>
+        <v>0.5542689801699716</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1184668989547038</v>
+        <v>0.1162227602905569</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1787634408602151</v>
+        <v>0.1773584905660377</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.007425742574257425</v>
+        <v>0.006756756756756757</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.125</v>
+        <v>0.1301775147928994</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3302556818181818</v>
+        <v>0.3313609467455622</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.7603125</v>
+        <v>5.719883040935673</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.30425</v>
+        <v>25.29840909090909</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3347245409015025</v>
+        <v>0.3374517374517375</v>
       </c>
       <c r="HS10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HT10" t="n">
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.02325581395348837</v>
       </c>
     </row>
     <row r="11">
@@ -11271,163 +11271,163 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>26520</v>
+        <v>29400</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J16" t="n">
-        <v>868</v>
+        <v>965</v>
       </c>
       <c r="K16" t="n">
-        <v>876</v>
+        <v>974</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="M16" t="n">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="N16" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="O16" t="n">
-        <v>1744</v>
+        <v>1939</v>
       </c>
       <c r="P16" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="Q16" t="n">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="R16" t="n">
         <v>23</v>
       </c>
       <c r="S16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="W16" t="n">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="X16" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AA16" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>9</v>
       </c>
       <c r="AE16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF16" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG16" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="n">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="AM16" t="n">
-        <v>462</v>
+        <v>520</v>
       </c>
       <c r="AN16" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="AO16" t="n">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="AP16" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1085</v>
+        <v>1207</v>
       </c>
       <c r="AR16" t="n">
-        <v>959</v>
+        <v>1072</v>
       </c>
       <c r="AS16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AT16" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AW16" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AX16" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AY16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AZ16" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="BA16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="BC16" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="BD16" t="n">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="BE16" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="BF16" t="n">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="BG16" t="n">
-        <v>339</v>
+        <v>378</v>
       </c>
       <c r="BH16" t="n">
         <v>48</v>
@@ -11436,100 +11436,100 @@
         <v>38</v>
       </c>
       <c r="BJ16" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="BK16" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="BL16" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BM16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN16" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="BO16" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="BP16" t="n">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="BQ16" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="BR16" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="BS16" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="BT16" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BV16" t="n">
-        <v>577</v>
+        <v>658</v>
       </c>
       <c r="BW16" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="BX16" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="CA16" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="CB16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CC16" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="CD16" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="CE16" t="n">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="CF16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CG16" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="CH16" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="CI16" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CJ16" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CK16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CL16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CM16" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="CN16" t="n">
         <v>11</v>
       </c>
       <c r="CO16" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CP16" t="n">
         <v>3</v>
@@ -11538,46 +11538,46 @@
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="CS16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CT16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="CU16" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="CV16" t="n">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
+        <v>19</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>212</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC16" t="n">
         <v>18</v>
       </c>
-      <c r="CY16" t="n">
-        <v>14</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>191</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>17</v>
-      </c>
       <c r="DD16" t="n">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="DE16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="DF16" t="n">
         <v>2</v>
@@ -11586,16 +11586,16 @@
         <v>4</v>
       </c>
       <c r="DH16" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="DI16" t="n">
         <v>3</v>
       </c>
       <c r="DJ16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="DK16" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="DL16" t="n">
         <v>1</v>
@@ -11604,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="DN16" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="DO16" t="n">
         <v>3</v>
@@ -11613,324 +11613,326 @@
         <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="DR16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DS16" t="inlineStr"/>
       <c r="DT16" t="n">
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>945</v>
+        <v>1050</v>
       </c>
       <c r="DV16" t="n">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="DW16" t="n">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="DX16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DY16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4440298507462687</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.4779116465863454</v>
+        <v>0.498220640569395</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.875968992248062</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.3794117647058823</v>
+        <v>0.3776595744680851</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.3775510204081632</v>
+        <v>0.3619047619047619</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.3794117647058823</v>
+        <v>0.3776595744680851</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.5800865800865801</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.5508474576271186</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.5754364089775561</v>
+        <v>0.5725446428571429</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.625</v>
+        <v>0.6018518518518519</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.5578703703703703</v>
+        <v>0.55</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.6100451467268623</v>
+        <v>0.6075757575757575</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.628</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.6091269841269841</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4239401496259352</v>
+        <v>0.4196428571428572</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01176470588235294</v>
+        <v>0.01329787234042553</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.05194805194805195</v>
+        <v>0.05576923076923077</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06944444444444445</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.05945945945945946</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.02531645569620253</v>
+        <v>0.03157894736842105</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01619433198380567</v>
+        <v>0.01503759398496241</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.85</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.6713615023474179</v>
+        <v>0.6508620689655172</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.3193717277486911</v>
+        <v>0.3133640552995391</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.6852791878172588</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.2980769230769231</v>
+        <v>0.3203463203463203</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.6780487804878049</v>
+        <v>0.6710816777041942</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.3082706766917293</v>
+        <v>0.3169642857142857</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.1956521739130435</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.3376623376623377</v>
+        <v>0.3772455089820359</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.171875</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.569620253164557</v>
+        <v>0.550561797752809</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.7191011235955056</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.678082191780822</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.711864406779661</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.02964959568733154</v>
+        <v>0.03381642512077294</v>
       </c>
       <c r="FQ16" t="n">
-        <v>94.69683257918552</v>
+        <v>94.97142857142858</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="FS16" t="n">
-        <v>14.74953917050691</v>
+        <v>14.82632124352332</v>
       </c>
       <c r="FT16" t="n">
-        <v>15.65913242009132</v>
+        <v>15.49548254620123</v>
       </c>
       <c r="FU16" t="n">
-        <v>14.12569124423963</v>
+        <v>14.16777202072539</v>
       </c>
       <c r="FV16" t="n">
-        <v>14.9953196347032</v>
+        <v>14.8605749486653</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.2468827930174564</v>
+        <v>0.2410714285714286</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.7323232323232324</v>
+        <v>0.7268518518518519</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.7754010695187166</v>
+        <v>0.7810945273631841</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.5241379310344828</v>
+        <v>0.554140127388535</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.2306733167082294</v>
+        <v>0.2332589285714286</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.4928229665071771</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5202020202020202</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.4466019417475728</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.09850374064837905</v>
+        <v>0.1060267857142857</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.4177215189873418</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="GH16" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.175</v>
       </c>
       <c r="GI16" t="n">
-        <v>0.1159600997506234</v>
+        <v>0.1227678571428571</v>
       </c>
       <c r="GJ16" t="n">
-        <v>0.4086021505376344</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="GK16" t="n">
-        <v>0.4086021505376344</v>
+        <v>0.4128440366972477</v>
       </c>
       <c r="GL16" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9777777777777777</v>
       </c>
       <c r="GM16" t="n">
-        <v>0.3079800498753117</v>
+        <v>0.296875</v>
       </c>
       <c r="GN16" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3646616541353384</v>
       </c>
       <c r="GO16" t="n">
-        <v>0.3744855967078189</v>
+        <v>0.3702290076335878</v>
       </c>
       <c r="GP16" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="GQ16" t="n">
-        <v>0.375</v>
+        <v>0.3425925925925926</v>
       </c>
       <c r="GR16" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="GS16" t="n">
         <v>0.1739130434782609</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.0625</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="GU16" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GV16" t="n">
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.34375</v>
+        <v>0.3425925925925926</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4324324324324325</v>
       </c>
       <c r="GY16" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.875</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.2546296296296297</v>
+        <v>0.25</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.1203703703703704</v>
+        <v>0.1125</v>
       </c>
       <c r="HC16" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.325</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3717948717948718</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6708229426433915</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3646616541353384</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.5400105757196496</v>
+        <v>0.5396019596864502</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5265270491803279</v>
+        <v>0.5284902985074627</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.5360640186915887</v>
+        <v>0.5318521008403361</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.08826945412311266</v>
+        <v>0.09138110072689512</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1403846153846154</v>
+        <v>0.1450511945392491</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.008797653958944282</v>
+        <v>0.007957559681697613</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1300745650372825</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.2847926267281106</v>
+        <v>0.2792046396023198</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.187445887445887</v>
+        <v>7.436153846153847</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.38902077151335</v>
+        <v>25.31179624664879</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.2764976958525346</v>
+        <v>0.2756476683937824</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
-      <c r="HU16" t="inlineStr"/>
+      <c r="HU16" t="n">
+        <v>0.00909090909090909</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -2999,265 +2999,265 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>44100</v>
+        <v>46980</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>-5</v>
       </c>
       <c r="J4" t="n">
-        <v>1447</v>
+        <v>1534</v>
       </c>
       <c r="K4" t="n">
-        <v>1458</v>
+        <v>1547</v>
       </c>
       <c r="L4" t="n">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="M4" t="n">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="N4" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="O4" t="n">
-        <v>2905</v>
+        <v>3081</v>
       </c>
       <c r="P4" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="Q4" t="n">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T4" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U4" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="V4" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="W4" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AA4" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AB4" t="n">
         <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AF4" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG4" t="n">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AJ4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AK4" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AL4" t="n">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="AM4" t="n">
-        <v>666</v>
+        <v>711</v>
       </c>
       <c r="AN4" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="AO4" t="n">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="AP4" t="n">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1649</v>
+        <v>1742</v>
       </c>
       <c r="AR4" t="n">
-        <v>1638</v>
+        <v>1747</v>
       </c>
       <c r="AS4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AU4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AW4" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AX4" t="n">
+        <v>238</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>119</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>221</v>
       </c>
-      <c r="AY4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>208</v>
-      </c>
       <c r="BA4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="BB4" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="BC4" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="BD4" t="n">
-        <v>558</v>
+        <v>596</v>
       </c>
       <c r="BE4" t="n">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="BF4" t="n">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="BG4" t="n">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="BH4" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="BI4" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="BJ4" t="n">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="BK4" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BL4" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BM4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN4" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="BO4" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="BP4" t="n">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="BQ4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BS4" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="BT4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="BU4" t="n">
         <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>809</v>
+        <v>845</v>
       </c>
       <c r="BW4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BX4" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="BY4" t="n">
         <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="CA4" t="n">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="CB4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="CC4" t="n">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="CD4" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="CE4" t="n">
-        <v>721</v>
+        <v>769</v>
       </c>
       <c r="CF4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CG4" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="CH4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="CI4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CJ4" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="CK4" t="n">
         <v>23</v>
       </c>
       <c r="CL4" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="CM4" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="CN4" t="n">
         <v>20</v>
       </c>
       <c r="CO4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="CP4" t="n">
         <v>9</v>
@@ -3266,46 +3266,46 @@
         <v>9</v>
       </c>
       <c r="CR4" t="n">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="CS4" t="n">
         <v>33</v>
       </c>
       <c r="CT4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="CU4" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="CV4" t="n">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="CW4" t="n">
         <v>3</v>
       </c>
       <c r="CX4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="CY4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CZ4" t="n">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="DA4" t="n">
         <v>4</v>
       </c>
       <c r="DB4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="DC4" t="n">
         <v>29</v>
       </c>
       <c r="DD4" t="n">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="DE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DF4" t="n">
         <v>6</v>
@@ -3314,352 +3314,352 @@
         <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="DI4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="DK4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="DL4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DN4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="DR4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="DS4" t="inlineStr"/>
       <c r="DT4" t="n">
         <v>2</v>
       </c>
       <c r="DU4" t="n">
-        <v>1428</v>
+        <v>1504</v>
       </c>
       <c r="DV4" t="n">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="DW4" t="n">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="DX4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="DY4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.4973404255319149</v>
+        <v>0.492462311557789</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.5451895043731778</v>
+        <v>0.5429362880886427</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.7512953367875648</v>
+        <v>0.7475247524752475</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.3344887348353553</v>
+        <v>0.3300653594771242</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.25</v>
+        <v>0.2537313432835821</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.3106796116504854</v>
+        <v>0.3087557603686636</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.3344887348353553</v>
+        <v>0.3300653594771242</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.5645645645645646</v>
+        <v>0.559774964838256</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.594059405940594</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.5288461538461539</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.5353982300884956</v>
+        <v>0.5298563869992441</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.509090909090909</v>
+        <v>0.5112994350282486</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.4975845410628019</v>
+        <v>0.5011415525114156</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.5730688935281837</v>
+        <v>0.5678851174934726</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.5497512437810945</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.5536779324055666</v>
+        <v>0.5560747663551402</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4641995172968624</v>
+        <v>0.4625850340136055</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0121317157712305</v>
+        <v>0.0130718954248366</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.1066066066066066</v>
+        <v>0.1054852320675106</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.09210526315789473</v>
+        <v>0.09393939393939393</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.124203821656051</v>
+        <v>0.1208459214501511</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.08</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.009280742459396751</v>
+        <v>0.01089324618736384</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5670498084291188</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.1636363636363636</v>
+        <v>0.15</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.6305418719211823</v>
+        <v>0.6367924528301887</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.4020979020979021</v>
+        <v>0.4174757281553398</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.703971119133574</v>
+        <v>0.7</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.3054054054054054</v>
+        <v>0.2904040404040404</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.6603221083455344</v>
+        <v>0.6629834254143646</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.3475609756097561</v>
+        <v>0.3460992907801418</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.3368421052631579</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.4785276073619632</v>
+        <v>0.4770114942528735</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.2</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.3057553956834532</v>
+        <v>0.29</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.5657894736842105</v>
+        <v>0.5786163522012578</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.645</v>
+        <v>0.6490384615384616</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.7543859649122807</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.7281553398058253</v>
+        <v>0.7232142857142857</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.6338028169014085</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.04655172413793104</v>
+        <v>0.04807692307692308</v>
       </c>
       <c r="FQ4" t="n">
-        <v>94.85714285714286</v>
+        <v>94.43678160919541</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.4938271604938271</v>
+        <v>0.5232558139534884</v>
       </c>
       <c r="FS4" t="n">
-        <v>15.38887353144437</v>
+        <v>15.38057366362451</v>
       </c>
       <c r="FT4" t="n">
-        <v>14.9741426611797</v>
+        <v>15.11712992889463</v>
       </c>
       <c r="FU4" t="n">
-        <v>14.5852798894264</v>
+        <v>14.58468057366362</v>
       </c>
       <c r="FV4" t="n">
-        <v>14.24183813443073</v>
+        <v>14.37472527472528</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2445695897023331</v>
+        <v>0.2494331065759637</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6787878787878788</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.7536231884057971</v>
+        <v>0.7491638795986622</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.5288461538461539</v>
+        <v>0.5223214285714286</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.252614641995173</v>
+        <v>0.2501889644746788</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.4713375796178344</v>
+        <v>0.4652567975830816</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.5381818181818182</v>
+        <v>0.5292096219931272</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.472972972972973</v>
+        <v>0.4675324675324675</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.03861625100563153</v>
+        <v>0.03779289493575208</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="GH4" t="n">
         <v>0.35</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.1174577634754626</v>
+        <v>0.1156462585034014</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3725490196078431</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3776223776223776</v>
+        <v>0.38</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3467417538213998</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3225058004640371</v>
+        <v>0.3159041394335512</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3255269320843091</v>
+        <v>0.3193832599118943</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.697841726618705</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.3878787878787879</v>
+        <v>0.4011299435028249</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.640625</v>
+        <v>0.6338028169014085</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.08484848484848485</v>
+        <v>0.0847457627118644</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GV4" t="n">
         <v>0.4</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2937853107344633</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.22</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="GY4" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.2270531400966184</v>
+        <v>0.2305936073059361</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.6732673267326733</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.1207729468599034</v>
+        <v>0.1187214611872146</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.42</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3768115942028986</v>
+        <v>0.3767123287671233</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.2756410256410257</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.7087691069991955</v>
+        <v>0.7120181405895691</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3225058004640371</v>
+        <v>0.3159041394335512</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.545791551584078</v>
+        <v>0.5464061403508772</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.5445642156862744</v>
+        <v>0.5462261061946903</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.5365751851851852</v>
+        <v>0.5369891608391608</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.1234657039711191</v>
+        <v>0.1227951153324288</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.195244055068836</v>
+        <v>0.1936619718309859</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.02559726962457338</v>
+        <v>0.02572347266881029</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.134020618556701</v>
+        <v>0.1366245694603904</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3383869011522135</v>
+        <v>0.3421354764638347</v>
       </c>
       <c r="HP4" t="n">
-        <v>5.614414414414414</v>
+        <v>5.581012658227848</v>
       </c>
       <c r="HQ4" t="n">
-        <v>25.62771929824561</v>
+        <v>25.59140495867769</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.331720801658604</v>
+        <v>0.333116036505867</v>
       </c>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
       <c r="HU4" t="n">
-        <v>0.02054794520547945</v>
+        <v>0.0196078431372549</v>
       </c>
     </row>
     <row r="5">
@@ -4377,310 +4377,310 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>31980</v>
+        <v>34860</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="J6" t="n">
-        <v>1059</v>
+        <v>1147</v>
       </c>
       <c r="K6" t="n">
-        <v>1070</v>
+        <v>1158</v>
       </c>
       <c r="L6" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="M6" t="n">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="N6" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="O6" t="n">
-        <v>2129</v>
+        <v>2305</v>
       </c>
       <c r="P6" t="n">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="Q6" t="n">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="R6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="T6" t="n">
+        <v>62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>97</v>
+      </c>
+      <c r="V6" t="n">
+        <v>100</v>
+      </c>
+      <c r="W6" t="n">
+        <v>204</v>
+      </c>
+      <c r="X6" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y6" t="n">
         <v>57</v>
       </c>
-      <c r="U6" t="n">
-        <v>89</v>
-      </c>
-      <c r="V6" t="n">
-        <v>90</v>
-      </c>
-      <c r="W6" t="n">
-        <v>186</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="n">
         <v>21</v>
       </c>
-      <c r="Y6" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>99</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>17</v>
-      </c>
       <c r="AF6" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="AG6" t="n">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AL6" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="AM6" t="n">
-        <v>572</v>
+        <v>621</v>
       </c>
       <c r="AN6" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="AO6" t="n">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="AP6" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1319</v>
+        <v>1428</v>
       </c>
       <c r="AR6" t="n">
-        <v>1114</v>
+        <v>1207</v>
       </c>
       <c r="AS6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AT6" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AU6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AW6" t="n">
         <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AY6" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AZ6" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="BA6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="BB6" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="BC6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BD6" t="n">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="BE6" t="n">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="BF6" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="BG6" t="n">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="BH6" t="n">
         <v>81</v>
       </c>
       <c r="BI6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BJ6" t="n">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="BK6" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="BL6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="BM6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN6" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="BO6" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="BP6" t="n">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="BQ6" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BS6" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="BT6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BU6" t="n">
         <v>8</v>
       </c>
       <c r="BV6" t="n">
-        <v>678</v>
+        <v>755</v>
       </c>
       <c r="BW6" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>225</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>181</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>37</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>443</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>170</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>613</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>21</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>100</v>
+      </c>
+      <c r="CH6" t="n">
         <v>58</v>
       </c>
-      <c r="BX6" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>201</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>172</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>32</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>405</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>157</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>562</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>19</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>95</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>54</v>
-      </c>
       <c r="CI6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CJ6" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="CK6" t="n">
         <v>17</v>
       </c>
       <c r="CL6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CM6" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="CN6" t="n">
         <v>8</v>
       </c>
       <c r="CO6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CP6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CQ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CR6" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="CS6" t="n">
         <v>15</v>
       </c>
       <c r="CT6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="CU6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="CV6" t="n">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CY6" t="n">
         <v>18</v>
       </c>
       <c r="CZ6" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="DA6" t="n">
         <v>3</v>
       </c>
       <c r="DB6" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="DC6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="DD6" t="n">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="DE6" t="n">
         <v>21</v>
@@ -4690,354 +4690,354 @@
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="DI6" t="n">
         <v>4</v>
       </c>
       <c r="DJ6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="DK6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DL6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DM6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DQ6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="DR6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="DS6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1125</v>
+        <v>1222</v>
       </c>
       <c r="DV6" t="n">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="DW6" t="n">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="DX6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="DY6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5029940119760479</v>
+        <v>0.5123287671232877</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5490196078431373</v>
+        <v>0.5565476190476191</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8246753246753247</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3949579831932773</v>
+        <v>0.3908629441624366</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4368932038834951</v>
+        <v>0.4375</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3949579831932773</v>
+        <v>0.3908629441624366</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.583916083916084</v>
+        <v>0.5877616747181964</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6136363636363636</v>
+        <v>0.6195652173913043</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5460526315789473</v>
+        <v>0.5562130177514792</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5871905274488698</v>
+        <v>0.587192118226601</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.7137096774193549</v>
+        <v>0.7052238805970149</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5901960784313726</v>
+        <v>0.5960854092526691</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6163227016885553</v>
+        <v>0.6138912855910268</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.708029197080292</v>
+        <v>0.6959459459459459</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6302395209580839</v>
+        <v>0.6322314049586777</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3842841765339075</v>
+        <v>0.3881773399014778</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.008403361344537815</v>
+        <v>0.01015228426395939</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07867132867132867</v>
+        <v>0.07890499194847021</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.09009009009009009</v>
+        <v>0.09166666666666666</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.07526881720430108</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.007751937984496124</v>
+        <v>0.01056338028169014</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5328947368421053</v>
+        <v>0.53125</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.925</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7257383966244726</v>
+        <v>0.6961538461538461</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.3948497854077253</v>
+        <v>0.3824701195219123</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.7335766423357665</v>
+        <v>0.75</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2748815165876777</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7299412915851272</v>
+        <v>0.725</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3378378378378378</v>
+        <v>0.334020618556701</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.358695652173913</v>
+        <v>0.35</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.243421052631579</v>
+        <v>0.2529411764705882</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3559322033898305</v>
+        <v>0.359375</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.7</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.75</v>
+        <v>0.7317073170731707</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6973684210526315</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.04797979797979798</v>
+        <v>0.04861111111111111</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.86491557223265</v>
+        <v>95.21514629948365</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.78508026440038</v>
+        <v>15.92877070619006</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.26504672897196</v>
+        <v>14.32616580310881</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.10217186024552</v>
+        <v>15.22781168265039</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.71476635514019</v>
+        <v>13.76753022452504</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.3584499461786868</v>
+        <v>0.354679802955665</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6696696696696697</v>
+        <v>0.675</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.735973597359736</v>
+        <v>0.7431192660550459</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.547085201793722</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2002152852529602</v>
+        <v>0.2009852216748768</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.5232558139534884</v>
+        <v>0.5291005291005291</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.44</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.05705059203444564</v>
+        <v>0.0561576354679803</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1065662002152852</v>
+        <v>0.1083743842364532</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.404040404040404</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4081632653061225</v>
+        <v>0.4128440366972477</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.95</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2777179763186222</v>
+        <v>0.2798029556650246</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3914728682170542</v>
+        <v>0.3838028169014084</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.39453125</v>
+        <v>0.3879003558718861</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.7706422018348624</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.4552238805970149</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6721311475409836</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.08955223880597014</v>
       </c>
       <c r="GU6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="GV6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="GW6" t="n">
+        <v>0.2238805970149254</v>
+      </c>
+      <c r="GX6" t="n">
         <v>0.6</v>
       </c>
-      <c r="GV6" t="n">
+      <c r="GY6" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="GW6" t="n">
-        <v>0.2096774193548387</v>
-      </c>
-      <c r="GX6" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="GY6" t="n">
-        <v>0.8235294117647058</v>
-      </c>
       <c r="GZ6" t="n">
-        <v>0.3490196078431372</v>
+        <v>0.3451957295373665</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6404494382022472</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07473309608540925</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3372549019607843</v>
+        <v>0.3238434163701068</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.4069767441860465</v>
+        <v>0.3956043956043956</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7427341227125942</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3914728682170542</v>
+        <v>0.3838028169014084</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.56926341991342</v>
+        <v>0.5682110505450941</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5514831395348837</v>
+        <v>0.5473632978723405</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5526806000000001</v>
+        <v>0.5502225454545455</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.1045364891518738</v>
+        <v>0.09963768115942029</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1562021439509954</v>
+        <v>0.1501416430594901</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.0110803324099723</v>
+        <v>0.01005025125628141</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1470811220621683</v>
+        <v>0.1442577030812325</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3206974981046247</v>
+        <v>0.3228291316526611</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.243881118881119</v>
+        <v>5.257004830917874</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.21388101983003</v>
+        <v>25.21516709511568</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.3040604343720491</v>
+        <v>0.3042720139494333</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.0101010101010101</v>
+        <v>0.00909090909090909</v>
       </c>
     </row>
     <row r="7">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,311 +7135,311 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>38040</v>
+        <v>40920</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="J10" t="n">
-        <v>1295</v>
+        <v>1392</v>
       </c>
       <c r="K10" t="n">
-        <v>1307</v>
+        <v>1404</v>
       </c>
       <c r="L10" t="n">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="M10" t="n">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="N10" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="O10" t="n">
-        <v>2602</v>
+        <v>2796</v>
       </c>
       <c r="P10" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="Q10" t="n">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="T10" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U10" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="V10" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="W10" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Z10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA10" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="AG10" t="n">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AK10" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AL10" t="n">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="AM10" t="n">
-        <v>684</v>
+        <v>723</v>
       </c>
       <c r="AN10" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AO10" t="n">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="AP10" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1521</v>
+        <v>1629</v>
       </c>
       <c r="AR10" t="n">
-        <v>1364</v>
+        <v>1487</v>
       </c>
       <c r="AS10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AT10" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AX10" t="n">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="AY10" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="AZ10" t="n">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="BA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>140</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>141</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>550</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>378</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>422</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>486</v>
+      </c>
+      <c r="BH10" t="n">
         <v>51</v>
       </c>
-      <c r="BB10" t="n">
-        <v>127</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>125</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>504</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>348</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>410</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>453</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>45</v>
-      </c>
       <c r="BI10" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="BJ10" t="n">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="BK10" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="BL10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BM10" t="n">
         <v>4</v>
       </c>
       <c r="BN10" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BO10" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="BP10" t="n">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="BQ10" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="BR10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="BS10" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="BT10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BU10" t="n">
         <v>10</v>
       </c>
       <c r="BV10" t="n">
-        <v>801</v>
+        <v>864</v>
       </c>
       <c r="BW10" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="BX10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="CA10" t="n">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="CB10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC10" t="n">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="CD10" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="CE10" t="n">
-        <v>700</v>
+        <v>743</v>
       </c>
       <c r="CF10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CG10" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="CH10" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="CI10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CJ10" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="CK10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CM10" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="CN10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CO10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CR10" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="CS10" t="n">
         <v>17</v>
       </c>
       <c r="CT10" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="CU10" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="CV10" t="n">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="CW10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CX10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CY10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CZ10" t="n">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="DC10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DD10" t="n">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="DE10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -7448,37 +7448,37 @@
         <v>5</v>
       </c>
       <c r="DH10" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="DI10" t="n">
         <v>5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="DK10" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="DL10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DM10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DN10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DP10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="DQ10" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="DR10" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="DS10" t="n">
         <v>5</v>
@@ -7487,310 +7487,310 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1323</v>
+        <v>1414</v>
       </c>
       <c r="DV10" t="n">
-        <v>502</v>
+        <v>548</v>
       </c>
       <c r="DW10" t="n">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="DX10" t="n">
+        <v>36</v>
+      </c>
+      <c r="DY10" t="n">
         <v>30</v>
       </c>
-      <c r="DY10" t="n">
-        <v>27</v>
-      </c>
       <c r="DZ10" t="n">
-        <v>0.4591029023746702</v>
+        <v>0.4725</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5132743362831859</v>
+        <v>0.5279329608938548</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9096385542168675</v>
+        <v>0.9050279329608939</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3755656108597285</v>
+        <v>0.3706004140786749</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.4015748031496063</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3755656108597285</v>
+        <v>0.3706004140786749</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.554093567251462</v>
+        <v>0.5532503457814661</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5377358490566038</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4956140350877193</v>
+        <v>0.5</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5577264653641207</v>
+        <v>0.5543117744610282</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5874125874125874</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5338028169014084</v>
+        <v>0.5325520833333334</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.5948023426061494</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6265822784810127</v>
+        <v>0.6323529411764706</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5862470862470862</v>
+        <v>0.5890557939914163</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.3925399644760213</v>
+        <v>0.400497512437811</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.009049773755656109</v>
+        <v>0.008281573498964804</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07602339181286549</v>
+        <v>0.07468879668049792</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09358288770053476</v>
+        <v>0.09296482412060302</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06578947368421052</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02298850574712644</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.003194888178913738</v>
+        <v>0.002958579881656805</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5073170731707317</v>
+        <v>0.5045454545454545</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6624040920716112</v>
+        <v>0.6690997566909975</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.33003300330033</v>
+        <v>0.3271028037383177</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7435064935064936</v>
+        <v>0.7386018237082067</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2841328413284133</v>
+        <v>0.2809364548494983</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.698140200286123</v>
+        <v>0.7</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3083623693379791</v>
+        <v>0.3048387096774193</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.3801652892561984</v>
+        <v>0.3875968992248062</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3174603174603174</v>
+        <v>0.3129770992366412</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.25</v>
+        <v>0.2295081967213115</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2887700534759358</v>
+        <v>0.2906403940886699</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6064516129032258</v>
+        <v>0.6037735849056604</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6703910614525139</v>
+        <v>0.6772486772486772</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7230046948356808</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.05202312138728324</v>
+        <v>0.0497335701598579</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.49842271293376</v>
+        <v>98.39296187683284</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5922330097087378</v>
+        <v>0.5871559633027523</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.51876447876448</v>
+        <v>14.4989224137931</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.71935730680949</v>
+        <v>14.77029914529914</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.94779922779923</v>
+        <v>13.9239224137931</v>
       </c>
       <c r="FV10" t="n">
-        <v>13.94537107880643</v>
+        <v>14.03333333333333</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3321492007104796</v>
+        <v>0.330016583747927</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6737967914438503</v>
+        <v>0.6733668341708543</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7433628318584071</v>
+        <v>0.7423822714681441</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4888059701492538</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2024866785079929</v>
+        <v>0.1973466003316749</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4429824561403509</v>
+        <v>0.4453781512605042</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4741784037558686</v>
+        <v>0.4753363228699551</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4356435643564356</v>
+        <v>0.4528301886792453</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07282415630550622</v>
+        <v>0.07213930348258707</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.2988505747126437</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.325</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="GH10" t="n">
         <v>0.3846153846153846</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1145648312611012</v>
+        <v>0.1202321724709784</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3488372093023256</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2779751332149201</v>
+        <v>0.2802653399668325</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3865814696485623</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3878205128205128</v>
+        <v>0.3857566765578635</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8760330578512396</v>
+        <v>0.8692307692307693</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5034965034965035</v>
+        <v>0.5032679738562091</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.5974025974025974</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1162790697674419</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06993006993006994</v>
+        <v>0.0718954248366013</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.4</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.1888111888111888</v>
+        <v>0.2026143790849673</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3436619718309859</v>
+        <v>0.3385416666666667</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5737704918032787</v>
+        <v>0.5923076923076923</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.09014084507042254</v>
+        <v>0.08854166666666667</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.40625</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.2760416666666667</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.4</v>
+        <v>0.3867924528301887</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7246891651865008</v>
+        <v>0.7305140961857379</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3865814696485623</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5647184772929653</v>
+        <v>0.5649832917705736</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5438000000000001</v>
+        <v>0.5431546391752577</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5542689801699716</v>
+        <v>0.5528777486910995</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1162227602905569</v>
+        <v>0.118796992481203</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1773584905660377</v>
+        <v>0.1834319526627219</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.006756756756756757</v>
+        <v>0.006185567010309278</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1301775147928994</v>
+        <v>0.1319828115408226</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3313609467455622</v>
+        <v>0.3376304481276857</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.719883040935673</v>
+        <v>5.704840940525588</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.29840909090909</v>
+        <v>25.28752598752599</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3374517374517375</v>
+        <v>0.3441091954022988</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.02068965517241379</v>
       </c>
     </row>
     <row r="11">
@@ -11271,67 +11271,67 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>29400</v>
+        <v>32280</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="J16" t="n">
-        <v>965</v>
+        <v>1061</v>
       </c>
       <c r="K16" t="n">
-        <v>974</v>
+        <v>1072</v>
       </c>
       <c r="L16" t="n">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="M16" t="n">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="N16" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="O16" t="n">
-        <v>1939</v>
+        <v>2133</v>
       </c>
       <c r="P16" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="Q16" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="R16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="S16" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="T16" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="V16" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="W16" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="X16" t="n">
         <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="Z16" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
@@ -11340,196 +11340,196 @@
         <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="n">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AK16" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="AM16" t="n">
-        <v>520</v>
+        <v>563</v>
       </c>
       <c r="AN16" t="n">
+        <v>159</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>415</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>209</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>49</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>179</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>79</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>142</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="BA16" t="n">
+        <v>43</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>117</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>89</v>
+      </c>
+      <c r="BD16" t="n">
         <v>376</v>
       </c>
-      <c r="AP16" t="n">
-        <v>181</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1207</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1072</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>35</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>62</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>157</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>135</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>105</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>73</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>337</v>
-      </c>
       <c r="BE16" t="n">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="BF16" t="n">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="BG16" t="n">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="BH16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BI16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BJ16" t="n">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="BK16" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="BL16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BM16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN16" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="BO16" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="BP16" t="n">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="BQ16" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="BR16" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="BS16" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BT16" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="BU16" t="n">
         <v>7</v>
       </c>
       <c r="BV16" t="n">
-        <v>658</v>
+        <v>732</v>
       </c>
       <c r="BW16" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="BX16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="CA16" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="CB16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CC16" t="n">
-        <v>321</v>
+        <v>356</v>
       </c>
       <c r="CD16" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="CE16" t="n">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="CF16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CG16" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="CH16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="CI16" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CJ16" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="CK16" t="n">
         <v>9</v>
       </c>
       <c r="CL16" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="CM16" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="CN16" t="n">
         <v>11</v>
       </c>
       <c r="CO16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="CP16" t="n">
         <v>3</v>
@@ -11538,64 +11538,64 @@
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="CS16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CU16" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="CV16" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CY16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CZ16" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="DA16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DB16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="DC16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="DD16" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="DE16" t="n">
         <v>19</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG16" t="n">
         <v>4</v>
       </c>
       <c r="DH16" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="DI16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="DK16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="DL16" t="n">
         <v>1</v>
@@ -11604,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="DN16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="DO16" t="n">
         <v>3</v>
@@ -11613,248 +11613,250 @@
         <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="DR16" t="n">
         <v>28</v>
       </c>
-      <c r="DS16" t="inlineStr"/>
+      <c r="DS16" t="n">
+        <v>1</v>
+      </c>
       <c r="DT16" t="n">
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>1050</v>
+        <v>1151</v>
       </c>
       <c r="DV16" t="n">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="DW16" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="DX16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="DY16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4751552795031056</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.498220640569395</v>
+        <v>0.5083056478405316</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.8873239436619719</v>
+        <v>0.8930817610062893</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.3776595744680851</v>
+        <v>0.3831325301204819</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.3619047619047619</v>
+        <v>0.3675213675213675</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.3776595744680851</v>
+        <v>0.3831325301204819</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5719360568383659</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5846153846153846</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5563380281690141</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.5725446428571429</v>
+        <v>0.5731083844580777</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.6018518518518519</v>
+        <v>0.6359649122807017</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.55</v>
+        <v>0.5540540540540541</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.6075757575757575</v>
+        <v>0.609935602575897</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.628</v>
+        <v>0.667910447761194</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.5982142857142857</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4196428571428572</v>
+        <v>0.4243353783231084</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01329787234042553</v>
+        <v>0.01445783132530121</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.05576923076923077</v>
+        <v>0.06039076376554174</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.06944444444444445</v>
+        <v>0.06926406926406926</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.05652173913043478</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.03157894736842105</v>
+        <v>0.04901960784313725</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01503759398496241</v>
+        <v>0.01689189189189189</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.5343511450381679</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.85</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.6508620689655172</v>
+        <v>0.656</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.3133640552995391</v>
+        <v>0.3037974683544304</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6987951807228916</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.3203463203463203</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.6710816777041942</v>
+        <v>0.6773547094188377</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.3169642857142857</v>
+        <v>0.3128834355828221</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1639344262295082</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.3772455089820359</v>
+        <v>0.375</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.171875</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.550561797752809</v>
+        <v>0.5463917525773195</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.7070707070707071</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.6851851851851852</v>
+        <v>0.6853932584269663</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.711864406779661</v>
+        <v>0.7323943661971831</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.03381642512077294</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="FQ16" t="n">
-        <v>94.97142857142858</v>
+        <v>95.15241635687732</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5490196078431373</v>
       </c>
       <c r="FS16" t="n">
-        <v>14.82632124352332</v>
+        <v>14.89792648444863</v>
       </c>
       <c r="FT16" t="n">
-        <v>15.49548254620123</v>
+        <v>15.36688432835821</v>
       </c>
       <c r="FU16" t="n">
-        <v>14.16777202072539</v>
+        <v>14.27719132893497</v>
       </c>
       <c r="FV16" t="n">
-        <v>14.8605749486653</v>
+        <v>14.73311567164179</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.2410714285714286</v>
+        <v>0.2361963190184049</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.7268518518518519</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.7810945273631841</v>
+        <v>0.7813953488372093</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.554140127388535</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.2332589285714286</v>
+        <v>0.2351738241308793</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.4956521739130435</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.5202020202020202</v>
+        <v>0.5253456221198156</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.4466019417475728</v>
+        <v>0.4649122807017544</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.1060267857142857</v>
+        <v>0.1042944785276074</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="GH16" t="n">
         <v>0.175</v>
       </c>
       <c r="GI16" t="n">
-        <v>0.1227678571428571</v>
+        <v>0.1216768916155419</v>
       </c>
       <c r="GJ16" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4201680672268908</v>
       </c>
       <c r="GK16" t="n">
-        <v>0.4128440366972477</v>
+        <v>0.423728813559322</v>
       </c>
       <c r="GL16" t="n">
-        <v>0.9777777777777777</v>
+        <v>0.98</v>
       </c>
       <c r="GM16" t="n">
-        <v>0.296875</v>
+        <v>0.3026584867075665</v>
       </c>
       <c r="GN16" t="n">
-        <v>0.3646616541353384</v>
+        <v>0.3682432432432433</v>
       </c>
       <c r="GO16" t="n">
-        <v>0.3702290076335878</v>
+        <v>0.3745704467353952</v>
       </c>
       <c r="GP16" t="n">
-        <v>0.845360824742268</v>
+        <v>0.8532110091743119</v>
       </c>
       <c r="GQ16" t="n">
-        <v>0.3425925925925926</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="GR16" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.65</v>
       </c>
       <c r="GS16" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07894736842105263</v>
       </c>
       <c r="GU16" t="n">
         <v>0.4444444444444444</v>
@@ -11863,75 +11865,75 @@
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.3425925925925926</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.4324324324324325</v>
+        <v>0.475</v>
       </c>
       <c r="GY16" t="n">
-        <v>0.875</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.25</v>
+        <v>0.2548262548262548</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.1125</v>
+        <v>0.1235521235521236</v>
       </c>
       <c r="HC16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.325</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3717948717948718</v>
+        <v>0.3647058823529412</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.6605316973415133</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3646616541353384</v>
+        <v>0.3682432432432433</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.5396019596864502</v>
+        <v>0.5386339835728953</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5284902985074627</v>
+        <v>0.5339355072463767</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.5318521008403361</v>
+        <v>0.5342046875000001</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.09138110072689512</v>
+        <v>0.09211775878442545</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1450511945392491</v>
+        <v>0.1446540880503145</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.007957559681697613</v>
+        <v>0.01199040767386091</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.1300745650372825</v>
+        <v>0.1345864661654135</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.2792046396023198</v>
+        <v>0.2827067669172932</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.436153846153847</v>
+        <v>7.49715808170515</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.31179624664879</v>
+        <v>25.33868613138686</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.2756476683937824</v>
+        <v>0.2733270499528747</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
       <c r="HU16" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.008403361344537815</v>
       </c>
     </row>
     <row r="17">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -2999,199 +2999,199 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>46980</v>
+        <v>49860</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>-5</v>
+        <v>-18</v>
       </c>
       <c r="J4" t="n">
-        <v>1534</v>
+        <v>1631</v>
       </c>
       <c r="K4" t="n">
-        <v>1547</v>
+        <v>1644</v>
       </c>
       <c r="L4" t="n">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="M4" t="n">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="N4" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="O4" t="n">
-        <v>3081</v>
+        <v>3275</v>
       </c>
       <c r="P4" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="Q4" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="R4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="T4" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="U4" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="V4" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="W4" t="n">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA4" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AD4" t="n">
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF4" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="AG4" t="n">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AJ4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AL4" t="n">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="AM4" t="n">
-        <v>711</v>
+        <v>754</v>
       </c>
       <c r="AN4" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AO4" t="n">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="AP4" t="n">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1742</v>
+        <v>1850</v>
       </c>
       <c r="AR4" t="n">
-        <v>1747</v>
+        <v>1868</v>
       </c>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AT4" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AW4" t="n">
         <v>57</v>
       </c>
       <c r="AX4" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="AY4" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="AZ4" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="BA4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="BB4" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="BC4" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BD4" t="n">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="BE4" t="n">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="BF4" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="BG4" t="n">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="BH4" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="BI4" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="BJ4" t="n">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="BK4" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BL4" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="BM4" t="n">
         <v>8</v>
       </c>
       <c r="BN4" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="BO4" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="BP4" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="BQ4" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="BR4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="BS4" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="BT4" t="n">
         <v>72</v>
@@ -3200,64 +3200,64 @@
         <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>845</v>
+        <v>899</v>
       </c>
       <c r="BW4" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="BX4" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="BY4" t="n">
         <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="CA4" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="CB4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CC4" t="n">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="CD4" t="n">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="CE4" t="n">
-        <v>769</v>
+        <v>807</v>
       </c>
       <c r="CF4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CG4" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="CH4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="CI4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CJ4" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="CK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>97</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="CN4" t="n">
         <v>23</v>
       </c>
-      <c r="CL4" t="n">
-        <v>87</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>113</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>20</v>
-      </c>
       <c r="CO4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CP4" t="n">
         <v>9</v>
@@ -3266,46 +3266,46 @@
         <v>9</v>
       </c>
       <c r="CR4" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="CS4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CT4" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="CU4" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="CV4" t="n">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="CW4" t="n">
         <v>3</v>
       </c>
       <c r="CX4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CY4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CZ4" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="DA4" t="n">
         <v>4</v>
       </c>
       <c r="DB4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DC4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="DD4" t="n">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="DE4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DF4" t="n">
         <v>6</v>
@@ -3314,7 +3314,7 @@
         <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="DI4" t="n">
         <v>16</v>
@@ -3323,7 +3323,7 @@
         <v>58</v>
       </c>
       <c r="DK4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="DL4" t="n">
         <v>4</v>
@@ -3332,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="DN4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
@@ -3341,325 +3341,325 @@
         <v>31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="DR4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="DS4" t="inlineStr"/>
       <c r="DT4" t="n">
         <v>2</v>
       </c>
       <c r="DU4" t="n">
-        <v>1504</v>
+        <v>1598</v>
       </c>
       <c r="DV4" t="n">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="DW4" t="n">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="DX4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="DY4" t="n">
         <v>55</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.492462311557789</v>
+        <v>0.485981308411215</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.5429362880886427</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.7475247524752475</v>
+        <v>0.7523364485981309</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.3300653594771242</v>
+        <v>0.327718223583461</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2537313432835821</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.3087557603686636</v>
+        <v>0.3017241379310345</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.3300653594771242</v>
+        <v>0.327718223583461</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.559774964838256</v>
+        <v>0.5676392572944297</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.6</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5497835497835498</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.5298563869992441</v>
+        <v>0.5323383084577115</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.5112994350282486</v>
+        <v>0.5241935483870968</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.5011415525114156</v>
+        <v>0.5010799136069114</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.5678851174934726</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5575221238938053</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.5560747663551402</v>
+        <v>0.5541740674955595</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4625850340136055</v>
+        <v>0.4641080312722104</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0130718954248366</v>
+        <v>0.01225114854517611</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.1054852320675106</v>
+        <v>0.1047745358090186</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.09393939393939393</v>
+        <v>0.09577464788732394</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1208459214501511</v>
+        <v>0.1181556195965418</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.08</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.01089324618736384</v>
+        <v>0.0101419878296146</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.5670498084291188</v>
+        <v>0.5698924731182796</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.6367924528301887</v>
+        <v>0.6349206349206349</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.4174757281553398</v>
+        <v>0.4174454828660436</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.7</v>
+        <v>0.7097791798107256</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2904040404040404</v>
+        <v>0.2860520094562648</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.6629834254143646</v>
+        <v>0.6662269129287599</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.3460992907801418</v>
+        <v>0.3427419354838709</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.4770114942528735</v>
+        <v>0.4640883977900552</v>
       </c>
       <c r="FH4" t="n">
         <v>0.2</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.29</v>
+        <v>0.2888198757763975</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2772277227722773</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.5786163522012578</v>
+        <v>0.5828220858895705</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.6490384615384616</v>
+        <v>0.6497695852534562</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.7543859649122807</v>
+        <v>0.7213114754098361</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.7232142857142857</v>
+        <v>0.7310924369747899</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6455696202531646</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.04807692307692308</v>
+        <v>0.04704097116843703</v>
       </c>
       <c r="FQ4" t="n">
-        <v>94.43678160919541</v>
+        <v>94.58483754512635</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.5232558139534884</v>
+        <v>0.5287356321839081</v>
       </c>
       <c r="FS4" t="n">
-        <v>15.38057366362451</v>
+        <v>15.31802575107296</v>
       </c>
       <c r="FT4" t="n">
-        <v>15.11712992889463</v>
+        <v>15.13156934306569</v>
       </c>
       <c r="FU4" t="n">
-        <v>14.58468057366362</v>
+        <v>14.53182096873084</v>
       </c>
       <c r="FV4" t="n">
-        <v>14.37472527472528</v>
+        <v>14.41222627737226</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2494331065759637</v>
+        <v>0.2523098791755508</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.6787878787878788</v>
+        <v>0.6873239436619718</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.7491638795986622</v>
+        <v>0.7601246105919003</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.5223214285714286</v>
+        <v>0.5286885245901639</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.2501889644746788</v>
+        <v>0.2466240227434257</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.4652567975830816</v>
+        <v>0.4668587896253602</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.5292096219931272</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.03779289493575208</v>
+        <v>0.03695806680881308</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.4</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.35</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.1156462585034014</v>
+        <v>0.1137171286425018</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.3725490196078431</v>
+        <v>0.36875</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.38</v>
+        <v>0.3757961783439491</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8983050847457628</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3503909026297086</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3159041394335512</v>
+        <v>0.3144016227180527</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3193832599118943</v>
+        <v>0.3176229508196721</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6967741935483871</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.4011299435028249</v>
+        <v>0.4086021505376344</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.6338028169014085</v>
+        <v>0.6447368421052632</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.0847457627118644</v>
+        <v>0.09139784946236559</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.2937853107344633</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2407407407407407</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.2305936073059361</v>
+        <v>0.2332613390928726</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.6732673267326733</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.1187214611872146</v>
+        <v>0.1166306695464363</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3767123287671233</v>
+        <v>0.3844492440604751</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.7120181405895691</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3159041394335512</v>
+        <v>0.3144016227180527</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.5464061403508772</v>
+        <v>0.5485321505376344</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.5462261061946903</v>
+        <v>0.5484042372881356</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.5369891608391608</v>
+        <v>0.5393629955947137</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.1227951153324288</v>
+        <v>0.1219667943805875</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.1936619718309859</v>
+        <v>0.1937984496124031</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.02572347266881029</v>
+        <v>0.02413273001508296</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.1366245694603904</v>
+        <v>0.1362162162162162</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3421354764638347</v>
+        <v>0.3378378378378378</v>
       </c>
       <c r="HP4" t="n">
-        <v>5.581012658227848</v>
+        <v>5.55079575596817</v>
       </c>
       <c r="HQ4" t="n">
-        <v>25.59140495867769</v>
+        <v>25.57693498452013</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.333116036505867</v>
+        <v>0.3323114653586757</v>
       </c>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
       <c r="HU4" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.01875</v>
       </c>
     </row>
     <row r="5">
@@ -4377,310 +4377,310 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>34860</v>
+        <v>37740</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J6" t="n">
-        <v>1147</v>
+        <v>1243</v>
       </c>
       <c r="K6" t="n">
-        <v>1158</v>
+        <v>1256</v>
       </c>
       <c r="L6" t="n">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="M6" t="n">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="N6" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="O6" t="n">
-        <v>2305</v>
+        <v>2499</v>
       </c>
       <c r="P6" t="n">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="Q6" t="n">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="R6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="U6" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="V6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="W6" t="n">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y6" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Z6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AB6" t="n">
         <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AK6" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AL6" t="n">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="AM6" t="n">
-        <v>621</v>
+        <v>670</v>
       </c>
       <c r="AN6" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AO6" t="n">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="AP6" t="n">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1428</v>
+        <v>1549</v>
       </c>
       <c r="AR6" t="n">
-        <v>1207</v>
+        <v>1315</v>
       </c>
       <c r="AS6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AT6" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="AY6" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AZ6" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="BA6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="BB6" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="BC6" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="BD6" t="n">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="BE6" t="n">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="BF6" t="n">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="BG6" t="n">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="BH6" t="n">
         <v>81</v>
       </c>
       <c r="BI6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BJ6" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="BK6" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="BL6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BM6" t="n">
         <v>4</v>
       </c>
       <c r="BN6" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="BO6" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="BP6" t="n">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="BQ6" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="BR6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="BS6" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="BT6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BU6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BV6" t="n">
-        <v>755</v>
+        <v>820</v>
       </c>
       <c r="BW6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BX6" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="BY6" t="n">
         <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="CA6" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="CB6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="CC6" t="n">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="CD6" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="CE6" t="n">
-        <v>613</v>
+        <v>653</v>
       </c>
       <c r="CF6" t="n">
+        <v>24</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>111</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>68</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>43</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>92</v>
+      </c>
+      <c r="CK6" t="n">
         <v>21</v>
       </c>
-      <c r="CG6" t="n">
-        <v>100</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>58</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>42</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>85</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>17</v>
-      </c>
       <c r="CL6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="CM6" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="CN6" t="n">
         <v>8</v>
       </c>
       <c r="CO6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CP6" t="n">
         <v>6</v>
       </c>
       <c r="CQ6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="CS6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CT6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="CU6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="CV6" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CY6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CZ6" t="n">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="DA6" t="n">
         <v>3</v>
       </c>
       <c r="DB6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DC6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="DD6" t="n">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="DE6" t="n">
         <v>21</v>
@@ -4690,16 +4690,16 @@
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="DI6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DJ6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="DK6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,336 +4708,336 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DQ6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="DR6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="DS6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1222</v>
+        <v>1333</v>
       </c>
       <c r="DV6" t="n">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="DW6" t="n">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="DX6" t="n">
         <v>33</v>
       </c>
       <c r="DY6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5123287671232877</v>
+        <v>0.5113350125944585</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5565476190476191</v>
+        <v>0.553133514986376</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8246753246753247</v>
+        <v>0.8363636363636363</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3908629441624366</v>
+        <v>0.3909952606635071</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4375</v>
+        <v>0.4369747899159664</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3908629441624366</v>
+        <v>0.3909952606635071</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5877616747181964</v>
+        <v>0.5925373134328358</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5562130177514792</v>
+        <v>0.5580110497237569</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.587192118226601</v>
+        <v>0.5902014652014652</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.7052238805970149</v>
+        <v>0.7</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5960854092526691</v>
+        <v>0.5966666666666667</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6138912855910268</v>
+        <v>0.6180944755804644</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.6959459459459459</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6322314049586777</v>
+        <v>0.6343669250645995</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3881773399014778</v>
+        <v>0.3864468864468865</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01015228426395939</v>
+        <v>0.009478672985781991</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07890499194847021</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.09166666666666666</v>
+        <v>0.08900523560209424</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.07352941176470588</v>
+        <v>0.06726457399103139</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01754385964912281</v>
+        <v>0.01538461538461539</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.01056338028169014</v>
+        <v>0.009836065573770493</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.53125</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.925</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.6961538461538461</v>
+        <v>0.6911764705882353</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.3824701195219123</v>
+        <v>0.3843283582089552</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.75</v>
+        <v>0.7522935779816514</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.282051282051282</v>
+        <v>0.2709163346613546</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.725</v>
+        <v>0.7245409015025042</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.334020618556701</v>
+        <v>0.3294797687861272</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.4297520661157025</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.35</v>
+        <v>0.3486238532110092</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2529411764705882</v>
+        <v>0.2445652173913044</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.359375</v>
+        <v>0.3432835820895522</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.6444444444444445</v>
+        <v>0.6210526315789474</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7384615384615385</v>
       </c>
       <c r="FM6" t="n">
         <v>0.7021276595744681</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7678571428571429</v>
+        <v>0.7642276422764228</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.6973684210526315</v>
+        <v>0.7160493827160493</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.04861111111111111</v>
+        <v>0.05161290322580645</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.21514629948365</v>
+        <v>95.35135135135135</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.92877070619006</v>
+        <v>15.89734513274336</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.32616580310881</v>
+        <v>14.31496815286624</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.22781168265039</v>
+        <v>15.22308930008045</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.76753022452504</v>
+        <v>13.75103503184713</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.354679802955665</v>
+        <v>0.3498168498168498</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.675</v>
+        <v>0.6832460732984293</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.7431192660550459</v>
+        <v>0.75</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5670498084291188</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2009852216748768</v>
+        <v>0.2042124542124542</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.4932735426008968</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.5291005291005291</v>
+        <v>0.5288461538461539</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.44</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0561576354679803</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3859649122807017</v>
+        <v>0.4</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.40625</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1083743842364532</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4188034188034188</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4128440366972477</v>
+        <v>0.4224137931034483</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9591836734693877</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2798029556650246</v>
+        <v>0.2793040293040293</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3838028169014084</v>
+        <v>0.380327868852459</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3879003558718861</v>
+        <v>0.3841059602649007</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7706422018348624</v>
+        <v>0.7844827586206896</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4552238805970149</v>
+        <v>0.45</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6721311475409836</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.09285714285714286</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="GV6" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2238805970149254</v>
+        <v>0.2214285714285714</v>
       </c>
       <c r="GX6" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="GY6" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="GZ6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="HA6" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="HB6" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="HC6" t="n">
         <v>0.6</v>
       </c>
-      <c r="GY6" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="GZ6" t="n">
-        <v>0.3451957295373665</v>
-      </c>
-      <c r="HA6" t="n">
-        <v>0.6391752577319587</v>
-      </c>
-      <c r="HB6" t="n">
-        <v>0.07473309608540925</v>
-      </c>
-      <c r="HC6" t="n">
-        <v>0.6190476190476191</v>
-      </c>
       <c r="HD6" t="n">
-        <v>0.3238434163701068</v>
+        <v>0.3133333333333334</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3956043956043956</v>
+        <v>0.3936170212765958</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7362637362637363</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3838028169014084</v>
+        <v>0.380327868852459</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5682110505450941</v>
+        <v>0.5669127532228361</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5473632978723405</v>
+        <v>0.5484762626262626</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5502225454545455</v>
+        <v>0.5483280612244897</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.09963768115942029</v>
+        <v>0.101510067114094</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1501416430594901</v>
+        <v>0.1516339869281046</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.01005025125628141</v>
+        <v>0.0117096018735363</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1442577030812325</v>
+        <v>0.1394448030987734</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3228291316526611</v>
+        <v>0.3182698515171078</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.257004830917874</v>
+        <v>5.390298507462687</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.21516709511568</v>
+        <v>25.29136690647482</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.3042720139494333</v>
+        <v>0.3016894609814964</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.008547008547008548</v>
       </c>
     </row>
     <row r="7">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,67 +7135,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>40920</v>
+        <v>43800</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="J10" t="n">
-        <v>1392</v>
+        <v>1492</v>
       </c>
       <c r="K10" t="n">
-        <v>1404</v>
+        <v>1504</v>
       </c>
       <c r="L10" t="n">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="M10" t="n">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="N10" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="O10" t="n">
-        <v>2796</v>
+        <v>2996</v>
       </c>
       <c r="P10" t="n">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="Q10" t="n">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S10" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="T10" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="U10" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="V10" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="W10" t="n">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="Z10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA10" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -7204,196 +7204,196 @@
         <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="n">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AK10" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AL10" t="n">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="AM10" t="n">
-        <v>723</v>
+        <v>780</v>
       </c>
       <c r="AN10" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AO10" t="n">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="AP10" t="n">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1629</v>
+        <v>1732</v>
       </c>
       <c r="AR10" t="n">
-        <v>1487</v>
+        <v>1569</v>
       </c>
       <c r="AS10" t="n">
+        <v>63</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>118</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>232</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>133</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>276</v>
+      </c>
+      <c r="BA10" t="n">
         <v>60</v>
       </c>
-      <c r="AT10" t="n">
-        <v>111</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>35</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>215</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>122</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>244</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>55</v>
-      </c>
       <c r="BB10" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="BC10" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="BD10" t="n">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="BE10" t="n">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="BF10" t="n">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="BG10" t="n">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="BH10" t="n">
         <v>51</v>
       </c>
       <c r="BI10" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="BJ10" t="n">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="BK10" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="BL10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="BM10" t="n">
         <v>4</v>
       </c>
       <c r="BN10" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="BO10" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="BP10" t="n">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="BQ10" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="BR10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="BS10" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="BT10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BU10" t="n">
         <v>10</v>
       </c>
       <c r="BV10" t="n">
-        <v>864</v>
+        <v>923</v>
       </c>
       <c r="BW10" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="BX10" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="CA10" t="n">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="CB10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CC10" t="n">
-        <v>551</v>
+        <v>593</v>
       </c>
       <c r="CD10" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="CE10" t="n">
-        <v>743</v>
+        <v>803</v>
       </c>
       <c r="CF10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="CG10" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="CH10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="CI10" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="CJ10" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="CK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CL10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CM10" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="CN10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CO10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
@@ -7402,44 +7402,44 @@
         <v>7</v>
       </c>
       <c r="CR10" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="CS10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CT10" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="CU10" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="CV10" t="n">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="CW10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CX10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="CY10" t="n">
         <v>30</v>
       </c>
       <c r="CZ10" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="DC10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DD10" t="n">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="DE10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -7448,16 +7448,16 @@
         <v>5</v>
       </c>
       <c r="DH10" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="DI10" t="n">
         <v>5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="DK10" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="DL10" t="n">
         <v>10</v>
@@ -7466,19 +7466,19 @@
         <v>6</v>
       </c>
       <c r="DN10" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="DO10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="DQ10" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="DR10" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="DS10" t="n">
         <v>5</v>
@@ -7487,238 +7487,238 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="DV10" t="n">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="DW10" t="n">
-        <v>478</v>
+        <v>532</v>
       </c>
       <c r="DX10" t="n">
+        <v>38</v>
+      </c>
+      <c r="DY10" t="n">
         <v>36</v>
       </c>
-      <c r="DY10" t="n">
-        <v>30</v>
-      </c>
       <c r="DZ10" t="n">
-        <v>0.4725</v>
+        <v>0.4812206572769953</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5279329608938548</v>
+        <v>0.5380577427821522</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9050279329608939</v>
+        <v>0.9095744680851063</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3706004140786749</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.375</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3706004140786749</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5532503457814661</v>
+        <v>0.5461538461538461</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.5338983050847458</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5</v>
+        <v>0.4818840579710145</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5543117744610282</v>
+        <v>0.5458750963762529</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5325520833333334</v>
+        <v>0.5114678899082569</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5948023426061494</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6323529411764706</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5890557939914163</v>
+        <v>0.5676190476190476</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.400497512437811</v>
+        <v>0.3986121819583655</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.008281573498964804</v>
+        <v>0.007736943907156673</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07468879668049792</v>
+        <v>0.07564102564102564</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09296482412060302</v>
+        <v>0.09259259259259259</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06302521008403361</v>
+        <v>0.06692913385826772</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.02298850574712644</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002958579881656805</v>
+        <v>0.002770083102493075</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5045454545454545</v>
+        <v>0.5150214592274678</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.08108108108108109</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6690997566909975</v>
+        <v>0.6644144144144144</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.3323863636363636</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7386018237082067</v>
+        <v>0.7415730337078652</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2809364548494983</v>
+        <v>0.2786377708978328</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.7</v>
+        <v>0.69875</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3048387096774193</v>
+        <v>0.3066666666666666</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.3875968992248062</v>
+        <v>0.4027777777777778</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3129770992366412</v>
+        <v>0.3049645390070922</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.2388059701492537</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2906403940886699</v>
+        <v>0.2889908256880734</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6037735849056604</v>
+        <v>0.6104651162790697</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6772486772486772</v>
+        <v>0.6733668341708543</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7173913043478261</v>
+        <v>0.716</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.8018867924528302</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0497335701598579</v>
+        <v>0.05057096247960848</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.39296187683284</v>
+        <v>98.49863013698631</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5871559633027523</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.4989224137931</v>
+        <v>14.40462466487936</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.77029914529914</v>
+        <v>14.83264627659574</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.9239224137931</v>
+        <v>13.82258713136729</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.03333333333333</v>
+        <v>14.07619680851064</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.330016583747927</v>
+        <v>0.3330763299922899</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6733668341708543</v>
+        <v>0.6643518518518519</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7423822714681441</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.4888059701492538</v>
+        <v>0.5017421602787456</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1973466003316749</v>
+        <v>0.1958365458750964</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4453781512605042</v>
+        <v>0.4409448818897638</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4753363228699551</v>
+        <v>0.4725738396624473</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.4553571428571428</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07213930348258707</v>
+        <v>0.07247494217424827</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.2988505747126437</v>
+        <v>0.2872340425531915</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.2934782608695652</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1202321724709784</v>
+        <v>0.1202775636083269</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3379310344827586</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3450704225352113</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2802653399668325</v>
+        <v>0.2783346183500385</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3795013850415512</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3857566765578635</v>
+        <v>0.3805555555555555</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8692307692307693</v>
+        <v>0.8759124087591241</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5032679738562091</v>
+        <v>0.5060975609756098</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5974025974025974</v>
+        <v>0.5903614457831325</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1224489795918367</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.0718954248366013</v>
+        <v>0.06707317073170732</v>
       </c>
       <c r="GU10" t="n">
         <v>0.4545454545454545</v>
@@ -7727,70 +7727,70 @@
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2026143790849673</v>
+        <v>0.2134146341463415</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3385416666666667</v>
+        <v>0.3394495412844037</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5923076923076923</v>
+        <v>0.5743243243243243</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.0963302752293578</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2760416666666667</v>
+        <v>0.2706422018348624</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3867924528301887</v>
+        <v>0.3728813559322034</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7305140961857379</v>
+        <v>0.7316885119506553</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3795013850415512</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5649832917705736</v>
+        <v>0.5663923374613004</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5431546391752577</v>
+        <v>0.543864761904762</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5528777486910995</v>
+        <v>0.5556268518518519</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.118796992481203</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1834319526627219</v>
+        <v>0.1822173435784852</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.006185567010309278</v>
+        <v>0.005780346820809248</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1319828115408226</v>
+        <v>0.1339491916859122</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3376304481276857</v>
+        <v>0.3446882217090069</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.704840940525588</v>
+        <v>5.688589743589744</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.28752598752599</v>
+        <v>25.28774319066148</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3441091954022988</v>
+        <v>0.3572386058981233</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.02068965517241379</v>
+        <v>0.01923076923076923</v>
       </c>
     </row>
     <row r="11">
@@ -11271,67 +11271,67 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>32280</v>
+        <v>35160</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="J16" t="n">
-        <v>1061</v>
+        <v>1160</v>
       </c>
       <c r="K16" t="n">
-        <v>1072</v>
+        <v>1173</v>
       </c>
       <c r="L16" t="n">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="M16" t="n">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="N16" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="O16" t="n">
-        <v>2133</v>
+        <v>2333</v>
       </c>
       <c r="P16" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="Q16" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="S16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="T16" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="V16" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="W16" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Y16" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AA16" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
@@ -11340,196 +11340,196 @@
         <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF16" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AG16" t="n">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AL16" t="n">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="AM16" t="n">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="AN16" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AO16" t="n">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="AP16" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1330</v>
+        <v>1412</v>
       </c>
       <c r="AR16" t="n">
-        <v>1180</v>
+        <v>1283</v>
       </c>
       <c r="AS16" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AT16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX16" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="AY16" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AZ16" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="BA16" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="BB16" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="BC16" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BD16" t="n">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="BE16" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="BF16" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="BG16" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="BH16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BI16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BJ16" t="n">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="BK16" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BL16" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BM16" t="n">
         <v>6</v>
       </c>
       <c r="BN16" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="BO16" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="BP16" t="n">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="BQ16" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BR16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="BS16" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="BT16" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="BU16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BV16" t="n">
-        <v>732</v>
+        <v>781</v>
       </c>
       <c r="BW16" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="BX16" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="CA16" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="CB16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CC16" t="n">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="CD16" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="CE16" t="n">
-        <v>513</v>
+        <v>572</v>
       </c>
       <c r="CF16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CG16" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="CH16" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="CI16" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="CJ16" t="n">
+        <v>81</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>10</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>39</v>
+      </c>
+      <c r="CM16" t="n">
         <v>70</v>
       </c>
-      <c r="CK16" t="n">
-        <v>9</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>37</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>61</v>
-      </c>
       <c r="CN16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CO16" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="CP16" t="n">
         <v>3</v>
@@ -11538,46 +11538,46 @@
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="CS16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CT16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CU16" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="CV16" t="n">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CY16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CZ16" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="DA16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DB16" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="DC16" t="n">
         <v>21</v>
       </c>
       <c r="DD16" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="DE16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -11586,16 +11586,16 @@
         <v>4</v>
       </c>
       <c r="DH16" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="DI16" t="n">
         <v>5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="DK16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="DL16" t="n">
         <v>1</v>
@@ -11604,19 +11604,19 @@
         <v>1</v>
       </c>
       <c r="DN16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="DO16" t="n">
         <v>3</v>
       </c>
       <c r="DP16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="DQ16" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="DR16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="DS16" t="n">
         <v>1</v>
@@ -11625,238 +11625,238 @@
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>1151</v>
+        <v>1219</v>
       </c>
       <c r="DV16" t="n">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="DW16" t="n">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="DX16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="DY16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4751552795031056</v>
+        <v>0.4913294797687861</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.5083056478405316</v>
+        <v>0.5279503105590062</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.8930817610062893</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.3831325301204819</v>
+        <v>0.3683035714285715</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.4339622641509434</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.3675213675213675</v>
+        <v>0.359375</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.3831325301204819</v>
+        <v>0.3683035714285715</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.5719360568383659</v>
+        <v>0.5571658615136876</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.5846153846153846</v>
+        <v>0.581081081081081</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.5563380281690141</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.5731083844580777</v>
+        <v>0.5551917680074836</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.6359649122807017</v>
+        <v>0.610236220472441</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.5540540540540541</v>
+        <v>0.5441696113074205</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.609935602575897</v>
+        <v>0.5935919055649241</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.667910447761194</v>
+        <v>0.6476510067114094</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.5985074626865672</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4243353783231084</v>
+        <v>0.4190832553788588</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01445783132530121</v>
+        <v>0.01339285714285714</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.06039076376554174</v>
+        <v>0.07085346215780998</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.06926406926406926</v>
+        <v>0.08880308880308881</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.05652173913043478</v>
+        <v>0.06147540983606557</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.04901960784313725</v>
+        <v>0.05084745762711865</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01689189189189189</v>
+        <v>0.01567398119122257</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.5343511450381679</v>
+        <v>0.5364238410596026</v>
       </c>
       <c r="EX16" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0.6512455516014235</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0.3148148148148148</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.7032967032967034</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0.3118279569892473</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0.6768953068592057</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0.3132969034608379</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.2112676056338028</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0.3676470588235294</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0.7155963302752294</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0.689119170984456</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0.03393213572854292</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>95.54948805460751</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>14.98060344827586</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>15.15984654731458</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>14.32405172413793</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>14.52267689684569</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0.2422825070159027</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0.7711864406779662</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0.5604395604395604</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0.2282507015902713</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0.4836065573770492</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0.5152838427947598</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0.4830508474576271</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0.1103835360149673</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0.3898305084745763</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0.4107142857142857</v>
+      </c>
+      <c r="GH16" t="n">
+        <v>0.2391304347826087</v>
+      </c>
+      <c r="GI16" t="n">
+        <v>0.1206735266604303</v>
+      </c>
+      <c r="GJ16" t="n">
+        <v>0.4108527131782946</v>
+      </c>
+      <c r="GK16" t="n">
+        <v>0.4140625</v>
+      </c>
+      <c r="GL16" t="n">
+        <v>0.9622641509433962</v>
+      </c>
+      <c r="GM16" t="n">
+        <v>0.2984097287184284</v>
+      </c>
+      <c r="GN16" t="n">
+        <v>0.3510971786833856</v>
+      </c>
+      <c r="GO16" t="n">
+        <v>0.356687898089172</v>
+      </c>
+      <c r="GP16" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="EY16" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-      <c r="EZ16" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="FA16" t="n">
-        <v>0.3037974683544304</v>
-      </c>
-      <c r="FB16" t="n">
-        <v>0.6987951807228916</v>
-      </c>
-      <c r="FC16" t="n">
-        <v>0.3214285714285715</v>
-      </c>
-      <c r="FD16" t="n">
-        <v>0.6773547094188377</v>
-      </c>
-      <c r="FE16" t="n">
-        <v>0.3128834355828221</v>
-      </c>
-      <c r="FF16" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-      <c r="FG16" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="FH16" t="n">
-        <v>0.1639344262295082</v>
-      </c>
-      <c r="FI16" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="FJ16" t="n">
-        <v>0.1764705882352941</v>
-      </c>
-      <c r="FK16" t="n">
-        <v>0.5463917525773195</v>
-      </c>
-      <c r="FL16" t="n">
-        <v>0.7070707070707071</v>
-      </c>
-      <c r="FM16" t="n">
-        <v>0.7592592592592593</v>
-      </c>
-      <c r="FN16" t="n">
-        <v>0.6853932584269663</v>
-      </c>
-      <c r="FO16" t="n">
-        <v>0.7323943661971831</v>
-      </c>
-      <c r="FP16" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="FQ16" t="n">
-        <v>95.15241635687732</v>
-      </c>
-      <c r="FR16" t="n">
-        <v>0.5490196078431373</v>
-      </c>
-      <c r="FS16" t="n">
-        <v>14.89792648444863</v>
-      </c>
-      <c r="FT16" t="n">
-        <v>15.36688432835821</v>
-      </c>
-      <c r="FU16" t="n">
-        <v>14.27719132893497</v>
-      </c>
-      <c r="FV16" t="n">
-        <v>14.73311567164179</v>
-      </c>
-      <c r="FW16" t="n">
-        <v>0.2361963190184049</v>
-      </c>
-      <c r="FX16" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="FY16" t="n">
-        <v>0.7813953488372093</v>
-      </c>
-      <c r="FZ16" t="n">
-        <v>0.5535714285714286</v>
-      </c>
-      <c r="GA16" t="n">
-        <v>0.2351738241308793</v>
-      </c>
-      <c r="GB16" t="n">
-        <v>0.4956521739130435</v>
-      </c>
-      <c r="GC16" t="n">
-        <v>0.5253456221198156</v>
-      </c>
-      <c r="GD16" t="n">
-        <v>0.4649122807017544</v>
-      </c>
-      <c r="GE16" t="n">
-        <v>0.1042944785276074</v>
-      </c>
-      <c r="GF16" t="n">
-        <v>0.392156862745098</v>
-      </c>
-      <c r="GG16" t="n">
-        <v>0.4123711340206185</v>
-      </c>
-      <c r="GH16" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="GI16" t="n">
-        <v>0.1216768916155419</v>
-      </c>
-      <c r="GJ16" t="n">
-        <v>0.4201680672268908</v>
-      </c>
-      <c r="GK16" t="n">
-        <v>0.423728813559322</v>
-      </c>
-      <c r="GL16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="GM16" t="n">
-        <v>0.3026584867075665</v>
-      </c>
-      <c r="GN16" t="n">
-        <v>0.3682432432432433</v>
-      </c>
-      <c r="GO16" t="n">
-        <v>0.3745704467353952</v>
-      </c>
-      <c r="GP16" t="n">
-        <v>0.8532110091743119</v>
-      </c>
       <c r="GQ16" t="n">
-        <v>0.3508771929824561</v>
+        <v>0.3779527559055118</v>
       </c>
       <c r="GR16" t="n">
-        <v>0.65</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="GS16" t="n">
-        <v>0.1923076923076923</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.07086614173228346</v>
       </c>
       <c r="GU16" t="n">
         <v>0.4444444444444444</v>
@@ -11865,75 +11865,75 @@
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.3508771929824561</v>
+        <v>0.3464566929133858</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.475</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="GY16" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.2548262548262548</v>
+        <v>0.2614840989399294</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.1235521235521236</v>
+        <v>0.127208480565371</v>
       </c>
       <c r="HC16" t="n">
-        <v>0.375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.3281853281853282</v>
+        <v>0.3250883392226148</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3647058823529412</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6605316973415133</v>
+        <v>0.6613657623947614</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3682432432432433</v>
+        <v>0.3510971786833856</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.5386339835728953</v>
+        <v>0.539843661971831</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5339355072463767</v>
+        <v>0.5469208860759494</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.5342046875000001</v>
+        <v>0.5374741071428571</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.09211775878442545</v>
+        <v>0.09043478260869565</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1446540880503145</v>
+        <v>0.1414285714285714</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.01199040767386091</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.1345864661654135</v>
+        <v>0.136685552407932</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.2827067669172932</v>
+        <v>0.2854107648725213</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.49715808170515</v>
+        <v>7.498872785829308</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.33868613138686</v>
+        <v>25.3027027027027</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.2733270499528747</v>
+        <v>0.2724137931034483</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
       <c r="HU16" t="n">
-        <v>0.008403361344537815</v>
+        <v>0.007751937984496124</v>
       </c>
     </row>
     <row r="17">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -2999,67 +2999,67 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>49860</v>
+        <v>52740</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
-        <v>-18</v>
+        <v>-55</v>
       </c>
       <c r="J4" t="n">
-        <v>1631</v>
+        <v>1732</v>
       </c>
       <c r="K4" t="n">
-        <v>1644</v>
+        <v>1745</v>
       </c>
       <c r="L4" t="n">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="M4" t="n">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="N4" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="O4" t="n">
-        <v>3275</v>
+        <v>3477</v>
       </c>
       <c r="P4" t="n">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="Q4" t="n">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="R4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="T4" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="U4" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="V4" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="W4" t="n">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Z4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AB4" t="n">
         <v>6</v>
@@ -3068,196 +3068,196 @@
         <v>17</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="AG4" t="n">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AK4" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="AL4" t="n">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="AM4" t="n">
-        <v>754</v>
+        <v>791</v>
       </c>
       <c r="AN4" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="AO4" t="n">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="AP4" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1850</v>
+        <v>1943</v>
       </c>
       <c r="AR4" t="n">
-        <v>1868</v>
+        <v>1998</v>
       </c>
       <c r="AS4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AT4" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AW4" t="n">
         <v>57</v>
       </c>
       <c r="AX4" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AY4" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="AZ4" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="BA4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB4" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="BC4" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="BD4" t="n">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="BE4" t="n">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="BF4" t="n">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="BG4" t="n">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="BH4" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="BI4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="BJ4" t="n">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="BK4" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="BL4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BM4" t="n">
         <v>8</v>
       </c>
       <c r="BN4" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="BO4" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="BP4" t="n">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="BQ4" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="BR4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BS4" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="BT4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BU4" t="n">
         <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>899</v>
+        <v>949</v>
       </c>
       <c r="BW4" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="BX4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BY4" t="n">
         <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="CA4" t="n">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="CB4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CC4" t="n">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="CD4" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="CE4" t="n">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="CF4" t="n">
         <v>31</v>
       </c>
       <c r="CG4" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="CH4" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="CI4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CJ4" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="CK4" t="n">
+        <v>28</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>106</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>127</v>
+      </c>
+      <c r="CN4" t="n">
         <v>24</v>
       </c>
-      <c r="CL4" t="n">
-        <v>97</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>23</v>
-      </c>
       <c r="CO4" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="CP4" t="n">
         <v>9</v>
@@ -3266,31 +3266,31 @@
         <v>9</v>
       </c>
       <c r="CR4" t="n">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="CS4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CT4" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="CU4" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="CV4" t="n">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="CW4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CX4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CY4" t="n">
         <v>23</v>
       </c>
       <c r="CZ4" t="n">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="DA4" t="n">
         <v>4</v>
@@ -3302,10 +3302,10 @@
         <v>30</v>
       </c>
       <c r="DD4" t="n">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="DE4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DF4" t="n">
         <v>6</v>
@@ -3314,16 +3314,16 @@
         <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="DI4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="DJ4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="DK4" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="DL4" t="n">
         <v>4</v>
@@ -3332,257 +3332,257 @@
         <v>4</v>
       </c>
       <c r="DN4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="DQ4" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="DR4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="DS4" t="inlineStr"/>
       <c r="DT4" t="n">
         <v>2</v>
       </c>
       <c r="DU4" t="n">
-        <v>1598</v>
+        <v>1686</v>
       </c>
       <c r="DV4" t="n">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="DW4" t="n">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="DX4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="DY4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.485981308411215</v>
+        <v>0.4922048997772829</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.5360824742268041</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.7523364485981309</v>
+        <v>0.7511111111111111</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.327718223583461</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.273972602739726</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.3017241379310345</v>
+        <v>0.3</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.327718223583461</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.5676392572944297</v>
+        <v>0.5676359039190898</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.6</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.5497835497835498</v>
+        <v>0.5542168674698795</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5299865229110512</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.5241935483870968</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.5010799136069114</v>
+        <v>0.5020040080160321</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.5689655172413793</v>
+        <v>0.5675438596491228</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.5575221238938053</v>
+        <v>0.5538793103448276</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.5541740674955595</v>
+        <v>0.5532445923460898</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4641080312722104</v>
+        <v>0.4669811320754717</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01225114854517611</v>
+        <v>0.01154401154401154</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.1047745358090186</v>
+        <v>0.1024020227560051</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.09577464788732394</v>
+        <v>0.09549071618037135</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1181556195965418</v>
+        <v>0.1145251396648045</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0101419878296146</v>
+        <v>0.009487666034155597</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.5698924731182796</v>
+        <v>0.5780730897009967</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.78</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.6349206349206349</v>
+        <v>0.6295503211991434</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.4174454828660436</v>
+        <v>0.400593471810089</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.7097791798107256</v>
+        <v>0.7008797653958945</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2860520094562648</v>
+        <v>0.2815964523281597</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.6662269129287599</v>
+        <v>0.6596534653465347</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.3427419354838709</v>
+        <v>0.33248730964467</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.4</v>
+        <v>0.3813559322033898</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.4640883977900552</v>
+        <v>0.4468085106382979</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.2</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.2888198757763975</v>
+        <v>0.2869565217391304</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2772277227722773</v>
+        <v>0.2641509433962264</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.5828220858895705</v>
+        <v>0.5722543352601156</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.6497695852534562</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.7213114754098361</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.7310924369747899</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.6455696202531646</v>
+        <v>0.6292134831460674</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.04704097116843703</v>
+        <v>0.0442225392296719</v>
       </c>
       <c r="FQ4" t="n">
-        <v>94.58483754512635</v>
+        <v>94.93515358361775</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.5287356321839081</v>
+        <v>0.5274725274725275</v>
       </c>
       <c r="FS4" t="n">
-        <v>15.31802575107296</v>
+        <v>15.23158198614319</v>
       </c>
       <c r="FT4" t="n">
-        <v>15.13156934306569</v>
+        <v>15.10538681948424</v>
       </c>
       <c r="FU4" t="n">
-        <v>14.53182096873084</v>
+        <v>14.47448036951501</v>
       </c>
       <c r="FV4" t="n">
-        <v>14.41222627737226</v>
+        <v>14.38103151862464</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2523098791755508</v>
+        <v>0.2540431266846361</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.6873239436619718</v>
+        <v>0.6843501326259946</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.7601246105919003</v>
+        <v>0.7565982404692082</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.5286885245901639</v>
+        <v>0.5426356589147286</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.2466240227434257</v>
+        <v>0.2412398921832884</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.4668587896253602</v>
+        <v>0.4636871508379888</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5236593059936908</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.03695806680881308</v>
+        <v>0.03773584905660377</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.28</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.1137171286425018</v>
+        <v>0.1118598382749326</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.36875</v>
+        <v>0.3614457831325301</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3757961783439491</v>
+        <v>0.3680981595092024</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.8983050847457628</v>
+        <v>0.9</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3503909026297086</v>
+        <v>0.3551212938005391</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3144016227180527</v>
+        <v>0.3130929791271347</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3176229508196721</v>
+        <v>0.3160919540229885</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.6967741935483871</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.4086021505376344</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.625</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.163265306122449</v>
+        <v>0.16</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.09139784946236559</v>
+        <v>0.08854166666666667</v>
       </c>
       <c r="GU4" t="n">
         <v>0.3529411764705883</v>
@@ -3591,75 +3591,75 @@
         <v>0.5</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.25</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.2332613390928726</v>
+        <v>0.2444889779559118</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.680327868852459</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.1166306695464363</v>
+        <v>0.1102204408817635</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3844492440604751</v>
+        <v>0.3907815631262525</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.7210242587601078</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3144016227180527</v>
+        <v>0.3130929791271347</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.5485321505376344</v>
+        <v>0.5495007472826087</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.5484042372881356</v>
+        <v>0.5486158333333333</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.5393629955947137</v>
+        <v>0.5434223469387756</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.1219667943805875</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.1937984496124031</v>
+        <v>0.1925925925925926</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.02413273001508296</v>
+        <v>0.02553191489361702</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.1362162162162162</v>
+        <v>0.1322696860524961</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3378378378378378</v>
+        <v>0.3427689140504375</v>
       </c>
       <c r="HP4" t="n">
-        <v>5.55079575596817</v>
+        <v>5.540455120101138</v>
       </c>
       <c r="HQ4" t="n">
-        <v>25.57693498452013</v>
+        <v>25.57434402332362</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.3323114653586757</v>
+        <v>0.3366050808314088</v>
       </c>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
       <c r="HU4" t="n">
-        <v>0.01875</v>
+        <v>0.01807228915662651</v>
       </c>
     </row>
     <row r="5">
@@ -4377,265 +4377,265 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>37740</v>
+        <v>40620</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="J6" t="n">
-        <v>1243</v>
+        <v>1343</v>
       </c>
       <c r="K6" t="n">
-        <v>1256</v>
+        <v>1358</v>
       </c>
       <c r="L6" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="M6" t="n">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="N6" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="O6" t="n">
-        <v>2499</v>
+        <v>2701</v>
       </c>
       <c r="P6" t="n">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="Q6" t="n">
-        <v>382</v>
+        <v>413</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="T6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U6" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V6" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W6" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="X6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="Z6" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AA6" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="AB6" t="n">
         <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>332</v>
+      </c>
+      <c r="AH6" t="n">
         <v>25</v>
       </c>
-      <c r="AF6" t="n">
-        <v>116</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>305</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>19</v>
-      </c>
       <c r="AI6" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AK6" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AL6" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="AM6" t="n">
-        <v>670</v>
+        <v>725</v>
       </c>
       <c r="AN6" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="AO6" t="n">
-        <v>422</v>
+        <v>466</v>
       </c>
       <c r="AP6" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1549</v>
+        <v>1679</v>
       </c>
       <c r="AR6" t="n">
-        <v>1315</v>
+        <v>1408</v>
       </c>
       <c r="AS6" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AT6" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AU6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AV6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="AY6" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AZ6" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="BA6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="BB6" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="BC6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="BD6" t="n">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="BE6" t="n">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="BF6" t="n">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="BG6" t="n">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="BH6" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="BI6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BJ6" t="n">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="BK6" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="BL6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="BM6" t="n">
         <v>4</v>
       </c>
       <c r="BN6" t="n">
+        <v>221</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>153</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>374</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>99</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>54</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>162</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>49</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>901</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>78</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>268</v>
+      </c>
+      <c r="CA6" t="n">
         <v>203</v>
       </c>
-      <c r="BO6" t="n">
-        <v>138</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>341</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>91</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>47</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>148</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>820</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>103</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>246</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>188</v>
-      </c>
       <c r="CB6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="CC6" t="n">
-        <v>474</v>
+        <v>514</v>
       </c>
       <c r="CD6" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="CE6" t="n">
-        <v>653</v>
+        <v>716</v>
       </c>
       <c r="CF6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CG6" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="CH6" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="CI6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="CJ6" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="CK6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CL6" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="CM6" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="CN6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CO6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CP6" t="n">
         <v>6</v>
@@ -4644,19 +4644,19 @@
         <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="CS6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CT6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="CU6" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="CV6" t="n">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
@@ -4668,19 +4668,19 @@
         <v>19</v>
       </c>
       <c r="CZ6" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="DA6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DB6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="DC6" t="n">
         <v>17</v>
       </c>
       <c r="DD6" t="n">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="DE6" t="n">
         <v>21</v>
@@ -4690,16 +4690,16 @@
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="DI6" t="n">
         <v>5</v>
       </c>
       <c r="DJ6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="DK6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,7 +4708,7 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
@@ -4717,327 +4717,327 @@
         <v>22</v>
       </c>
       <c r="DQ6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="DR6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="DS6" t="n">
         <v>6</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1333</v>
+        <v>1431</v>
       </c>
       <c r="DV6" t="n">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="DW6" t="n">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="DX6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DY6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5113350125944585</v>
+        <v>0.5187793427230047</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.553133514986376</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8363636363636363</v>
+        <v>0.8315217391304348</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3909952606635071</v>
+        <v>0.3948497854077253</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4369747899159664</v>
+        <v>0.4242424242424243</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3909952606635071</v>
+        <v>0.3948497854077253</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5925373134328358</v>
+        <v>0.5875862068965517</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6074766355140186</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5580110497237569</v>
+        <v>0.5440414507772021</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5902014652014652</v>
+        <v>0.5894206549118388</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.7</v>
+        <v>0.710691823899371</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.5815384615384616</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6180944755804644</v>
+        <v>0.6163475699558174</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6343669250645995</v>
+        <v>0.6201923076923077</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3864468864468865</v>
+        <v>0.3912678421494543</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.009478672985781991</v>
+        <v>0.008583690987124463</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07462686567164178</v>
+        <v>0.07448275862068965</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.08900523560209424</v>
+        <v>0.08958837772397095</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.06726457399103139</v>
+        <v>0.06639004149377593</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01538461538461539</v>
+        <v>0.01408450704225352</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.009836065573770493</v>
+        <v>0.009036144578313253</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5257142857142857</v>
+        <v>0.531578947368421</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9302325581395349</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.6911764705882353</v>
+        <v>0.7048611111111112</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.3843283582089552</v>
+        <v>0.391156462585034</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.7522935779816514</v>
+        <v>0.7549295774647887</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2709163346613546</v>
+        <v>0.2836363636363636</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7245409015025042</v>
+        <v>0.7325038880248833</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3294797687861272</v>
+        <v>0.3391915641476274</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4297520661157025</v>
+        <v>0.4427480916030535</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.3486238532110092</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.3421052631578947</v>
+        <v>0.35</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2445652173913044</v>
+        <v>0.2525252525252525</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3432835820895522</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.6210526315789474</v>
+        <v>0.6407766990291263</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.7384615384615385</v>
+        <v>0.7518248175182481</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7642276422764228</v>
+        <v>0.7620817843866171</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.7160493827160493</v>
+        <v>0.7325581395348837</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.05161290322580645</v>
+        <v>0.05088062622309197</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.35135135135135</v>
+        <v>95.75184638109306</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.89734513274336</v>
+        <v>15.81757259865972</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.31496815286624</v>
+        <v>14.26877761413844</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.22308930008045</v>
+        <v>15.13291139240506</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.75103503184713</v>
+        <v>13.72584683357879</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.3498168498168498</v>
+        <v>0.346767422334173</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6832460732984293</v>
+        <v>0.6828087167070218</v>
       </c>
       <c r="FY6" t="n">
         <v>0.75</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5670498084291188</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2042124542124542</v>
+        <v>0.2023509655751469</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4932735426008968</v>
+        <v>0.4730290456431535</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.5288461538461539</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4181818181818182</v>
+        <v>0.4298245614035088</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.05961376994122586</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.4</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.40625</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1125104953820319</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.4188034188034188</v>
+        <v>0.417910447761194</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4224137931034483</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2793040293040293</v>
+        <v>0.2787573467674223</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.380327868852459</v>
+        <v>0.3855421686746988</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3841059602649007</v>
+        <v>0.3890577507598784</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7844827586206896</v>
+        <v>0.7734375</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.45</v>
+        <v>0.4591194968553459</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1875</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.09285714285714286</v>
+        <v>0.0880503144654088</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5</v>
       </c>
       <c r="GV6" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2214285714285714</v>
+        <v>0.2389937106918239</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6442307692307693</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.08923076923076922</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.6</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3133333333333334</v>
+        <v>0.3169230769230769</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3936170212765958</v>
+        <v>0.3980582524271845</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7362637362637363</v>
+        <v>0.7380352644836272</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.380327868852459</v>
+        <v>0.3855421686746988</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5669127532228361</v>
+        <v>0.5687484797297298</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5484762626262626</v>
+        <v>0.5550714285714285</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5483280612244897</v>
+        <v>0.5447915094339623</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.101510067114094</v>
+        <v>0.09861325115562404</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1516339869281046</v>
+        <v>0.1487303506650544</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.0117096018735363</v>
+        <v>0.01061571125265393</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1394448030987734</v>
+        <v>0.1477069684335914</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3182698515171078</v>
+        <v>0.3085169743895176</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.390298507462687</v>
+        <v>5.410620689655172</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.29136690647482</v>
+        <v>25.27630434782609</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.3016894609814964</v>
+        <v>0.2993298585256888</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.008547008547008548</v>
+        <v>0.007462686567164179</v>
       </c>
     </row>
     <row r="7">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,329 +7135,329 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>43800</v>
+        <v>46680</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="J10" t="n">
-        <v>1492</v>
+        <v>1593</v>
       </c>
       <c r="K10" t="n">
-        <v>1504</v>
+        <v>1606</v>
       </c>
       <c r="L10" t="n">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="M10" t="n">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="N10" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="O10" t="n">
-        <v>2996</v>
+        <v>3199</v>
       </c>
       <c r="P10" t="n">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="Q10" t="n">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="R10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="S10" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="T10" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U10" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="V10" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W10" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y10" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="Z10" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA10" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AF10" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="n">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AK10" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AL10" t="n">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="AM10" t="n">
-        <v>780</v>
+        <v>831</v>
       </c>
       <c r="AN10" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="AO10" t="n">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="AP10" t="n">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1732</v>
+        <v>1846</v>
       </c>
       <c r="AR10" t="n">
-        <v>1569</v>
+        <v>1696</v>
       </c>
       <c r="AS10" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AT10" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
+        <v>51</v>
+      </c>
+      <c r="AW10" t="n">
         <v>46</v>
       </c>
-      <c r="AW10" t="n">
-        <v>40</v>
-      </c>
       <c r="AX10" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="AY10" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AZ10" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="BA10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BB10" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="BC10" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="BD10" t="n">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="BE10" t="n">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="BF10" t="n">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="BG10" t="n">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="BH10" t="n">
         <v>51</v>
       </c>
       <c r="BI10" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="BJ10" t="n">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="BK10" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="BL10" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="BM10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN10" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="BO10" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="BP10" t="n">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="BQ10" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="BR10" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="BS10" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="BT10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="BU10" t="n">
         <v>10</v>
       </c>
       <c r="BV10" t="n">
-        <v>923</v>
+        <v>985</v>
       </c>
       <c r="BW10" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="BX10" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="BY10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="CA10" t="n">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="CB10" t="n">
+        <v>37</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>620</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>231</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>851</v>
+      </c>
+      <c r="CF10" t="n">
         <v>34</v>
       </c>
-      <c r="CC10" t="n">
-        <v>593</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>210</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>803</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>31</v>
-      </c>
       <c r="CG10" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="CH10" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="CI10" t="n">
+        <v>68</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>129</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>22</v>
+      </c>
+      <c r="CL10" t="n">
         <v>62</v>
       </c>
-      <c r="CJ10" t="n">
-        <v>120</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>19</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>58</v>
-      </c>
       <c r="CM10" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="CN10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO10" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CR10" t="n">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="CS10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="CT10" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="CU10" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="CV10" t="n">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="CW10" t="n">
         <v>12</v>
       </c>
       <c r="CX10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CY10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CZ10" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="DC10" t="n">
         <v>16</v>
       </c>
       <c r="DD10" t="n">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="DE10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
         <v>5</v>
       </c>
       <c r="DH10" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="DI10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DJ10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="DK10" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="DL10" t="n">
         <v>10</v>
@@ -7466,19 +7466,19 @@
         <v>6</v>
       </c>
       <c r="DN10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DQ10" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="DR10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="DS10" t="n">
         <v>5</v>
@@ -7487,310 +7487,310 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1500</v>
+        <v>1599</v>
       </c>
       <c r="DV10" t="n">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="DW10" t="n">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="DX10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="DY10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4812206572769953</v>
+        <v>0.4833702882483371</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5380577427821522</v>
+        <v>0.5409429280397022</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9095744680851063</v>
+        <v>0.915</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3584229390681004</v>
       </c>
       <c r="ED10" t="n">
+        <v>0.4509803921568628</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.3652694610778443</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.3584229390681004</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.542719614921781</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.4776632302405499</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.5406767458603312</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.5677966101694916</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0.5032751091703057</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0.5836501901140685</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0.6175</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0.563963963963964</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.4017278617710583</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0.008960573476702509</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.07581227436823104</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.0911062906724512</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.06985294117647059</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0.005141388174807198</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.5201612903225806</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.6609808102345416</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.3386243386243386</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.7319034852546917</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.6923990498812351</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.310958904109589</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.4240506329113924</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.297071129707113</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.247787610619469</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.6055555555555555</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.6763285024154589</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.7439024390243902</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.7104247104247104</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.7807017543859649</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>98.68380462724936</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.5655737704918032</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>14.34036409290647</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>14.84171855541718</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>13.74664155681105</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>14.09414694894147</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.3318934485241181</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.6550976138828634</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.720763723150358</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.5066225165562914</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.1958243340532757</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.4448529411764706</v>
+      </c>
+      <c r="GC10" t="n">
         <v>0.4782608695652174</v>
       </c>
-      <c r="EE10" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="EF10" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="EG10" t="n">
-        <v>0.5461538461538461</v>
-      </c>
-      <c r="EH10" t="n">
-        <v>0.5338983050847458</v>
-      </c>
-      <c r="EI10" t="n">
-        <v>0.4818840579710145</v>
-      </c>
-      <c r="EJ10" t="n">
-        <v>0.5458750963762529</v>
-      </c>
-      <c r="EK10" t="n">
-        <v>0.5853658536585366</v>
-      </c>
-      <c r="EL10" t="n">
-        <v>0.5114678899082569</v>
-      </c>
-      <c r="EM10" t="n">
-        <v>0.5869565217391305</v>
-      </c>
-      <c r="EN10" t="n">
-        <v>0.6304347826086957</v>
-      </c>
-      <c r="EO10" t="n">
-        <v>0.5676190476190476</v>
-      </c>
-      <c r="EP10" t="n">
-        <v>0.3986121819583655</v>
-      </c>
-      <c r="EQ10" t="n">
-        <v>0.007736943907156673</v>
-      </c>
-      <c r="ER10" t="n">
-        <v>0.07564102564102564</v>
-      </c>
-      <c r="ES10" t="n">
-        <v>0.09259259259259259</v>
-      </c>
-      <c r="ET10" t="n">
-        <v>0.06692913385826772</v>
-      </c>
-      <c r="EU10" t="n">
-        <v>0.02127659574468085</v>
-      </c>
-      <c r="EV10" t="n">
-        <v>0.002770083102493075</v>
-      </c>
-      <c r="EW10" t="n">
-        <v>0.5150214592274678</v>
-      </c>
-      <c r="EX10" t="n">
-        <v>0.8717948717948718</v>
-      </c>
-      <c r="EY10" t="n">
-        <v>0.08108108108108109</v>
-      </c>
-      <c r="EZ10" t="n">
-        <v>0.6644144144144144</v>
-      </c>
-      <c r="FA10" t="n">
-        <v>0.3323863636363636</v>
-      </c>
-      <c r="FB10" t="n">
-        <v>0.7415730337078652</v>
-      </c>
-      <c r="FC10" t="n">
-        <v>0.2786377708978328</v>
-      </c>
-      <c r="FD10" t="n">
-        <v>0.69875</v>
-      </c>
-      <c r="FE10" t="n">
-        <v>0.3066666666666666</v>
-      </c>
-      <c r="FF10" t="n">
-        <v>0.4027777777777778</v>
-      </c>
-      <c r="FG10" t="n">
-        <v>0.3049645390070922</v>
-      </c>
-      <c r="FH10" t="n">
-        <v>0.2388059701492537</v>
-      </c>
-      <c r="FI10" t="n">
-        <v>0.2889908256880734</v>
-      </c>
-      <c r="FJ10" t="n">
-        <v>0.2571428571428571</v>
-      </c>
-      <c r="FK10" t="n">
-        <v>0.6104651162790697</v>
-      </c>
-      <c r="FL10" t="n">
-        <v>0.6733668341708543</v>
-      </c>
-      <c r="FM10" t="n">
-        <v>0.7671232876712328</v>
-      </c>
-      <c r="FN10" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="FO10" t="n">
-        <v>0.8018867924528302</v>
-      </c>
-      <c r="FP10" t="n">
-        <v>0.05057096247960848</v>
-      </c>
-      <c r="FQ10" t="n">
-        <v>98.49863013698631</v>
-      </c>
-      <c r="FR10" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="FS10" t="n">
-        <v>14.40462466487936</v>
-      </c>
-      <c r="FT10" t="n">
-        <v>14.83264627659574</v>
-      </c>
-      <c r="FU10" t="n">
-        <v>13.82258713136729</v>
-      </c>
-      <c r="FV10" t="n">
-        <v>14.07619680851064</v>
-      </c>
-      <c r="FW10" t="n">
-        <v>0.3330763299922899</v>
-      </c>
-      <c r="FX10" t="n">
-        <v>0.6643518518518519</v>
-      </c>
-      <c r="FY10" t="n">
-        <v>0.7321428571428571</v>
-      </c>
-      <c r="FZ10" t="n">
-        <v>0.5017421602787456</v>
-      </c>
-      <c r="GA10" t="n">
-        <v>0.1958365458750964</v>
-      </c>
-      <c r="GB10" t="n">
-        <v>0.4409448818897638</v>
-      </c>
-      <c r="GC10" t="n">
-        <v>0.4725738396624473</v>
-      </c>
       <c r="GD10" t="n">
-        <v>0.4553571428571428</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07247494217424827</v>
+        <v>0.07055435565154787</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.2872340425531915</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.2934782608695652</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1202775636083269</v>
+        <v>0.1216702663786897</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.3313609467455622</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3373493975903614</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2783346183500385</v>
+        <v>0.2800575953923686</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3795013850415512</v>
+        <v>0.3701799485861182</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3805555555555555</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8759124087591241</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5060975609756098</v>
+        <v>0.5084745762711864</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5903614457831325</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1224489795918367</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06707317073170732</v>
+        <v>0.06779661016949153</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2134146341463415</v>
+        <v>0.2203389830508475</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3394495412844037</v>
+        <v>0.3406113537117904</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5743243243243243</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.0963302752293578</v>
+        <v>0.0982532751091703</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2706422018348624</v>
+        <v>0.2663755458515284</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3728813559322034</v>
+        <v>0.3688524590163935</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7316885119506553</v>
+        <v>0.7336213102951764</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3795013850415512</v>
+        <v>0.3701799485861182</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5663923374613004</v>
+        <v>0.5659708453757225</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.543864761904762</v>
+        <v>0.5451378260869565</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5556268518518519</v>
+        <v>0.5544959251101321</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.118798955613577</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1822173435784852</v>
+        <v>0.1831275720164609</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.005780346820809248</v>
+        <v>0.007142857142857143</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1339491916859122</v>
+        <v>0.1338028169014084</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3446882217090069</v>
+        <v>0.3396533044420368</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.688589743589744</v>
+        <v>5.642238267148014</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.28774319066148</v>
+        <v>25.25279279279279</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3572386058981233</v>
+        <v>0.3496547394852479</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01923076923076923</v>
+        <v>0.01775147928994083</v>
       </c>
     </row>
     <row r="11">
@@ -11271,67 +11271,67 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>35160</v>
+        <v>38040</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J16" t="n">
-        <v>1160</v>
+        <v>1261</v>
       </c>
       <c r="K16" t="n">
-        <v>1173</v>
+        <v>1275</v>
       </c>
       <c r="L16" t="n">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="M16" t="n">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="N16" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="O16" t="n">
-        <v>2333</v>
+        <v>2536</v>
       </c>
       <c r="P16" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="Q16" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="R16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U16" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="V16" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="W16" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="X16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Y16" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="Z16" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AA16" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
@@ -11343,193 +11343,193 @@
         <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AF16" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="AG16" t="n">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
+        <v>49</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>37</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>99</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>372</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>672</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>179</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>258</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1539</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1397</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>47</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>58</v>
+      </c>
+      <c r="AW16" t="n">
         <v>44</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>92</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>346</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>621</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>165</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>448</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>225</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1412</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1283</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>43</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>74</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>53</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>38</v>
-      </c>
       <c r="AX16" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="AY16" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AZ16" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="BA16" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="BB16" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="BC16" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="BD16" t="n">
-        <v>403</v>
+        <v>455</v>
       </c>
       <c r="BE16" t="n">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="BF16" t="n">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="BG16" t="n">
-        <v>441</v>
+        <v>480</v>
       </c>
       <c r="BH16" t="n">
+        <v>57</v>
+      </c>
+      <c r="BI16" t="n">
         <v>54</v>
       </c>
-      <c r="BI16" t="n">
-        <v>48</v>
-      </c>
       <c r="BJ16" t="n">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="BK16" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="BL16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="BM16" t="n">
         <v>6</v>
       </c>
       <c r="BN16" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="BO16" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="BP16" t="n">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="BQ16" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="BR16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BS16" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="BT16" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="BU16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BV16" t="n">
-        <v>781</v>
+        <v>846</v>
       </c>
       <c r="BW16" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="BX16" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="CA16" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="CB16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CC16" t="n">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="CD16" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="CE16" t="n">
-        <v>572</v>
+        <v>627</v>
       </c>
       <c r="CF16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CG16" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="CH16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="CI16" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CJ16" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="CK16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CL16" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="CM16" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="CN16" t="n">
         <v>14</v>
       </c>
       <c r="CO16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="CP16" t="n">
         <v>3</v>
@@ -11538,325 +11538,325 @@
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="CS16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CT16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CU16" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="CV16" t="n">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CY16" t="n">
         <v>18</v>
       </c>
       <c r="CZ16" t="n">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="DA16" t="n">
         <v>9</v>
       </c>
       <c r="DB16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="DC16" t="n">
+        <v>22</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>303</v>
+      </c>
+      <c r="DE16" t="n">
         <v>21</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>265</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>20</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
       </c>
       <c r="DG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DH16" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="DI16" t="n">
         <v>5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="DK16" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="DL16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DM16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DN16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="DO16" t="n">
         <v>3</v>
       </c>
       <c r="DP16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="DQ16" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="DR16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="DS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DT16" t="n">
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>1219</v>
+        <v>1320</v>
       </c>
       <c r="DV16" t="n">
-        <v>399</v>
+        <v>451</v>
       </c>
       <c r="DW16" t="n">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="DX16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="DY16" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4913294797687861</v>
+        <v>0.4919354838709677</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.5279503105590062</v>
+        <v>0.5304347826086957</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.8909090909090909</v>
+        <v>0.8938547486033519</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.3683035714285715</v>
+        <v>0.3729166666666667</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.4339622641509434</v>
+        <v>0.4655172413793103</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.359375</v>
+        <v>0.3695652173913043</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.3683035714285715</v>
+        <v>0.3729166666666667</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.5571658615136876</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.581081081081081</v>
+        <v>0.5875</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.5551917680074836</v>
+        <v>0.5559895833333334</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.610236220472441</v>
+        <v>0.6340579710144928</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.5441696113074205</v>
+        <v>0.5473856209150327</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.5935919055649241</v>
+        <v>0.5959595959595959</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.6476510067114094</v>
+        <v>0.6717791411042945</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.5985074626865672</v>
+        <v>0.6075268817204301</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4190832553788588</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01339285714285714</v>
+        <v>0.0125</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.07085346215780998</v>
+        <v>0.06994047619047619</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.08880308880308881</v>
+        <v>0.08992805755395683</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.06147540983606557</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.05084745762711865</v>
+        <v>0.04615384615384616</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01567398119122257</v>
+        <v>0.01474926253687316</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.5364238410596026</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.875</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.2</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.6512455516014235</v>
+        <v>0.6449511400651465</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.7019867549668874</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.3118279569892473</v>
+        <v>0.3209459459459459</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.6768953068592057</v>
+        <v>0.6732348111658456</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.3132969034608379</v>
+        <v>0.3214890016920474</v>
       </c>
       <c r="FF16" t="n">
+        <v>0.4096385542168675</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0.3181818181818182</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0.3708920187793427</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0.5158730158730159</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0.7203389830508474</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0.6822429906542056</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>96</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0.5245901639344263</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>14.99206978588422</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>15.0078431372549</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>14.33822363203807</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>14.36094117647059</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0.2413194444444444</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0.6942446043165468</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0.7628458498023716</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0.5544041450777202</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0.2291666666666667</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0.4924242424242424</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0.5241935483870968</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0.4923076923076923</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0.1128472222222222</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0.3769230769230769</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0.3951612903225806</v>
+      </c>
+      <c r="GH16" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="GI16" t="n">
+        <v>0.1223958333333333</v>
+      </c>
+      <c r="GJ16" t="n">
+        <v>0.3971631205673759</v>
+      </c>
+      <c r="GK16" t="n">
         <v>0.4</v>
       </c>
-      <c r="FG16" t="n">
-        <v>0.3225806451612903</v>
-      </c>
-      <c r="FH16" t="n">
-        <v>0.2112676056338028</v>
-      </c>
-      <c r="FI16" t="n">
-        <v>0.3676470588235294</v>
-      </c>
-      <c r="FJ16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="FK16" t="n">
-        <v>0.5357142857142857</v>
-      </c>
-      <c r="FL16" t="n">
-        <v>0.7155963302752294</v>
-      </c>
-      <c r="FM16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="FN16" t="n">
-        <v>0.689119170984456</v>
-      </c>
-      <c r="FO16" t="n">
-        <v>0.7375</v>
-      </c>
-      <c r="FP16" t="n">
-        <v>0.03393213572854292</v>
-      </c>
-      <c r="FQ16" t="n">
-        <v>95.54948805460751</v>
-      </c>
-      <c r="FR16" t="n">
-        <v>0.5357142857142857</v>
-      </c>
-      <c r="FS16" t="n">
-        <v>14.98060344827586</v>
-      </c>
-      <c r="FT16" t="n">
-        <v>15.15984654731458</v>
-      </c>
-      <c r="FU16" t="n">
-        <v>14.32405172413793</v>
-      </c>
-      <c r="FV16" t="n">
-        <v>14.52267689684569</v>
-      </c>
-      <c r="FW16" t="n">
-        <v>0.2422825070159027</v>
-      </c>
-      <c r="FX16" t="n">
-        <v>0.7027027027027027</v>
-      </c>
-      <c r="FY16" t="n">
-        <v>0.7711864406779662</v>
-      </c>
-      <c r="FZ16" t="n">
-        <v>0.5604395604395604</v>
-      </c>
-      <c r="GA16" t="n">
-        <v>0.2282507015902713</v>
-      </c>
-      <c r="GB16" t="n">
-        <v>0.4836065573770492</v>
-      </c>
-      <c r="GC16" t="n">
-        <v>0.5152838427947598</v>
-      </c>
-      <c r="GD16" t="n">
-        <v>0.4830508474576271</v>
-      </c>
-      <c r="GE16" t="n">
-        <v>0.1103835360149673</v>
-      </c>
-      <c r="GF16" t="n">
-        <v>0.3898305084745763</v>
-      </c>
-      <c r="GG16" t="n">
-        <v>0.4107142857142857</v>
-      </c>
-      <c r="GH16" t="n">
-        <v>0.2391304347826087</v>
-      </c>
-      <c r="GI16" t="n">
-        <v>0.1206735266604303</v>
-      </c>
-      <c r="GJ16" t="n">
-        <v>0.4108527131782946</v>
-      </c>
-      <c r="GK16" t="n">
-        <v>0.4140625</v>
-      </c>
       <c r="GL16" t="n">
-        <v>0.9622641509433962</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="GM16" t="n">
-        <v>0.2984097287184284</v>
+        <v>0.2942708333333333</v>
       </c>
       <c r="GN16" t="n">
-        <v>0.3510971786833856</v>
+        <v>0.3628318584070797</v>
       </c>
       <c r="GO16" t="n">
-        <v>0.356687898089172</v>
+        <v>0.3682634730538922</v>
       </c>
       <c r="GP16" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8617886178861789</v>
       </c>
       <c r="GQ16" t="n">
-        <v>0.3779527559055118</v>
+        <v>0.3623188405797101</v>
       </c>
       <c r="GR16" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.66</v>
       </c>
       <c r="GS16" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.07086614173228346</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="GU16" t="n">
         <v>0.4444444444444444</v>
@@ -11865,75 +11865,75 @@
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.3464566929133858</v>
+        <v>0.355072463768116</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="GY16" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.2614840989399294</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.127208480565371</v>
+        <v>0.1274509803921569</v>
       </c>
       <c r="HC16" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.3250883392226148</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3737373737373738</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6613657623947614</v>
+        <v>0.6579861111111112</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3510971786833856</v>
+        <v>0.3628318584070797</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.539843661971831</v>
+        <v>0.5395619773519164</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5469208860759494</v>
+        <v>0.5468635294117647</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.5374741071428571</v>
+        <v>0.5356179867986799</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.09043478260869565</v>
+        <v>0.09251810136765889</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1414285714285714</v>
+        <v>0.1445466491458607</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.01037344398340249</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.136685552407932</v>
+        <v>0.1423001949317739</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.2854107648725213</v>
+        <v>0.2956465237166991</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.498872785829308</v>
+        <v>7.556845238095238</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.3027027027027</v>
+        <v>25.27121848739496</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.2724137931034483</v>
+        <v>0.2791435368754956</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
       <c r="HU16" t="n">
-        <v>0.007751937984496124</v>
+        <v>0.007092198581560284</v>
       </c>
     </row>
     <row r="17">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,67 +7135,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>46680</v>
+        <v>49560</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="J10" t="n">
-        <v>1593</v>
+        <v>1691</v>
       </c>
       <c r="K10" t="n">
-        <v>1606</v>
+        <v>1705</v>
       </c>
       <c r="L10" t="n">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="M10" t="n">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="N10" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="O10" t="n">
-        <v>3199</v>
+        <v>3396</v>
       </c>
       <c r="P10" t="n">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="Q10" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="R10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="T10" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="U10" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="V10" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="W10" t="n">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="X10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="Z10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AA10" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -7207,13 +7207,13 @@
         <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AG10" t="n">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="AH10" t="n">
         <v>18</v>
@@ -7222,37 +7222,37 @@
         <v>39</v>
       </c>
       <c r="AJ10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK10" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="AL10" t="n">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="AM10" t="n">
-        <v>831</v>
+        <v>878</v>
       </c>
       <c r="AN10" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="AO10" t="n">
-        <v>558</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1846</v>
+        <v>1964</v>
       </c>
       <c r="AR10" t="n">
-        <v>1696</v>
+        <v>1787</v>
       </c>
       <c r="AS10" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AT10" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
@@ -7261,185 +7261,185 @@
         <v>51</v>
       </c>
       <c r="AW10" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AX10" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="AY10" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="AZ10" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="BA10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BB10" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="BC10" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="BD10" t="n">
-        <v>627</v>
+        <v>663</v>
       </c>
       <c r="BE10" t="n">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="BF10" t="n">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="BG10" t="n">
-        <v>549</v>
+        <v>591</v>
       </c>
       <c r="BH10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BI10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BJ10" t="n">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="BK10" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="BL10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="BM10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="BO10" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="BP10" t="n">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="BQ10" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="BR10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="BS10" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="BT10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="BU10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>985</v>
+        <v>1059</v>
       </c>
       <c r="BW10" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="BX10" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="BY10" t="n">
         <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="CA10" t="n">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="CB10" t="n">
         <v>37</v>
       </c>
       <c r="CC10" t="n">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="CD10" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="CE10" t="n">
-        <v>851</v>
+        <v>909</v>
       </c>
       <c r="CF10" t="n">
         <v>34</v>
       </c>
       <c r="CG10" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="CH10" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="CI10" t="n">
         <v>68</v>
       </c>
       <c r="CJ10" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="CK10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CL10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="CM10" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="CN10" t="n">
         <v>18</v>
       </c>
       <c r="CO10" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CR10" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="CS10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CT10" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="CU10" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="CV10" t="n">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="CW10" t="n">
         <v>12</v>
       </c>
       <c r="CX10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CY10" t="n">
         <v>31</v>
       </c>
       <c r="CZ10" t="n">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="DC10" t="n">
         <v>16</v>
       </c>
       <c r="DD10" t="n">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="DE10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
@@ -7448,16 +7448,16 @@
         <v>5</v>
       </c>
       <c r="DH10" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="DI10" t="n">
         <v>6</v>
       </c>
       <c r="DJ10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="DK10" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="DL10" t="n">
         <v>10</v>
@@ -7466,259 +7466,259 @@
         <v>6</v>
       </c>
       <c r="DN10" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DQ10" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="DR10" t="n">
         <v>69</v>
       </c>
       <c r="DS10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DT10" t="n">
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1599</v>
+        <v>1703</v>
       </c>
       <c r="DV10" t="n">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="DW10" t="n">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="DX10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="DY10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4833702882483371</v>
+        <v>0.4905660377358491</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5409429280397022</v>
+        <v>0.5467289719626168</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.915</v>
+        <v>0.9162790697674419</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3584229390681004</v>
+        <v>0.3583333333333333</v>
       </c>
       <c r="ED10" t="n">
         <v>0.4509803921568628</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3652694610778443</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3584229390681004</v>
+        <v>0.3583333333333333</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.542719614921781</v>
+        <v>0.5432801822323462</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5303030303030303</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4776632302405499</v>
+        <v>0.4808917197452229</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5406767458603312</v>
+        <v>0.5409336941813261</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5677966101694916</v>
+        <v>0.5710382513661202</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5032751091703057</v>
+        <v>0.4939271255060729</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5836501901140685</v>
+        <v>0.5840286054827175</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6175</v>
+        <v>0.6214285714285714</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.563963963963964</v>
+        <v>0.5553691275167785</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4017278617710583</v>
+        <v>0.4059539918809202</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.008960573476702509</v>
+        <v>0.01</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07581227436823104</v>
+        <v>0.07403189066059225</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0911062906724512</v>
+        <v>0.08731808731808732</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06985294117647059</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.01941747572815534</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.005141388174807198</v>
+        <v>0.007177033492822967</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5201612903225806</v>
+        <v>0.5287356321839081</v>
       </c>
       <c r="EX10" t="n">
         <v>0.8809523809523809</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6609808102345416</v>
+        <v>0.6646586345381527</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3386243386243386</v>
+        <v>0.3383458646616541</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7319034852546917</v>
+        <v>0.736318407960199</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.28125</v>
+        <v>0.2804232804232804</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6923990498812351</v>
+        <v>0.6966666666666667</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.310958904109589</v>
+        <v>0.3101673101673101</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4240506329113924</v>
+        <v>0.4121212121212121</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3</v>
+        <v>0.3067484662576687</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.2394366197183098</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.297071129707113</v>
+        <v>0.2862745098039216</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.247787610619469</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6055555555555555</v>
+        <v>0.6030927835051546</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6763285024154589</v>
+        <v>0.6820276497695853</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7439024390243902</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7104247104247104</v>
+        <v>0.7224199288256228</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7807017543859649</v>
+        <v>0.768595041322314</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.05128205128205128</v>
+        <v>0.04809052333804809</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.68380462724936</v>
+        <v>98.67312348668281</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5655737704918032</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.34036409290647</v>
+        <v>14.33435836782969</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.84171855541718</v>
+        <v>14.8507917888563</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.74664155681105</v>
+        <v>13.73926670609107</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.09414694894147</v>
+        <v>14.10070381231671</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3318934485241181</v>
+        <v>0.3254397834912043</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6550976138828634</v>
+        <v>0.6548856548856549</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.720763723150358</v>
+        <v>0.7175398633257403</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5066225165562914</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1958243340532757</v>
+        <v>0.1989174560216509</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4448529411764706</v>
+        <v>0.4421768707482993</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4538461538461538</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07055435565154787</v>
+        <v>0.06968876860622462</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3106796116504854</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3168316831683168</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.40625</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1216702663786897</v>
+        <v>0.1231393775372124</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3313609467455622</v>
+        <v>0.3241758241758242</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.329608938547486</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2800575953923686</v>
+        <v>0.2828146143437077</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3701799485861182</v>
+        <v>0.3732057416267943</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3720930232558139</v>
+        <v>0.3759036144578313</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5084745762711864</v>
+        <v>0.5027322404371585</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.5760869565217391</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.1132075471698113</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06779661016949153</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="GU10" t="n">
         <v>0.4166666666666667</v>
@@ -7727,7 +7727,7 @@
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2203389830508475</v>
+        <v>0.2131147540983606</v>
       </c>
       <c r="GX10" t="n">
         <v>0.4615384615384616</v>
@@ -7736,61 +7736,61 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3406113537117904</v>
+        <v>0.3319838056680162</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.5670731707317073</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.0982532751091703</v>
+        <v>0.1012145748987854</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.32</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2663755458515284</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3688524590163935</v>
+        <v>0.3538461538461539</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7336213102951764</v>
+        <v>0.7313937753721245</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3701799485861182</v>
+        <v>0.3732057416267943</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5659708453757225</v>
+        <v>0.5646444293478261</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5451378260869565</v>
+        <v>0.5428783898305085</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5544959251101321</v>
+        <v>0.5517602249488752</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.118798955613577</v>
+        <v>0.1179361179361179</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1831275720164609</v>
+        <v>0.1832358674463938</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.007142857142857143</v>
+        <v>0.006644518272425249</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.1328920570264766</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3396533044420368</v>
+        <v>0.3375763747454175</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.642238267148014</v>
+        <v>5.691116173120729</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.25279279279279</v>
+        <v>25.25654362416107</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3496547394852479</v>
+        <v>0.3530455351862803</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01775147928994083</v>
+        <v>0.01648351648351648</v>
       </c>
     </row>
     <row r="11">
@@ -11271,67 +11271,67 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>38040</v>
+        <v>40920</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="J16" t="n">
-        <v>1261</v>
+        <v>1359</v>
       </c>
       <c r="K16" t="n">
-        <v>1275</v>
+        <v>1374</v>
       </c>
       <c r="L16" t="n">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="M16" t="n">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="N16" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="O16" t="n">
-        <v>2536</v>
+        <v>2733</v>
       </c>
       <c r="P16" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="Q16" t="n">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="R16" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U16" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="V16" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="W16" t="n">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="X16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Y16" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="Z16" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
@@ -11340,193 +11340,193 @@
         <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="n">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
+        <v>54</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>111</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>397</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>726</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>521</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>269</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1515</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>52</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>63</v>
+      </c>
+      <c r="AW16" t="n">
         <v>49</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>37</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>99</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>372</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>672</v>
-      </c>
-      <c r="AN16" t="n">
+      <c r="AX16" t="n">
+        <v>237</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>94</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>179</v>
       </c>
-      <c r="AO16" t="n">
-        <v>480</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>258</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1539</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1397</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>47</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>58</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>219</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>91</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>168</v>
-      </c>
       <c r="BA16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="BB16" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="BC16" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BD16" t="n">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="BE16" t="n">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="BF16" t="n">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="BG16" t="n">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="BH16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BI16" t="n">
+        <v>62</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>369</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>129</v>
+      </c>
+      <c r="BL16" t="n">
         <v>54</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>339</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>123</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>47</v>
       </c>
       <c r="BM16" t="n">
         <v>6</v>
       </c>
       <c r="BN16" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="BO16" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="BP16" t="n">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="BQ16" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="BR16" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BS16" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="BT16" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="BU16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BV16" t="n">
-        <v>846</v>
+        <v>899</v>
       </c>
       <c r="BW16" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="BX16" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
+        <v>231</v>
+      </c>
+      <c r="CA16" t="n">
         <v>212</v>
       </c>
-      <c r="CA16" t="n">
-        <v>198</v>
-      </c>
       <c r="CB16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CC16" t="n">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="CD16" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="CE16" t="n">
-        <v>627</v>
+        <v>675</v>
       </c>
       <c r="CF16" t="n">
         <v>18</v>
       </c>
       <c r="CG16" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="CH16" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="CI16" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="CJ16" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="CK16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CL16" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="CM16" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="CN16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CO16" t="n">
         <v>48</v>
@@ -11538,46 +11538,46 @@
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="CS16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CT16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CU16" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="CV16" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="CY16" t="n">
         <v>18</v>
       </c>
       <c r="CZ16" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="DA16" t="n">
         <v>9</v>
       </c>
       <c r="DB16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="DC16" t="n">
         <v>22</v>
       </c>
       <c r="DD16" t="n">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="DE16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -11586,22 +11586,22 @@
         <v>5</v>
       </c>
       <c r="DH16" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="DI16" t="n">
         <v>5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DK16" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="DL16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DM16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DN16" t="n">
         <v>41</v>
@@ -11610,13 +11610,13 @@
         <v>3</v>
       </c>
       <c r="DP16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="DR16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="DS16" t="n">
         <v>2</v>
@@ -11625,238 +11625,238 @@
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>1320</v>
+        <v>1393</v>
       </c>
       <c r="DV16" t="n">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="DW16" t="n">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="DX16" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="DY16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4919354838709677</v>
+        <v>0.4937027707808564</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.5304347826086957</v>
+        <v>0.5355191256830601</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.8938547486033519</v>
+        <v>0.8941798941798942</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.3729166666666667</v>
+        <v>0.362763915547025</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.3695652173913043</v>
+        <v>0.3464052287581699</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.3729166666666667</v>
+        <v>0.362763915547025</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.546831955922865</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.5875</v>
+        <v>0.611764705882353</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5251396648044693</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.5559895833333334</v>
+        <v>0.5457097032878909</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.6340579710144928</v>
+        <v>0.6351351351351351</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.5473856209150327</v>
+        <v>0.5225903614457831</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.5959595959595959</v>
+        <v>0.5857966834895458</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.6717791411042945</v>
+        <v>0.6771428571428572</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.6075268817204301</v>
+        <v>0.5839598997493735</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4178027265437049</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0125</v>
+        <v>0.01151631477927063</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.06994047619047619</v>
+        <v>0.0743801652892562</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.08992805755395683</v>
+        <v>0.1019736842105263</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.06007067137809187</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.04615384615384616</v>
+        <v>0.04316546762589928</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01474926253687316</v>
+        <v>0.01355013550135501</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.5654761904761905</v>
+        <v>0.5635359116022099</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="EY16" t="n">
         <v>0.1739130434782609</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.6449511400651465</v>
+        <v>0.6463414634146342</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.3220338983050847</v>
+        <v>0.3179012345679013</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.7019867549668874</v>
+        <v>0.7042682926829268</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.3209459459459459</v>
+        <v>0.3107692307692307</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.6732348111658456</v>
+        <v>0.6753048780487805</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.3214890016920474</v>
+        <v>0.3143297380585516</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.4096385542168675</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3098591549295774</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.2375</v>
+        <v>0.2235294117647059</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.3708920187793427</v>
+        <v>0.348936170212766</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.1927710843373494</v>
+        <v>0.2111111111111111</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.5158730158730159</v>
+        <v>0.5338345864661654</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.7203389830508474</v>
+        <v>0.7099236641221374</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.75</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.6822429906542056</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.75</v>
+        <v>0.7244897959183674</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03045685279187817</v>
       </c>
       <c r="FQ16" t="n">
-        <v>96</v>
+        <v>96.17595307917888</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.5245901639344263</v>
+        <v>0.53125</v>
       </c>
       <c r="FS16" t="n">
-        <v>14.99206978588422</v>
+        <v>15.00353200883002</v>
       </c>
       <c r="FT16" t="n">
-        <v>15.0078431372549</v>
+        <v>14.94192139737991</v>
       </c>
       <c r="FU16" t="n">
-        <v>14.33822363203807</v>
+        <v>14.3392200147167</v>
       </c>
       <c r="FV16" t="n">
-        <v>14.36094117647059</v>
+        <v>14.29759825327511</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.2413194444444444</v>
+        <v>0.243785084202085</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.6942446043165468</v>
+        <v>0.6743421052631579</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.7628458498023716</v>
+        <v>0.7509157509157509</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.5544041450777202</v>
+        <v>0.551219512195122</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.2269446672012831</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.4924242424242424</v>
+        <v>0.4911660777385159</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.5241935483870968</v>
+        <v>0.5225563909774437</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.4923076923076923</v>
+        <v>0.5035971223021583</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.1128472222222222</v>
+        <v>0.111467522052927</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.381294964028777</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.3951612903225806</v>
+        <v>0.3984962406015037</v>
       </c>
       <c r="GH16" t="n">
-        <v>0.2448979591836735</v>
+        <v>0.2452830188679245</v>
       </c>
       <c r="GI16" t="n">
-        <v>0.1223958333333333</v>
+        <v>0.1218925421010425</v>
       </c>
       <c r="GJ16" t="n">
-        <v>0.3971631205673759</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="GK16" t="n">
-        <v>0.4</v>
+        <v>0.3973509933774834</v>
       </c>
       <c r="GL16" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="GM16" t="n">
-        <v>0.2942708333333333</v>
+        <v>0.2959101844426624</v>
       </c>
       <c r="GN16" t="n">
-        <v>0.3628318584070797</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="GO16" t="n">
-        <v>0.3682634730538922</v>
+        <v>0.3543956043956044</v>
       </c>
       <c r="GP16" t="n">
-        <v>0.8617886178861789</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="GQ16" t="n">
-        <v>0.3623188405797101</v>
+        <v>0.3716216216216216</v>
       </c>
       <c r="GR16" t="n">
-        <v>0.66</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="GS16" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.06081081081081081</v>
       </c>
       <c r="GU16" t="n">
         <v>0.4444444444444444</v>
@@ -11865,75 +11865,75 @@
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.355072463768116</v>
+        <v>0.3648648648648649</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GY16" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.25</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6506024096385542</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.1274509803921569</v>
+        <v>0.1265060240963855</v>
       </c>
       <c r="HC16" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.3343373493975904</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3737373737373738</v>
+        <v>0.3423423423423423</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6579861111111112</v>
+        <v>0.6615878107457899</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3628318584070797</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.5395619773519164</v>
+        <v>0.53899231078905</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5468635294117647</v>
+        <v>0.5462673913043478</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.5356179867986799</v>
+        <v>0.5353156534954407</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.09251810136765889</v>
+        <v>0.09016393442622951</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1445466491458607</v>
+        <v>0.1416361416361416</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.01037344398340249</v>
+        <v>0.009560229445506692</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.1423001949317739</v>
+        <v>0.145398773006135</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.2956465237166991</v>
+        <v>0.2877300613496933</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.556845238095238</v>
+        <v>7.537741046831956</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.27121848739496</v>
+        <v>25.29282945736434</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.2791435368754956</v>
+        <v>0.2803532008830022</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
       <c r="HU16" t="n">
-        <v>0.007092198581560284</v>
+        <v>0.006578947368421052</v>
       </c>
     </row>
     <row r="17">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -7135,265 +7135,265 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>49560</v>
+        <v>52440</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="J10" t="n">
-        <v>1691</v>
+        <v>1783</v>
       </c>
       <c r="K10" t="n">
-        <v>1705</v>
+        <v>1798</v>
       </c>
       <c r="L10" t="n">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="M10" t="n">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="N10" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="O10" t="n">
-        <v>3396</v>
+        <v>3581</v>
       </c>
       <c r="P10" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="Q10" t="n">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="R10" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="S10" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U10" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V10" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="W10" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Y10" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Z10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AA10" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AF10" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="AG10" t="n">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="AH10" t="n">
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AJ10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AK10" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AL10" t="n">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>878</v>
+        <v>926</v>
       </c>
       <c r="AN10" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="AP10" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1964</v>
+        <v>2075</v>
       </c>
       <c r="AR10" t="n">
-        <v>1787</v>
+        <v>1890</v>
       </c>
       <c r="AS10" t="n">
+        <v>76</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>141</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>56</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>54</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>278</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>155</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>322</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>63</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>188</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>176</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>675</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>484</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>516</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>630</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>66</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>108</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>446</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL10" t="n">
         <v>70</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>132</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>52</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>261</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>151</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>314</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>62</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>180</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>175</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>663</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>468</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>486</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>591</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>54</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>98</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>418</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>156</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>65</v>
       </c>
       <c r="BM10" t="n">
         <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="BO10" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="BP10" t="n">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="BQ10" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="BR10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="BS10" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="BT10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="BU10" t="n">
         <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>1059</v>
+        <v>1114</v>
       </c>
       <c r="BW10" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="BX10" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="BY10" t="n">
         <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="CA10" t="n">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="CB10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="CC10" t="n">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="CD10" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="CE10" t="n">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="CF10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CG10" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="CH10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="CI10" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="CK10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CL10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="CM10" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CN10" t="n">
         <v>18</v>
       </c>
       <c r="CO10" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
@@ -7402,62 +7402,62 @@
         <v>10</v>
       </c>
       <c r="CR10" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="CS10" t="n">
         <v>29</v>
       </c>
       <c r="CT10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="CU10" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="CV10" t="n">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="CW10" t="n">
         <v>12</v>
       </c>
       <c r="CX10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="CY10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CZ10" t="n">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="DC10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DD10" t="n">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="DE10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DH10" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="DI10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DJ10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="DK10" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="DL10" t="n">
         <v>10</v>
@@ -7466,7 +7466,7 @@
         <v>6</v>
       </c>
       <c r="DN10" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
@@ -7475,10 +7475,10 @@
         <v>35</v>
       </c>
       <c r="DQ10" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="DR10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="DS10" t="n">
         <v>6</v>
@@ -7487,310 +7487,310 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1703</v>
+        <v>1797</v>
       </c>
       <c r="DV10" t="n">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="DW10" t="n">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="DX10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="DY10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4905660377358491</v>
+        <v>0.484</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5467289719626168</v>
+        <v>0.5426008968609866</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9162790697674419</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.3625</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.3351063829787234</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3583333333333333</v>
+        <v>0.3625</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5432801822323462</v>
+        <v>0.5399568034557235</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5303030303030303</v>
+        <v>0.5390070921985816</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4808917197452229</v>
+        <v>0.4813664596273292</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5409336941813261</v>
+        <v>0.541507024265645</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5710382513661202</v>
+        <v>0.5685279187817259</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4939271255060729</v>
+        <v>0.4892156862745098</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5840286054827175</v>
+        <v>0.5834272829763247</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6214285714285714</v>
+        <v>0.6150442477876106</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5553691275167785</v>
+        <v>0.5497553017944535</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4059539918809202</v>
+        <v>0.4086845466155811</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01</v>
+        <v>0.009375</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07403189066059225</v>
+        <v>0.0755939524838013</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.08731808731808732</v>
+        <v>0.09197651663405088</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06885245901639345</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01941747572815534</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.007177033492822967</v>
+        <v>0.006726457399103139</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5287356321839081</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0975609756097561</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6646586345381527</v>
+        <v>0.6621880998080614</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3383458646616541</v>
+        <v>0.3419811320754717</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.736318407960199</v>
+        <v>0.731764705882353</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2804232804232804</v>
+        <v>0.2793017456359102</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6966666666666667</v>
+        <v>0.693446088794926</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3101673101673101</v>
+        <v>0.3115151515151515</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4121212121212121</v>
+        <v>0.4134078212290503</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3067484662576687</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2394366197183098</v>
+        <v>0.2533333333333334</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2862745098039216</v>
+        <v>0.2862453531598513</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2651515151515151</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6030927835051546</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6820276497695853</v>
+        <v>0.6768558951965066</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7224199288256228</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.768595041322314</v>
+        <v>0.776</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04809052333804809</v>
+        <v>0.048</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.67312348668281</v>
+        <v>98.33409610983982</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5343511450381679</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.33435836782969</v>
+        <v>14.4019068984857</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.8507917888563</v>
+        <v>14.88398220244716</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.73926670609107</v>
+        <v>13.81278743690409</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.10070381231671</v>
+        <v>14.1178531701891</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3254397834912043</v>
+        <v>0.326309067688378</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6548856548856549</v>
+        <v>0.6477495107632094</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7175398633257403</v>
+        <v>0.7133620689655172</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.5075528700906344</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1989174560216509</v>
+        <v>0.1947637292464879</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4421768707482993</v>
+        <v>0.4393442622950819</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4718309859154929</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4538461538461538</v>
+        <v>0.4552238805970149</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06968876860622462</v>
+        <v>0.07024265644955301</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3106796116504854</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3168316831683168</v>
+        <v>0.3240740740740741</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.40625</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1231393775372124</v>
+        <v>0.123882503192848</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3241758241758242</v>
+        <v>0.3195876288659794</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.329608938547486</v>
+        <v>0.3246073298429319</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2828146143437077</v>
+        <v>0.2848020434227331</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3732057416267943</v>
+        <v>0.3811659192825112</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3759036144578313</v>
+        <v>0.3837471783295711</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5027322404371585</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5760869565217391</v>
+        <v>0.58</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.06598984771573604</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2131147540983606</v>
+        <v>0.2182741116751269</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="GY10" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3319838056680162</v>
+        <v>0.3294117647058823</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5670731707317073</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1012145748987854</v>
+        <v>0.1058823529411765</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.32</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2627450980392157</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3538461538461539</v>
+        <v>0.3507462686567164</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7313937753721245</v>
+        <v>0.7349936143039592</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3732057416267943</v>
+        <v>0.3811659192825112</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5646444293478261</v>
+        <v>0.5645959615384615</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5428783898305085</v>
+        <v>0.54584609375</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5517602249488752</v>
+        <v>0.5514178217821782</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1179361179361179</v>
+        <v>0.1160766105629716</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1832358674463938</v>
+        <v>0.1805555555555556</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.006644518272425249</v>
+        <v>0.007776049766718507</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1328920570264766</v>
+        <v>0.1339759036144578</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3375763747454175</v>
+        <v>0.3253012048192771</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.691116173120729</v>
+        <v>5.706371490280778</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.25654362416107</v>
+        <v>25.25581761006289</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3530455351862803</v>
+        <v>0.3438025799214807</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01648351648351648</v>
+        <v>0.0154639175257732</v>
       </c>
     </row>
     <row r="11">
@@ -11271,73 +11271,73 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>40920</v>
+        <v>43800</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>1359</v>
+        <v>1451</v>
       </c>
       <c r="K16" t="n">
-        <v>1374</v>
+        <v>1467</v>
       </c>
       <c r="L16" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="M16" t="n">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="N16" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="O16" t="n">
-        <v>2733</v>
+        <v>2918</v>
       </c>
       <c r="P16" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q16" t="n">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="R16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S16" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="T16" t="n">
         <v>54</v>
       </c>
       <c r="U16" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V16" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="W16" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="X16" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="Z16" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AA16" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="AB16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>15</v>
@@ -11346,190 +11346,190 @@
         <v>42</v>
       </c>
       <c r="AF16" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="AG16" t="n">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI16" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AK16" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="AM16" t="n">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="AN16" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="n">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="AP16" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1630</v>
+        <v>1733</v>
       </c>
       <c r="AR16" t="n">
-        <v>1515</v>
+        <v>1626</v>
       </c>
       <c r="AS16" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AT16" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AU16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AV16" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="AW16" t="n">
         <v>49</v>
       </c>
       <c r="AX16" t="n">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="AY16" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AZ16" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="BA16" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="BB16" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="BC16" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BD16" t="n">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="BE16" t="n">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="BF16" t="n">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="BG16" t="n">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="BH16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="BI16" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="BJ16" t="n">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="BK16" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="BL16" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BM16" t="n">
         <v>6</v>
       </c>
       <c r="BN16" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="BO16" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="BP16" t="n">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="BQ16" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="BR16" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="BS16" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="BT16" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="BU16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BV16" t="n">
-        <v>899</v>
+        <v>956</v>
       </c>
       <c r="BW16" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="BX16" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="BY16" t="n">
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="CA16" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="CB16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CC16" t="n">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="CD16" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="CE16" t="n">
-        <v>675</v>
+        <v>726</v>
       </c>
       <c r="CF16" t="n">
+        <v>20</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>153</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>77</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>76</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>111</v>
+      </c>
+      <c r="CK16" t="n">
         <v>18</v>
       </c>
-      <c r="CG16" t="n">
-        <v>144</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>75</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>69</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>102</v>
-      </c>
-      <c r="CK16" t="n">
+      <c r="CL16" t="n">
+        <v>59</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>84</v>
+      </c>
+      <c r="CN16" t="n">
         <v>16</v>
       </c>
-      <c r="CL16" t="n">
-        <v>54</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>79</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>15</v>
-      </c>
       <c r="CO16" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CP16" t="n">
         <v>3</v>
@@ -11538,46 +11538,46 @@
         <v>3</v>
       </c>
       <c r="CR16" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="CS16" t="n">
         <v>26</v>
       </c>
       <c r="CT16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CU16" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="CV16" t="n">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CY16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CZ16" t="n">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="DA16" t="n">
         <v>9</v>
       </c>
       <c r="DB16" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="DC16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="DD16" t="n">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="DE16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -11586,16 +11586,16 @@
         <v>5</v>
       </c>
       <c r="DH16" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="DI16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DJ16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="DK16" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="DL16" t="n">
         <v>3</v>
@@ -11604,7 +11604,7 @@
         <v>3</v>
       </c>
       <c r="DN16" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="DO16" t="n">
         <v>3</v>
@@ -11613,10 +11613,10 @@
         <v>17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="DR16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="DS16" t="n">
         <v>2</v>
@@ -11625,315 +11625,315 @@
         <v>1</v>
       </c>
       <c r="DU16" t="n">
-        <v>1393</v>
+        <v>1476</v>
       </c>
       <c r="DV16" t="n">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="DW16" t="n">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="DX16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DY16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.4937027707808564</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.5355191256830601</v>
+        <v>0.5347043701799485</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.8941798941798942</v>
+        <v>0.8955223880597015</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.362763915547025</v>
+        <v>0.3602150537634409</v>
       </c>
       <c r="ED16" t="n">
         <v>0.4444444444444444</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.3464052287581699</v>
+        <v>0.345679012345679</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.362763915547025</v>
+        <v>0.3602150537634409</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.546831955922865</v>
+        <v>0.5452196382428941</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.611764705882353</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.5251396648044693</v>
+        <v>0.526595744680851</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.5457097032878909</v>
+        <v>0.5431681681681682</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.6351351351351351</v>
+        <v>0.6380368098159509</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.5225903614457831</v>
+        <v>0.5228571428571429</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.5857966834895458</v>
+        <v>0.582995951417004</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.6771428571428572</v>
+        <v>0.6763157894736842</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.5839598997493735</v>
+        <v>0.5835322195704057</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4178027265437049</v>
+        <v>0.4189189189189189</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01151631477927063</v>
+        <v>0.01075268817204301</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0743801652892562</v>
+        <v>0.07235142118863049</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.1019736842105263</v>
+        <v>0.1041009463722398</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.06007067137809187</v>
+        <v>0.05519480519480519</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.04316546762589928</v>
+        <v>0.04026845637583892</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01355013550135501</v>
+        <v>0.01259445843828715</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.5635359116022099</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.16</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.6463414634146342</v>
+        <v>0.6430594900849859</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.3179012345679013</v>
+        <v>0.3227665706051873</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.7042682926829268</v>
+        <v>0.7065527065527065</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.3107692307692307</v>
+        <v>0.3132183908045977</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.6753048780487805</v>
+        <v>0.6747159090909091</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.3143297380585516</v>
+        <v>0.3179856115107914</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.4123711340206185</v>
+        <v>0.4095238095238095</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.3098591549295774</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.2235294117647059</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.348936170212766</v>
+        <v>0.3543307086614173</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.2111111111111111</v>
+        <v>0.2021276595744681</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.5338345864661654</v>
+        <v>0.5374149659863946</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.7099236641221374</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.75</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6967213114754098</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.7244897959183674</v>
+        <v>0.7289719626168224</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.03045685279187817</v>
+        <v>0.03149606299212598</v>
       </c>
       <c r="FQ16" t="n">
-        <v>96.17595307917888</v>
+        <v>95.93424657534247</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.53125</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="FS16" t="n">
-        <v>15.00353200883002</v>
+        <v>15.04521019986216</v>
       </c>
       <c r="FT16" t="n">
-        <v>14.94192139737991</v>
+        <v>14.97573278800273</v>
       </c>
       <c r="FU16" t="n">
-        <v>14.3392200147167</v>
+        <v>14.35506547208821</v>
       </c>
       <c r="FV16" t="n">
-        <v>14.29759825327511</v>
+        <v>14.34219495569189</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.243785084202085</v>
+        <v>0.237987987987988</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.6743421052631579</v>
+        <v>0.6624605678233438</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.7509157509157509</v>
+        <v>0.7394366197183099</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.551219512195122</v>
+        <v>0.5523809523809524</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.2269446672012831</v>
+        <v>0.2312312312312312</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.4911660777385159</v>
+        <v>0.4935064935064935</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.5225563909774437</v>
+        <v>0.5223367697594502</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.5035971223021583</v>
+        <v>0.5</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.111467522052927</v>
+        <v>0.1118618618618619</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.381294964028777</v>
+        <v>0.4026845637583892</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.3984962406015037</v>
+        <v>0.4195804195804196</v>
       </c>
       <c r="GH16" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="GI16" t="n">
-        <v>0.1218925421010425</v>
+        <v>0.1208708708708709</v>
       </c>
       <c r="GJ16" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.3975155279503105</v>
       </c>
       <c r="GK16" t="n">
-        <v>0.3973509933774834</v>
+        <v>0.4</v>
       </c>
       <c r="GL16" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.96875</v>
       </c>
       <c r="GM16" t="n">
-        <v>0.2959101844426624</v>
+        <v>0.2980480480480481</v>
       </c>
       <c r="GN16" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.345088161209068</v>
       </c>
       <c r="GO16" t="n">
-        <v>0.3543956043956044</v>
+        <v>0.3494897959183674</v>
       </c>
       <c r="GP16" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8613138686131386</v>
       </c>
       <c r="GQ16" t="n">
-        <v>0.3716216216216216</v>
+        <v>0.3619631901840491</v>
       </c>
       <c r="GR16" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="GS16" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="GT16" t="n">
-        <v>0.06081081081081081</v>
+        <v>0.06134969325153374</v>
       </c>
       <c r="GU16" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="GV16" t="n">
         <v>1</v>
       </c>
       <c r="GW16" t="n">
-        <v>0.3648648648648649</v>
+        <v>0.3803680981595092</v>
       </c>
       <c r="GX16" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="GY16" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="GZ16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="HA16" t="n">
-        <v>0.6506024096385542</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="HB16" t="n">
-        <v>0.1265060240963855</v>
+        <v>0.12</v>
       </c>
       <c r="HC16" t="n">
         <v>0.3571428571428572</v>
       </c>
       <c r="HD16" t="n">
-        <v>0.3343373493975904</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="HE16" t="n">
-        <v>0.3423423423423423</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="HF16" t="n">
-        <v>0.6615878107457899</v>
+        <v>0.6569069069069069</v>
       </c>
       <c r="HG16" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.345088161209068</v>
       </c>
       <c r="HH16" t="n">
-        <v>0.53899231078905</v>
+        <v>0.5372925660377358</v>
       </c>
       <c r="HI16" t="n">
-        <v>0.5462673913043478</v>
+        <v>0.5465691176470588</v>
       </c>
       <c r="HJ16" t="n">
-        <v>0.5353156534954407</v>
+        <v>0.5315336231884058</v>
       </c>
       <c r="HK16" t="n">
-        <v>0.09016393442622951</v>
+        <v>0.09059233449477352</v>
       </c>
       <c r="HL16" t="n">
-        <v>0.1416361416361416</v>
+        <v>0.1418764302059496</v>
       </c>
       <c r="HM16" t="n">
-        <v>0.009560229445506692</v>
+        <v>0.0106951871657754</v>
       </c>
       <c r="HN16" t="n">
-        <v>0.145398773006135</v>
+        <v>0.1482977495672245</v>
       </c>
       <c r="HO16" t="n">
-        <v>0.2877300613496933</v>
+        <v>0.2839007501442585</v>
       </c>
       <c r="HP16" t="n">
-        <v>7.537741046831956</v>
+        <v>7.60826873385013</v>
       </c>
       <c r="HQ16" t="n">
-        <v>25.29282945736434</v>
+        <v>25.28784029038113</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.2803532008830022</v>
+        <v>0.275671950379049</v>
       </c>
       <c r="HS16" t="inlineStr"/>
       <c r="HT16" t="inlineStr"/>
       <c r="HU16" t="n">
-        <v>0.006578947368421052</v>
+        <v>0.006211180124223602</v>
       </c>
     </row>
     <row r="17">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -4377,85 +4377,85 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>40620</v>
+        <v>43500</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="J6" t="n">
-        <v>1343</v>
+        <v>1442</v>
       </c>
       <c r="K6" t="n">
-        <v>1358</v>
+        <v>1458</v>
       </c>
       <c r="L6" t="n">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="M6" t="n">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="N6" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="O6" t="n">
-        <v>2701</v>
+        <v>2900</v>
       </c>
       <c r="P6" t="n">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="Q6" t="n">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="R6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="S6" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="T6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U6" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="V6" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="W6" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Y6" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="Z6" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="AA6" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AF6" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AG6" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
@@ -4467,175 +4467,175 @@
         <v>41</v>
       </c>
       <c r="AK6" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AL6" t="n">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="AM6" t="n">
-        <v>725</v>
+        <v>783</v>
       </c>
       <c r="AN6" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AO6" t="n">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="AP6" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1679</v>
+        <v>1784</v>
       </c>
       <c r="AR6" t="n">
-        <v>1408</v>
+        <v>1503</v>
       </c>
       <c r="AS6" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="AT6" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AU6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AV6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="AY6" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="AZ6" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="BA6" t="n">
+        <v>58</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>141</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>150</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>548</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>462</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>446</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>489</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>96</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>356</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>131</v>
+      </c>
+      <c r="BL6" t="n">
         <v>56</v>
       </c>
-      <c r="BB6" t="n">
-        <v>132</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>140</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>518</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>442</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>410</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>459</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>93</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>332</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>128</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>54</v>
-      </c>
       <c r="BM6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN6" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="BO6" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="BP6" t="n">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="BQ6" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="BR6" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="BS6" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="BT6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="BU6" t="n">
         <v>10</v>
       </c>
       <c r="BV6" t="n">
-        <v>901</v>
+        <v>951</v>
       </c>
       <c r="BW6" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="BX6" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="BY6" t="n">
         <v>9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="CA6" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="CB6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="CC6" t="n">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="CD6" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="CE6" t="n">
-        <v>716</v>
+        <v>775</v>
       </c>
       <c r="CF6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CG6" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="CH6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="CI6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CJ6" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="CK6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CL6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="CM6" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="CN6" t="n">
         <v>10</v>
       </c>
       <c r="CO6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CP6" t="n">
         <v>6</v>
@@ -4644,62 +4644,62 @@
         <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="CS6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CT6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="CU6" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="CV6" t="n">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CY6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CZ6" t="n">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="DA6" t="n">
         <v>4</v>
       </c>
       <c r="DB6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="DC6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="DD6" t="n">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="DE6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="DF6" t="inlineStr"/>
       <c r="DG6" t="n">
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="DI6" t="n">
         <v>5</v>
       </c>
       <c r="DJ6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="DK6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,266 +4708,266 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="DQ6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="DR6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DS6" t="n">
         <v>6</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1431</v>
+        <v>1513</v>
       </c>
       <c r="DV6" t="n">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="DW6" t="n">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="DX6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DY6" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5187793427230047</v>
+        <v>0.5088105726872246</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5566265060240964</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8315217391304348</v>
+        <v>0.8358974358974359</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3948497854077253</v>
+        <v>0.3876739562624255</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.4113475177304964</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3948497854077253</v>
+        <v>0.3876739562624255</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5875862068965517</v>
+        <v>0.5798212005108557</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6074766355140186</v>
+        <v>0.6101694915254238</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5440414507772021</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5894206549118388</v>
+        <v>0.5804821150855366</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.710691823899371</v>
+        <v>0.7151162790697675</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5815384615384616</v>
+        <v>0.5784883720930233</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6163475699558174</v>
+        <v>0.608829568788501</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.7045454545454546</v>
+        <v>0.7131578947368421</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6201923076923077</v>
+        <v>0.621867881548975</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3912678421494543</v>
+        <v>0.3911353032659409</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.008583690987124463</v>
+        <v>0.01192842942345924</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07448275862068965</v>
+        <v>0.07151979565772669</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.08958837772397095</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.06639004149377593</v>
+        <v>0.06177606177606178</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.009036144578313253</v>
+        <v>0.01404494382022472</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.531578947368421</v>
+        <v>0.5276381909547738</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9347826086956522</v>
+        <v>0.9387755102040817</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1956521739130435</v>
+        <v>0.1914893617021277</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7048611111111112</v>
+        <v>0.7028753993610224</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.391156462585034</v>
+        <v>0.3734567901234568</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.7549295774647887</v>
+        <v>0.7538860103626943</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2836363636363636</v>
+        <v>0.292358803986711</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7325038880248833</v>
+        <v>0.7310443490701002</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3391915641476274</v>
+        <v>0.3344</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4427480916030535</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.3481481481481482</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.35</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2525252525252525</v>
+        <v>0.273972602739726</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.6407766990291263</v>
+        <v>0.6396396396396397</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.7518248175182481</v>
+        <v>0.7450980392156863</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7620817843866171</v>
+        <v>0.7602739726027398</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.7325581395348837</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.05088062622309197</v>
+        <v>0.0497335701598579</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.75184638109306</v>
+        <v>96</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.81757259865972</v>
+        <v>15.83439667128988</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.26877761413844</v>
+        <v>14.17475994513032</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.13291139240506</v>
+        <v>15.16699029126213</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.72584683357879</v>
+        <v>13.63065843621399</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.346767422334173</v>
+        <v>0.343701399688958</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6828087167070218</v>
+        <v>0.6809954751131222</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.75</v>
+        <v>0.7468982630272953</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5647840531561462</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2023509655751469</v>
+        <v>0.2013996889580093</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4730290456431535</v>
+        <v>0.4633204633204633</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.5066666666666667</v>
+        <v>0.4938271604938271</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4298245614035088</v>
+        <v>0.425</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.05961376994122586</v>
+        <v>0.06376360808709176</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.4225352112676056</v>
+        <v>0.4024390243902439</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1125104953820319</v>
+        <v>0.1143079315707621</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.417910447761194</v>
+        <v>0.4353741496598639</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.953125</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2787573467674223</v>
+        <v>0.2768273716951788</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3855421686746988</v>
+        <v>0.3679775280898877</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3890577507598784</v>
+        <v>0.3732193732193732</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7734375</v>
+        <v>0.7786259541984732</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4591194968553459</v>
+        <v>0.4825581395348837</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6575342465753424</v>
+        <v>0.6506024096385542</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.1875</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.0880503144654088</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2389937106918239</v>
+        <v>0.2209302325581395</v>
       </c>
       <c r="GX6" t="n">
         <v>0.6578947368421053</v>
@@ -4976,68 +4976,68 @@
         <v>0.8</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.32</v>
+        <v>0.3168604651162791</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6442307692307693</v>
+        <v>0.6513761467889908</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.08923076923076922</v>
+        <v>0.09011627906976744</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3169230769230769</v>
+        <v>0.3197674418604651</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3980582524271845</v>
+        <v>0.3727272727272727</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7380352644836272</v>
+        <v>0.7348367029548989</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3855421686746988</v>
+        <v>0.3679775280898877</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5687484797297298</v>
+        <v>0.5656515649452269</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5550714285714285</v>
+        <v>0.5566676470588235</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5447915094339623</v>
+        <v>0.5449288690476191</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.09861325115562404</v>
+        <v>0.09663564781675017</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1487303506650544</v>
+        <v>0.1462317210348706</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.01061571125265393</v>
+        <v>0.00984251968503937</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1477069684335914</v>
+        <v>0.1519058295964126</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3085169743895176</v>
+        <v>0.3071748878923767</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.410620689655172</v>
+        <v>5.498084291187739</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.27630434782609</v>
+        <v>25.28588709677419</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.2993298585256888</v>
+        <v>0.2940360610263523</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.006802721088435374</v>
       </c>
     </row>
     <row r="7">
@@ -7135,311 +7135,311 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>52440</v>
+        <v>55320</v>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="J10" t="n">
-        <v>1783</v>
+        <v>1882</v>
       </c>
       <c r="K10" t="n">
-        <v>1798</v>
+        <v>1898</v>
       </c>
       <c r="L10" t="n">
-        <v>613</v>
+        <v>664</v>
       </c>
       <c r="M10" t="n">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="N10" t="n">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="O10" t="n">
-        <v>3581</v>
+        <v>3780</v>
       </c>
       <c r="P10" t="n">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="Q10" t="n">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="R10" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="T10" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="U10" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="V10" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="W10" t="n">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="X10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Z10" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AA10" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AF10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AG10" t="n">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="AH10" t="n">
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AJ10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AK10" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="AM10" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="AN10" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="AO10" t="n">
-        <v>640</v>
+        <v>683</v>
       </c>
       <c r="AP10" t="n">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2075</v>
+        <v>2170</v>
       </c>
       <c r="AR10" t="n">
-        <v>1890</v>
+        <v>1995</v>
       </c>
       <c r="AS10" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AT10" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AW10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AX10" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="AY10" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="AZ10" t="n">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="BA10" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="BB10" t="n">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="BC10" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="BD10" t="n">
-        <v>675</v>
+        <v>728</v>
       </c>
       <c r="BE10" t="n">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="BF10" t="n">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="BG10" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="BH10" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BI10" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="BJ10" t="n">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="BK10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="BL10" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="BM10" t="n">
         <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="BO10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BP10" t="n">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="BQ10" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="BR10" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="BS10" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="BT10" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="BU10" t="n">
         <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>1114</v>
+        <v>1156</v>
       </c>
       <c r="BW10" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="BX10" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="BY10" t="n">
         <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="CA10" t="n">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="CB10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CC10" t="n">
-        <v>695</v>
+        <v>736</v>
       </c>
       <c r="CD10" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="CE10" t="n">
-        <v>956</v>
+        <v>1013</v>
       </c>
       <c r="CF10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CG10" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="CH10" t="n">
+        <v>88</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>73</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>155</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>25</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>70</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>131</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>19</v>
+      </c>
+      <c r="CO10" t="n">
         <v>85</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>72</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>147</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>66</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>126</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>18</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>81</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CR10" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="CS10" t="n">
         <v>29</v>
       </c>
       <c r="CT10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="CU10" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="CV10" t="n">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="CW10" t="n">
         <v>12</v>
       </c>
       <c r="CX10" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="CY10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CZ10" t="n">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="DC10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DD10" t="n">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="DE10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
@@ -7448,25 +7448,25 @@
         <v>6</v>
       </c>
       <c r="DH10" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="DI10" t="n">
         <v>7</v>
       </c>
       <c r="DJ10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="DK10" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="DL10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="DM10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="DN10" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
@@ -7475,322 +7475,322 @@
         <v>35</v>
       </c>
       <c r="DQ10" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="DR10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="DS10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DT10" t="n">
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1797</v>
+        <v>1878</v>
       </c>
       <c r="DV10" t="n">
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="DW10" t="n">
-        <v>612</v>
+        <v>663</v>
       </c>
       <c r="DX10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="DY10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.484</v>
+        <v>0.4760076775431862</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5426008968609866</v>
+        <v>0.5356371490280778</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.9053497942386831</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3625</v>
+        <v>0.3557833089311859</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3934426229508197</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3351063829787234</v>
+        <v>0.3380952380952381</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3625</v>
+        <v>0.3557833089311859</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5399568034557235</v>
+        <v>0.5360082304526749</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5390070921985816</v>
+        <v>0.5436241610738255</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4813664596273292</v>
+        <v>0.4811594202898551</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.541507024265645</v>
+        <v>0.5350453172205438</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5685279187817259</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4892156862745098</v>
+        <v>0.490990990990991</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5834272829763247</v>
+        <v>0.5773333333333334</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6150442477876106</v>
+        <v>0.6033057851239669</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5497553017944535</v>
+        <v>0.548265460030166</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4086845466155811</v>
+        <v>0.4126888217522658</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.009375</v>
+        <v>0.008784773060029283</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0755939524838013</v>
+        <v>0.07613168724279835</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09197651663405088</v>
+        <v>0.0898876404494382</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06885245901639345</v>
+        <v>0.0736196319018405</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01818181818181818</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.006726457399103139</v>
+        <v>0.00631578947368421</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.541958041958042</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.09302325581395349</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6621880998080614</v>
+        <v>0.6696914700544465</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3419811320754717</v>
+        <v>0.3407572383073497</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.731764705882353</v>
+        <v>0.7250554323725056</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2793017456359102</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.693446088794926</v>
+        <v>0.6946107784431138</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3115151515151515</v>
+        <v>0.3098751418842225</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4134078212290503</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3058823529411765</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2533333333333334</v>
+        <v>0.25</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2862453531598513</v>
+        <v>0.2842465753424658</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2651515151515151</v>
+        <v>0.2642857142857143</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6039603960396039</v>
+        <v>0.6132075471698113</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6768558951965066</v>
+        <v>0.6763485477178424</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7755102040816326</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.7009345794392523</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.776</v>
+        <v>0.7846153846153846</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.048</v>
+        <v>0.04738154613466334</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.33409610983982</v>
+        <v>98.39479392624729</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5343511450381679</v>
+        <v>0.5259259259259259</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.4019068984857</v>
+        <v>14.32964930924548</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.88398220244716</v>
+        <v>14.93761854583772</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.81278743690409</v>
+        <v>13.74176408076514</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.1178531701891</v>
+        <v>14.18925184404636</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.326309067688378</v>
+        <v>0.3226586102719033</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6477495107632094</v>
+        <v>0.6479400749063671</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7133620689655172</v>
+        <v>0.7119341563786008</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5075528700906344</v>
+        <v>0.4971098265895953</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1947637292464879</v>
+        <v>0.1969788519637462</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4393442622950819</v>
+        <v>0.4263803680981595</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4718309859154929</v>
+        <v>0.4602649006622517</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4552238805970149</v>
+        <v>0.4532374100719425</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07024265644955301</v>
+        <v>0.06767371601208459</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3240740740740741</v>
+        <v>0.3272727272727273</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.123882503192848</v>
+        <v>0.1256797583081571</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3195876288659794</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3246073298429319</v>
+        <v>0.3317073170731707</v>
       </c>
       <c r="GL10" t="n">
         <v>1</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2848020434227331</v>
+        <v>0.2870090634441088</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3811659192825112</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3837471783295711</v>
+        <v>0.3707627118644068</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8685714285714285</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5076142131979695</v>
+        <v>0.5047619047619047</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.58</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.103448275862069</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06598984771573604</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2182741116751269</v>
+        <v>0.2238095238095238</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.3829787234042553</v>
       </c>
       <c r="GY10" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3294117647058823</v>
+        <v>0.3207207207207207</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5654761904761905</v>
+        <v>0.5786516853932584</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1058823529411765</v>
+        <v>0.1135135135135135</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3492063492063492</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2627450980392157</v>
+        <v>0.2648648648648649</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3507462686567164</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7349936143039592</v>
+        <v>0.7353474320241692</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3811659192825112</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5645959615384615</v>
+        <v>0.5634677986658582</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.54584609375</v>
+        <v>0.5495533333333333</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5514178217821782</v>
+        <v>0.5507059090909091</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1160766105629716</v>
+        <v>0.1158704008786381</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1805555555555556</v>
+        <v>0.1814977973568282</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.007776049766718507</v>
+        <v>0.007288629737609329</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1339759036144578</v>
+        <v>0.1345622119815668</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3253012048192771</v>
+        <v>0.335483870967742</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.706371490280778</v>
+        <v>5.706995884773662</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.25581761006289</v>
+        <v>25.2678939617084</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3438025799214807</v>
+        <v>0.3528161530286929</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.0154639175257732</v>
+        <v>0.01442307692307692</v>
       </c>
     </row>
     <row r="11">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -4377,67 +4377,67 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>43500</v>
+        <v>46380</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" t="n">
-        <v>1442</v>
+        <v>1539</v>
       </c>
       <c r="K6" t="n">
-        <v>1458</v>
+        <v>1555</v>
       </c>
       <c r="L6" t="n">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="M6" t="n">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="N6" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="O6" t="n">
-        <v>2900</v>
+        <v>3094</v>
       </c>
       <c r="P6" t="n">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="Q6" t="n">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="R6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="S6" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="T6" t="n">
+        <v>73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>111</v>
+      </c>
+      <c r="V6" t="n">
+        <v>127</v>
+      </c>
+      <c r="W6" t="n">
+        <v>277</v>
+      </c>
+      <c r="X6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z6" t="n">
         <v>71</v>
       </c>
-      <c r="U6" t="n">
-        <v>109</v>
-      </c>
-      <c r="V6" t="n">
-        <v>120</v>
-      </c>
-      <c r="W6" t="n">
-        <v>259</v>
-      </c>
-      <c r="X6" t="n">
-        <v>33</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>64</v>
-      </c>
       <c r="AA6" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="AB6" t="n">
         <v>9</v>
@@ -4446,241 +4446,241 @@
         <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AG6" t="n">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
         <v>41</v>
       </c>
       <c r="AK6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL6" t="n">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="AM6" t="n">
-        <v>783</v>
+        <v>834</v>
       </c>
       <c r="AN6" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="AO6" t="n">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="AP6" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1784</v>
+        <v>1889</v>
       </c>
       <c r="AR6" t="n">
-        <v>1503</v>
+        <v>1607</v>
       </c>
       <c r="AS6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AT6" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="AU6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AV6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AW6" t="n">
         <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="AY6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AZ6" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="BA6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BB6" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BC6" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="BD6" t="n">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="BE6" t="n">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="BF6" t="n">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="BG6" t="n">
-        <v>489</v>
+        <v>531</v>
       </c>
       <c r="BH6" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BI6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="BJ6" t="n">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="BK6" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="BL6" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="BM6" t="n">
         <v>6</v>
       </c>
       <c r="BN6" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="BO6" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="BP6" t="n">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="BQ6" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="BR6" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="BS6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BT6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="BU6" t="n">
         <v>10</v>
       </c>
       <c r="BV6" t="n">
-        <v>951</v>
+        <v>1023</v>
       </c>
       <c r="BW6" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="BX6" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="BY6" t="n">
         <v>9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="CA6" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="CB6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CC6" t="n">
-        <v>557</v>
+        <v>592</v>
       </c>
       <c r="CD6" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="CE6" t="n">
-        <v>775</v>
+        <v>827</v>
       </c>
       <c r="CF6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="CG6" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="CH6" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="CI6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CJ6" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="CK6" t="n">
         <v>25</v>
       </c>
       <c r="CL6" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="CM6" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="CN6" t="n">
         <v>10</v>
       </c>
       <c r="CO6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="CP6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CQ6" t="n">
         <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="CS6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CT6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="CU6" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="CV6" t="n">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CY6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CZ6" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="DA6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DB6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DC6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="DD6" t="n">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="DE6" t="n">
         <v>24</v>
@@ -4690,16 +4690,16 @@
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="DI6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DJ6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="DK6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,257 +4708,257 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="DQ6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="DR6" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="DS6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1513</v>
+        <v>1604</v>
       </c>
       <c r="DV6" t="n">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="DW6" t="n">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="DX6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DY6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5088105726872246</v>
+        <v>0.5168067226890757</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5566265060240964</v>
+        <v>0.5642201834862385</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8358974358974359</v>
+        <v>0.8428571428571429</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3876739562624255</v>
+        <v>0.388170055452865</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4113475177304964</v>
+        <v>0.4125874125874126</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3876739562624255</v>
+        <v>0.388170055452865</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5798212005108557</v>
+        <v>0.5707434052757794</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6101694915254238</v>
+        <v>0.608</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.5450236966824644</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5804821150855366</v>
+        <v>0.5752727272727273</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.7151162790697675</v>
+        <v>0.7103825136612022</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5784883720930233</v>
+        <v>0.5748587570621468</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.608829568788501</v>
+        <v>0.6042334830019244</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.7131578947368421</v>
+        <v>0.7089552238805971</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.621867881548975</v>
+        <v>0.6169977924944813</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3911353032659409</v>
+        <v>0.3934545454545454</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01192842942345924</v>
+        <v>0.011090573012939</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07151979565772669</v>
+        <v>0.07553956834532374</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.09207708779443255</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.06177606177606178</v>
+        <v>0.06859205776173286</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01219512195121951</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.01404494382022472</v>
+        <v>0.01319261213720317</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5276381909547738</v>
+        <v>0.5233644859813084</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1914893617021277</v>
+        <v>0.18</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7028753993610224</v>
+        <v>0.7155688622754491</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.3734567901234568</v>
+        <v>0.3739376770538244</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.7538860103626943</v>
+        <v>0.754950495049505</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.292358803986711</v>
+        <v>0.2901234567901235</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7310443490701002</v>
+        <v>0.7371273712737128</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3344</v>
+        <v>0.3338257016248153</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.425531914893617</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.3481481481481482</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2909090909090909</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.273972602739726</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.75625</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7602739726027398</v>
+        <v>0.760655737704918</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.7373737373737373</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0497335701598579</v>
+        <v>0.05098684210526316</v>
       </c>
       <c r="FQ6" t="n">
-        <v>96</v>
+        <v>96.0620957309185</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.83439667128988</v>
+        <v>15.8638726445744</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.17475994513032</v>
+        <v>14.12572347266881</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.16699029126213</v>
+        <v>15.19928525016244</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.63065843621399</v>
+        <v>13.59627009646302</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.343701399688958</v>
+        <v>0.3396363636363636</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6809954751131222</v>
+        <v>0.6745182012847966</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.7468982630272953</v>
+        <v>0.7429245283018868</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5647840531561462</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2013996889580093</v>
+        <v>0.2014545454545454</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4633204633204633</v>
+        <v>0.4584837545126354</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.4938271604938271</v>
+        <v>0.4922480620155039</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.425</v>
+        <v>0.4409448818897638</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.06376360808709176</v>
+        <v>0.06545454545454546</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.4024390243902439</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.3820224719101123</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1143079315707621</v>
+        <v>0.1178181818181818</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.4353741496598639</v>
+        <v>0.4382716049382716</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4409937888198758</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.953125</v>
+        <v>0.9577464788732394</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2768273716951788</v>
+        <v>0.2756363636363636</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3679775280898877</v>
+        <v>0.366754617414248</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3732193732193732</v>
+        <v>0.3716577540106952</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7786259541984732</v>
+        <v>0.7841726618705036</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4825581395348837</v>
+        <v>0.4808743169398907</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6506024096385542</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.2241379310344828</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.09302325581395349</v>
+        <v>0.08743169398907104</v>
       </c>
       <c r="GU6" t="n">
         <v>0.5625</v>
@@ -4967,77 +4967,77 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2209302325581395</v>
+        <v>0.2295081967213115</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.8</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3168604651162791</v>
+        <v>0.3135593220338983</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6513761467889908</v>
+        <v>0.6576576576576577</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.09011627906976744</v>
+        <v>0.0903954802259887</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5625</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3197674418604651</v>
+        <v>0.3135593220338983</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3727272727272727</v>
+        <v>0.3693693693693694</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7348367029548989</v>
+        <v>0.7330909090909091</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3679775280898877</v>
+        <v>0.366754617414248</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5656515649452269</v>
+        <v>0.5646588514996342</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5566676470588235</v>
+        <v>0.5625044</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5449288690476191</v>
+        <v>0.5438562138728323</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.09663564781675017</v>
+        <v>0.09389671361502347</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1462317210348706</v>
+        <v>0.1401273885350318</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.00984251968503937</v>
+        <v>0.01457194899817851</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1519058295964126</v>
+        <v>0.1508734780307041</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3071748878923767</v>
+        <v>0.2969825304393859</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.498084291187739</v>
+        <v>5.573860911270984</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.28588709677419</v>
+        <v>25.24925093632959</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.2940360610263523</v>
+        <v>0.2846003898635477</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.006802721088435374</v>
+        <v>0.006172839506172839</v>
       </c>
     </row>
     <row r="7">
@@ -7135,67 +7135,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>55320</v>
+        <v>58200</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J10" t="n">
-        <v>1882</v>
+        <v>1978</v>
       </c>
       <c r="K10" t="n">
-        <v>1898</v>
+        <v>1996</v>
       </c>
       <c r="L10" t="n">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="M10" t="n">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="N10" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O10" t="n">
-        <v>3780</v>
+        <v>3974</v>
       </c>
       <c r="P10" t="n">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="Q10" t="n">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="R10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S10" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T10" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="U10" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="V10" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="W10" t="n">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y10" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Z10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AA10" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
@@ -7207,193 +7207,193 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AG10" t="n">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AK10" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AL10" t="n">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="AM10" t="n">
-        <v>972</v>
+        <v>1021</v>
       </c>
       <c r="AN10" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="AO10" t="n">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="AP10" t="n">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2170</v>
+        <v>2274</v>
       </c>
       <c r="AR10" t="n">
-        <v>1995</v>
+        <v>2100</v>
       </c>
       <c r="AS10" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AT10" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV10" t="n">
+        <v>62</v>
+      </c>
+      <c r="AW10" t="n">
         <v>61</v>
       </c>
-      <c r="AW10" t="n">
-        <v>58</v>
-      </c>
       <c r="AX10" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="AY10" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AZ10" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="BA10" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BB10" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="BC10" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="BD10" t="n">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="BE10" t="n">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="BF10" t="n">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="BG10" t="n">
-        <v>660</v>
+        <v>684</v>
       </c>
       <c r="BH10" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="BI10" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="BJ10" t="n">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="BK10" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="BL10" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="BM10" t="n">
         <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="BO10" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="BP10" t="n">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="BQ10" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="BR10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BS10" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="BT10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BV10" t="n">
-        <v>1156</v>
+        <v>1208</v>
       </c>
       <c r="BW10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="BX10" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BY10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="CA10" t="n">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="CB10" t="n">
+        <v>43</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>774</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>284</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1058</v>
+      </c>
+      <c r="CF10" t="n">
         <v>40</v>
       </c>
-      <c r="CC10" t="n">
-        <v>736</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>277</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>1013</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>38</v>
-      </c>
       <c r="CG10" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="CH10" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="CI10" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="CJ10" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="CK10" t="n">
         <v>25</v>
       </c>
       <c r="CL10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="CM10" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="CN10" t="n">
         <v>19</v>
       </c>
       <c r="CO10" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="CP10" t="n">
         <v>2</v>
@@ -7402,62 +7402,62 @@
         <v>11</v>
       </c>
       <c r="CR10" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="CS10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CT10" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="CU10" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="CV10" t="n">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="CW10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CX10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CY10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CZ10" t="n">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="DC10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DD10" t="n">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="DE10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DH10" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="DI10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DJ10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="DK10" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="DL10" t="n">
         <v>12</v>
@@ -7466,19 +7466,19 @@
         <v>8</v>
       </c>
       <c r="DN10" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="DQ10" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="DR10" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="DS10" t="n">
         <v>7</v>
@@ -7487,238 +7487,238 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1878</v>
+        <v>1972</v>
       </c>
       <c r="DV10" t="n">
-        <v>726</v>
+        <v>771</v>
       </c>
       <c r="DW10" t="n">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="DX10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="DY10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4760076775431862</v>
+        <v>0.4789762340036563</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5356371490280778</v>
+        <v>0.5379876796714579</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9053497942386831</v>
+        <v>0.8976377952755905</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3557833089311859</v>
+        <v>0.3562412342215989</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.3934426229508197</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3380952380952381</v>
+        <v>0.3378378378378378</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3557833089311859</v>
+        <v>0.3562412342215989</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5360082304526749</v>
+        <v>0.5357492654260528</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5436241610738255</v>
+        <v>0.5424836601307189</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4811594202898551</v>
+        <v>0.4904109589041096</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5350453172205438</v>
+        <v>0.5351787773933102</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5571428571428572</v>
+        <v>0.5604651162790698</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.490990990990991</v>
+        <v>0.4965928449744463</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5773333333333334</v>
+        <v>0.5770992366412214</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.6068548387096774</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.548265460030166</v>
+        <v>0.5522174535050072</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4126888217522658</v>
+        <v>0.4111880046136102</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.008784773060029283</v>
+        <v>0.008415147265077139</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07613168724279835</v>
+        <v>0.07835455435847209</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0898876404494382</v>
+        <v>0.09187279151943463</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0736196319018405</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.0170940170940171</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.00631578947368421</v>
+        <v>0.006024096385542169</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.541958041958042</v>
+        <v>0.5496688741721855</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6696914700544465</v>
+        <v>0.6672413793103448</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3407572383073497</v>
+        <v>0.3297872340425532</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7250554323725056</v>
+        <v>0.7257383966244726</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2755555555555556</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6946107784431138</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3098751418842225</v>
+        <v>0.3032608695652174</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3969849246231156</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.2953367875647668</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.25</v>
+        <v>0.2435897435897436</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2842465753424658</v>
+        <v>0.2819672131147541</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2642857142857143</v>
+        <v>0.2620689655172414</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6132075471698113</v>
+        <v>0.6143497757847534</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6763485477178424</v>
+        <v>0.6706349206349206</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7755102040816326</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7009345794392523</v>
+        <v>0.7053571428571429</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7846153846153846</v>
+        <v>0.7753623188405797</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04738154613466334</v>
+        <v>0.04790419161676647</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.39479392624729</v>
+        <v>98.32577319587629</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5259259259259259</v>
+        <v>0.5211267605633803</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.32964930924548</v>
+        <v>14.29074823053589</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.93761854583772</v>
+        <v>14.99644288577154</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.74176408076514</v>
+        <v>13.71622851365015</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.18925184404636</v>
+        <v>14.25455911823647</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3226586102719033</v>
+        <v>0.3264129181084198</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6479400749063671</v>
+        <v>0.6466431095406361</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7119341563786008</v>
+        <v>0.7120622568093385</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.4971098265895953</v>
+        <v>0.5027322404371585</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1969788519637462</v>
+        <v>0.1949250288350634</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4263803680981595</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4602649006622517</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4532374100719425</v>
+        <v>0.4475524475524476</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06767371601208459</v>
+        <v>0.06747404844290658</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3247863247863248</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3272727272727273</v>
+        <v>0.3304347826086956</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1256797583081571</v>
+        <v>0.1239907727797001</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3317073170731707</v>
+        <v>0.330188679245283</v>
       </c>
       <c r="GL10" t="n">
-        <v>1</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2870090634441088</v>
+        <v>0.28719723183391</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3694779116465863</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3707627118644068</v>
+        <v>0.3717171717171717</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8685714285714285</v>
+        <v>0.8641304347826086</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5047619047619047</v>
+        <v>0.5069767441860465</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5943396226415094</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06511627906976744</v>
       </c>
       <c r="GU10" t="n">
         <v>0.4285714285714285</v>
@@ -7727,70 +7727,70 @@
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2238095238095238</v>
+        <v>0.2232558139534884</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.3829787234042553</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3207207207207207</v>
+        <v>0.3253833049403748</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5786516853932584</v>
+        <v>0.5916230366492147</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1135135135135135</v>
+        <v>0.110732538330494</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3492063492063492</v>
+        <v>0.3384615384615385</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2648648648648649</v>
+        <v>0.2674616695059625</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3375796178343949</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7353474320241692</v>
+        <v>0.73760092272203</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3694779116465863</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5634677986658582</v>
+        <v>0.5642493051534453</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5495533333333333</v>
+        <v>0.5503383211678832</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5507059090909091</v>
+        <v>0.551470395869191</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1158704008786381</v>
+        <v>0.1173389209009953</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1814977973568282</v>
+        <v>0.1827326068734283</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.007288629737609329</v>
+        <v>0.008379888268156424</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1345622119815668</v>
+        <v>0.1328056288478452</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.335483870967742</v>
+        <v>0.3399296394019349</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.706995884773662</v>
+        <v>5.654260528893242</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.2678939617084</v>
+        <v>25.25353107344633</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3528161530286929</v>
+        <v>0.3564206268958544</v>
       </c>
       <c r="HS10" t="n">
         <v>4</v>
@@ -7799,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01442307692307692</v>
+        <v>0.01395348837209302</v>
       </c>
     </row>
     <row r="11">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -4377,265 +4377,265 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>46380</v>
+        <v>49260</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="J6" t="n">
-        <v>1539</v>
+        <v>1630</v>
       </c>
       <c r="K6" t="n">
-        <v>1555</v>
+        <v>1649</v>
       </c>
       <c r="L6" t="n">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="M6" t="n">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="N6" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="O6" t="n">
-        <v>3094</v>
+        <v>3279</v>
       </c>
       <c r="P6" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="Q6" t="n">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="S6" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="T6" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="V6" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="W6" t="n">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="X6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y6" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Z6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AA6" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="AB6" t="n">
         <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AG6" t="n">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AJ6" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="AL6" t="n">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="AM6" t="n">
-        <v>834</v>
+        <v>885</v>
       </c>
       <c r="AN6" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="AO6" t="n">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="AP6" t="n">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1889</v>
+        <v>2000</v>
       </c>
       <c r="AR6" t="n">
-        <v>1607</v>
+        <v>1722</v>
       </c>
       <c r="AS6" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AT6" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="AU6" t="n">
         <v>36</v>
       </c>
       <c r="AV6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AW6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX6" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AY6" t="n">
+        <v>123</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>227</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>67</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>153</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>160</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>607</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>506</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>564</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>105</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>399</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>147</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>68</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>253</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>188</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>441</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>115</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>211</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>59</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>143</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>154</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>561</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>492</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>460</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>531</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>99</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>379</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>139</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>63</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>246</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>177</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>423</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>109</v>
-      </c>
       <c r="BR6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="BS6" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="BT6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BU6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BV6" t="n">
-        <v>1023</v>
+        <v>1070</v>
       </c>
       <c r="BW6" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="BX6" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="BY6" t="n">
         <v>9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="CA6" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="CB6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CC6" t="n">
-        <v>592</v>
+        <v>628</v>
       </c>
       <c r="CD6" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="CE6" t="n">
-        <v>827</v>
+        <v>881</v>
       </c>
       <c r="CF6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CG6" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="CH6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="CJ6" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="CK6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CL6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="CM6" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="CN6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CO6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="CP6" t="n">
         <v>8</v>
@@ -4644,62 +4644,62 @@
         <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="CS6" t="n">
         <v>25</v>
       </c>
       <c r="CT6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="CU6" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="CV6" t="n">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="CY6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CZ6" t="n">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="DA6" t="n">
         <v>5</v>
       </c>
       <c r="DB6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="DC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DD6" t="n">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="DE6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DF6" t="inlineStr"/>
       <c r="DG6" t="n">
         <v>5</v>
       </c>
       <c r="DH6" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="DI6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DJ6" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK6" t="n">
         <v>68</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>62</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,336 +4708,336 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="DQ6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="DR6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="DS6" t="n">
         <v>7</v>
       </c>
       <c r="DT6" t="inlineStr"/>
       <c r="DU6" t="n">
-        <v>1604</v>
+        <v>1694</v>
       </c>
       <c r="DV6" t="n">
-        <v>558</v>
+        <v>604</v>
       </c>
       <c r="DW6" t="n">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="DX6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="DY6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5168067226890757</v>
+        <v>0.5029821073558648</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5642201834862385</v>
+        <v>0.5524017467248908</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8428571428571429</v>
+        <v>0.8430493273542601</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.388170055452865</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4125874125874126</v>
+        <v>0.4379084967320261</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.388170055452865</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5707434052757794</v>
+        <v>0.5683615819209039</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.608</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5450236966824644</v>
+        <v>0.5418502202643172</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5752727272727273</v>
+        <v>0.5724538619275461</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.7103825136612022</v>
+        <v>0.6934673366834171</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5748587570621468</v>
+        <v>0.5881578947368421</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6042334830019244</v>
+        <v>0.6019915509957755</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.7089552238805971</v>
+        <v>0.6986301369863014</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6169977924944813</v>
+        <v>0.6262939958592133</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3934545454545454</v>
+        <v>0.3950786056049214</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.011090573012939</v>
+        <v>0.01384083044982699</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07553956834532374</v>
+        <v>0.0768361581920904</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.09207708779443255</v>
+        <v>0.09775967413441955</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.06859205776173286</v>
+        <v>0.06418918918918919</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.01020408163265306</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.01319261213720317</v>
+        <v>0.01503759398496241</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5233644859813084</v>
+        <v>0.5242290748898678</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.18</v>
+        <v>0.169811320754717</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7155688622754491</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.3739376770538244</v>
+        <v>0.376657824933687</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.754950495049505</v>
+        <v>0.7535211267605634</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2901234567901235</v>
+        <v>0.2939481268011527</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7371273712737128</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3338257016248153</v>
+        <v>0.3370165745856354</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.43125</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3607594936708861</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2909090909090909</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2764227642276423</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.3366336633663367</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6492537313432836</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.75625</v>
+        <v>0.7602339181286549</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.7254901960784313</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.760655737704918</v>
+        <v>0.7570093457943925</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.7373737373737373</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.05098684210526316</v>
+        <v>0.05092592592592592</v>
       </c>
       <c r="FQ6" t="n">
-        <v>96.0620957309185</v>
+        <v>95.85383678440925</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.6621621621621622</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.8638726445744</v>
+        <v>15.91552147239264</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.12572347266881</v>
+        <v>14.14050939963614</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.19928525016244</v>
+        <v>15.25104294478528</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.59627009646302</v>
+        <v>13.61449363250455</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.3396363636363636</v>
+        <v>0.3356117566643882</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6745182012847966</v>
+        <v>0.6741344195519349</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.7429245283018868</v>
+        <v>0.7471783295711061</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5558912386706949</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2014545454545454</v>
+        <v>0.202323991797676</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4584837545126354</v>
+        <v>0.4527027027027027</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.4922480620155039</v>
+        <v>0.4837545126353791</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4409448818897638</v>
+        <v>0.4253731343283582</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.06545454545454546</v>
+        <v>0.06698564593301436</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3820224719101123</v>
+        <v>0.3917525773195876</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1178181818181818</v>
+        <v>0.1223513328776487</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.4382716049382716</v>
+        <v>0.4245810055865922</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4409937888198758</v>
+        <v>0.4293785310734463</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9577464788732394</v>
+        <v>0.9605263157894737</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2756363636363636</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.366754617414248</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3716577540106952</v>
+        <v>0.3740458015267176</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7841726618705036</v>
+        <v>0.782312925170068</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4808743169398907</v>
+        <v>0.4874371859296482</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6590909090909091</v>
+        <v>0.6597938144329897</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.2241379310344828</v>
+        <v>0.21875</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.08743169398907104</v>
+        <v>0.09045226130653267</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="GV6" t="n">
         <v>0.8888888888888888</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.2160804020100502</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="GY6" t="n">
         <v>0.8148148148148148</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3135593220338983</v>
+        <v>0.3184210526315789</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6576576576576577</v>
+        <v>0.6611570247933884</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.0903954802259887</v>
+        <v>0.09473684210526316</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3135593220338983</v>
+        <v>0.3078947368421053</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3693693693693694</v>
+        <v>0.3931623931623932</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7330909090909091</v>
+        <v>0.7306903622693096</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.366754617414248</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5646588514996342</v>
+        <v>0.5630874914089347</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5625044</v>
+        <v>0.5617746323529411</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5438562138728323</v>
+        <v>0.5438030913978494</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.09389671361502347</v>
+        <v>0.09394703656998739</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1401273885350318</v>
+        <v>0.1401401401401401</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.01457194899817851</v>
+        <v>0.01533219761499148</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1508734780307041</v>
+        <v>0.153</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.2969825304393859</v>
+        <v>0.3035</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.573860911270984</v>
+        <v>5.624293785310734</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.24925093632959</v>
+        <v>25.20350262697023</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.2846003898635477</v>
+        <v>0.2852760736196319</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.006172839506172839</v>
+        <v>0.0111731843575419</v>
       </c>
     </row>
     <row r="7">
@@ -7135,73 +7135,73 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>58200</v>
+        <v>61080</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J10" t="n">
-        <v>1978</v>
+        <v>2071</v>
       </c>
       <c r="K10" t="n">
-        <v>1996</v>
+        <v>2088</v>
       </c>
       <c r="L10" t="n">
-        <v>705</v>
+        <v>740</v>
       </c>
       <c r="M10" t="n">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="N10" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="O10" t="n">
-        <v>3974</v>
+        <v>4159</v>
       </c>
       <c r="P10" t="n">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="Q10" t="n">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="R10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S10" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="T10" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="U10" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="V10" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="W10" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="X10" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Y10" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="Z10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -7210,10 +7210,10 @@
         <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="AG10" t="n">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -7222,251 +7222,251 @@
         <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AK10" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AL10" t="n">
-        <v>547</v>
+        <v>574</v>
       </c>
       <c r="AM10" t="n">
-        <v>1021</v>
+        <v>1071</v>
       </c>
       <c r="AN10" t="n">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AO10" t="n">
-        <v>713</v>
+        <v>747</v>
       </c>
       <c r="AP10" t="n">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2274</v>
+        <v>2389</v>
       </c>
       <c r="AR10" t="n">
-        <v>2100</v>
+        <v>2211</v>
       </c>
       <c r="AS10" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AT10" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="AU10" t="n">
         <v>25</v>
       </c>
       <c r="AV10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AW10" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AX10" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="AY10" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AZ10" t="n">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="BA10" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="BB10" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="BC10" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="BD10" t="n">
-        <v>773</v>
+        <v>812</v>
       </c>
       <c r="BE10" t="n">
+        <v>558</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>590</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>717</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>81</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>122</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>524</v>
       </c>
-      <c r="BF10" t="n">
-        <v>570</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>684</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>78</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>120</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>498</v>
-      </c>
       <c r="BK10" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="BL10" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="BM10" t="n">
         <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="BO10" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="BP10" t="n">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="BQ10" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="BR10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BS10" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="BT10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BU10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BV10" t="n">
-        <v>1208</v>
+        <v>1275</v>
       </c>
       <c r="BW10" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BX10" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="BY10" t="n">
         <v>5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="CA10" t="n">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="CB10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="CC10" t="n">
-        <v>774</v>
+        <v>806</v>
       </c>
       <c r="CD10" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="CE10" t="n">
-        <v>1058</v>
+        <v>1103</v>
       </c>
       <c r="CF10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CG10" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="CH10" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="CI10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="CJ10" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="CK10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="CM10" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="CN10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CO10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CQ10" t="n">
         <v>11</v>
       </c>
       <c r="CR10" t="n">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="CS10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CT10" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="CU10" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="CV10" t="n">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="CW10" t="n">
         <v>13</v>
       </c>
       <c r="CX10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CY10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CZ10" t="n">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="DC10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DD10" t="n">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="DE10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
       </c>
       <c r="DG10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DH10" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="DI10" t="n">
         <v>8</v>
       </c>
       <c r="DJ10" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="DK10" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="DL10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DM10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DN10" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
@@ -7475,10 +7475,10 @@
         <v>38</v>
       </c>
       <c r="DQ10" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="DR10" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="DS10" t="n">
         <v>7</v>
@@ -7487,247 +7487,247 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1972</v>
+        <v>2077</v>
       </c>
       <c r="DV10" t="n">
-        <v>771</v>
+        <v>808</v>
       </c>
       <c r="DW10" t="n">
-        <v>704</v>
+        <v>738</v>
       </c>
       <c r="DX10" t="n">
+        <v>55</v>
+      </c>
+      <c r="DY10" t="n">
         <v>53</v>
       </c>
-      <c r="DY10" t="n">
-        <v>48</v>
-      </c>
       <c r="DZ10" t="n">
-        <v>0.4789762340036563</v>
+        <v>0.4860627177700348</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5379876796714579</v>
+        <v>0.543859649122807</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8976377952755905</v>
+        <v>0.8984962406015038</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3562412342215989</v>
+        <v>0.356091030789826</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.390625</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3378378378378378</v>
+        <v>0.3390557939914163</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3562412342215989</v>
+        <v>0.356091030789826</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5357492654260528</v>
+        <v>0.5359477124183006</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5424836601307189</v>
+        <v>0.5345911949685535</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4904109589041096</v>
+        <v>0.4831168831168831</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5351787773933102</v>
+        <v>0.5352035203520352</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5604651162790698</v>
+        <v>0.5493273542600897</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4965928449744463</v>
+        <v>0.4927184466019418</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5770992366412214</v>
+        <v>0.5775569558894813</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6068548387096774</v>
+        <v>0.6003861003861004</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5522174535050072</v>
+        <v>0.5502035278154681</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4111880046136102</v>
+        <v>0.4108910891089109</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.008415147265077139</v>
+        <v>0.008032128514056224</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07835455435847209</v>
+        <v>0.08029878618113913</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09187279151943463</v>
+        <v>0.09380234505862646</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07977207977207977</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0170940170940171</v>
+        <v>0.01626016260162602</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.006024096385542169</v>
+        <v>0.005725190839694656</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5496688741721855</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9019607843137255</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1020408163265306</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6672413793103448</v>
+        <v>0.6639072847682119</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3297872340425532</v>
+        <v>0.3286004056795132</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7257383966244726</v>
+        <v>0.7223340040241448</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2755555555555556</v>
+        <v>0.2754237288135593</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.6902815622161671</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3032608695652174</v>
+        <v>0.3025906735751295</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.3969849246231156</v>
+        <v>0.4</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2953367875647668</v>
+        <v>0.2892156862745098</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2435897435897436</v>
+        <v>0.2405063291139241</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2819672131147541</v>
+        <v>0.2834890965732087</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2620689655172414</v>
+        <v>0.2582781456953642</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6143497757847534</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6706349206349206</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7798165137614679</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7053571428571429</v>
+        <v>0.7011494252873564</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7753623188405797</v>
+        <v>0.7718120805369127</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04790419161676647</v>
+        <v>0.04805491990846682</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.32577319587629</v>
+        <v>98.05108055009823</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5211267605633803</v>
+        <v>0.5167785234899329</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.29074823053589</v>
+        <v>14.30193143408981</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.99644288577154</v>
+        <v>15.06738505747126</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.71622851365015</v>
+        <v>13.73191694833414</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.25455911823647</v>
+        <v>14.32931034482759</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3264129181084198</v>
+        <v>0.3283828382838284</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6466431095406361</v>
+        <v>0.6465661641541038</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7120622568093385</v>
+        <v>0.7134935304990758</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5027322404371585</v>
+        <v>0.5077720207253886</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1949250288350634</v>
+        <v>0.1930693069306931</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4131054131054131</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4489164086687307</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4475524475524476</v>
+        <v>0.4551724137931035</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06747404844290658</v>
+        <v>0.06765676567656766</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3247863247863248</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3304347826086956</v>
+        <v>0.3553719008264463</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1239907727797001</v>
+        <v>0.1226622662266227</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3228699551569507</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.330188679245283</v>
+        <v>0.3272727272727273</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.9857142857142858</v>
+        <v>0.9861111111111112</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.28719723183391</v>
+        <v>0.2882288228822882</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3694779116465863</v>
+        <v>0.3702290076335878</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3717171717171717</v>
+        <v>0.3723608445297505</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8641304347826086</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5069767441860465</v>
+        <v>0.5067264573991032</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.5929203539823009</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1076923076923077</v>
+        <v>0.1194029850746269</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06511627906976744</v>
+        <v>0.07174887892376682</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2232558139534884</v>
+        <v>0.2152466367713005</v>
       </c>
       <c r="GX10" t="n">
         <v>0.3958333333333333</v>
@@ -7736,70 +7736,70 @@
         <v>0.7894736842105263</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3253833049403748</v>
+        <v>0.3300970873786408</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5916230366492147</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.110732538330494</v>
+        <v>0.1051779935275081</v>
       </c>
       <c r="HC10" t="n">
         <v>0.3384615384615385</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2674616695059625</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3375796178343949</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.73760092272203</v>
+        <v>0.7392739273927392</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3694779116465863</v>
+        <v>0.3702290076335878</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5642493051534453</v>
+        <v>0.565078602981778</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5503383211678832</v>
+        <v>0.5512853146853146</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.551470395869191</v>
+        <v>0.5520001633986928</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1173389209009953</v>
+        <v>0.117</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1827326068734283</v>
+        <v>0.1824</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.008379888268156424</v>
+        <v>0.008</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1328056288478452</v>
+        <v>0.1305985768103809</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3399296394019349</v>
+        <v>0.339891167852658</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.654260528893242</v>
+        <v>5.614285714285714</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.25353107344633</v>
+        <v>25.26185983827493</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3564206268958544</v>
+        <v>0.3573153066151618</v>
       </c>
       <c r="HS10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="HT10" t="n">
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01395348837209302</v>
+        <v>0.01345291479820628</v>
       </c>
     </row>
     <row r="11">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -4377,265 +4377,265 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>49260</v>
+        <v>52140</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J6" t="n">
-        <v>1630</v>
+        <v>1722</v>
       </c>
       <c r="K6" t="n">
-        <v>1649</v>
+        <v>1743</v>
       </c>
       <c r="L6" t="n">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="M6" t="n">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="N6" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="O6" t="n">
-        <v>3279</v>
+        <v>3465</v>
       </c>
       <c r="P6" t="n">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="Q6" t="n">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="R6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S6" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U6" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="V6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="W6" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="X6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Z6" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AA6" t="n">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="n">
         <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AF6" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="AG6" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AK6" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AL6" t="n">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="AM6" t="n">
-        <v>885</v>
+        <v>931</v>
       </c>
       <c r="AN6" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="AO6" t="n">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="AP6" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="AR6" t="n">
-        <v>1722</v>
+        <v>1828</v>
       </c>
       <c r="AS6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AT6" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AU6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AV6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AW6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AX6" t="n">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="AY6" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AZ6" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="BA6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BB6" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="BC6" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="BD6" t="n">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="BE6" t="n">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="BF6" t="n">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="BG6" t="n">
-        <v>564</v>
+        <v>609</v>
       </c>
       <c r="BH6" t="n">
         <v>105</v>
       </c>
       <c r="BI6" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="BK6" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="BL6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BM6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="BO6" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="BP6" t="n">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="BQ6" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="BR6" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="BS6" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="BT6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BU6" t="n">
         <v>12</v>
       </c>
       <c r="BV6" t="n">
-        <v>1070</v>
+        <v>1131</v>
       </c>
       <c r="BW6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="BX6" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="CA6" t="n">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="CB6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CC6" t="n">
-        <v>628</v>
+        <v>664</v>
       </c>
       <c r="CD6" t="n">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="CE6" t="n">
-        <v>881</v>
+        <v>929</v>
       </c>
       <c r="CF6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CG6" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="CH6" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="CI6" t="n">
         <v>56</v>
       </c>
       <c r="CJ6" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="CK6" t="n">
         <v>29</v>
       </c>
       <c r="CL6" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="CM6" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="CN6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CO6" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="CP6" t="n">
         <v>8</v>
@@ -4644,62 +4644,62 @@
         <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="CS6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CT6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="CU6" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="CV6" t="n">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="CY6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CZ6" t="n">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="DA6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DB6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="DC6" t="n">
         <v>22</v>
       </c>
       <c r="DD6" t="n">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="DE6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="DF6" t="inlineStr"/>
       <c r="DG6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DH6" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="DI6" t="n">
         <v>9</v>
       </c>
       <c r="DJ6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="DK6" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,336 +4708,338 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="DQ6" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="DR6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="DS6" t="n">
         <v>7</v>
       </c>
-      <c r="DT6" t="inlineStr"/>
+      <c r="DT6" t="n">
+        <v>1</v>
+      </c>
       <c r="DU6" t="n">
-        <v>1694</v>
+        <v>1787</v>
       </c>
       <c r="DV6" t="n">
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="DW6" t="n">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="DX6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DY6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.5029821073558648</v>
+        <v>0.4980916030534351</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5524017467248908</v>
+        <v>0.5471698113207547</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8430493273542601</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.3901639344262295</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.582089552238806</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.4379084967320261</v>
+        <v>0.425</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.3901639344262295</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5683615819209039</v>
+        <v>0.5628356605800214</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6056338028169014</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5418502202643172</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5724538619275461</v>
+        <v>0.5717066839714471</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.6934673366834171</v>
+        <v>0.6913875598086124</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5881578947368421</v>
+        <v>0.5808080808080808</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6019915509957755</v>
+        <v>0.6013165426445335</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.6986301369863014</v>
+        <v>0.6986899563318777</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6262939958592133</v>
+        <v>0.6185770750988142</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3950786056049214</v>
+        <v>0.3958468526930565</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01384083044982699</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0768361581920904</v>
+        <v>0.07518796992481203</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.09775967413441955</v>
+        <v>0.095703125</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.06418918918918919</v>
+        <v>0.06389776357827476</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01020408163265306</v>
+        <v>0.009433962264150943</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.01503759398496241</v>
+        <v>0.01449275362318841</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5242290748898678</v>
+        <v>0.5330578512396694</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.169811320754717</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="EZ6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.371571072319202</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.7610619469026548</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.2912087912087912</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.7331730769230769</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.4345238095238095</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.3470588235294118</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.2698412698412698</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.2755905511811024</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.3272727272727273</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.6301369863013698</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.7528089887640449</v>
+      </c>
+      <c r="FM6" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="FA6" t="n">
-        <v>0.376657824933687</v>
-      </c>
-      <c r="FB6" t="n">
-        <v>0.7535211267605634</v>
-      </c>
-      <c r="FC6" t="n">
-        <v>0.2939481268011527</v>
-      </c>
-      <c r="FD6" t="n">
-        <v>0.735632183908046</v>
-      </c>
-      <c r="FE6" t="n">
-        <v>0.3370165745856354</v>
-      </c>
-      <c r="FF6" t="n">
-        <v>0.43125</v>
-      </c>
-      <c r="FG6" t="n">
-        <v>0.3607594936708861</v>
-      </c>
-      <c r="FH6" t="n">
-        <v>0.2711864406779661</v>
-      </c>
-      <c r="FI6" t="n">
-        <v>0.2764227642276423</v>
-      </c>
-      <c r="FJ6" t="n">
-        <v>0.3366336633663367</v>
-      </c>
-      <c r="FK6" t="n">
-        <v>0.6492537313432836</v>
-      </c>
-      <c r="FL6" t="n">
-        <v>0.7602339181286549</v>
-      </c>
-      <c r="FM6" t="n">
-        <v>0.7307692307692307</v>
-      </c>
       <c r="FN6" t="n">
-        <v>0.7570093457943925</v>
+        <v>0.7660818713450293</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.05092592592592592</v>
+        <v>0.05109489051094891</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.85383678440925</v>
+        <v>95.69620253164557</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6621621621621622</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.91552147239264</v>
+        <v>15.91149825783972</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.14050939963614</v>
+        <v>14.19414802065405</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.25104294478528</v>
+        <v>15.24819976771196</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.61449363250455</v>
+        <v>13.67343660355709</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.3356117566643882</v>
+        <v>0.3322517845554834</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.6741344195519349</v>
+        <v>0.671875</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.7471783295711061</v>
+        <v>0.7429805615550756</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5558912386706949</v>
+        <v>0.5552325581395349</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.202323991797676</v>
+        <v>0.2031148604802077</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4527027027027027</v>
+        <v>0.4408945686900959</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.4837545126353791</v>
+        <v>0.4709897610921502</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4253731343283582</v>
+        <v>0.4202898550724637</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.06698564593301436</v>
+        <v>0.06878650227125244</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3877551020408163</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3917525773195876</v>
+        <v>0.4</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.1223513328776487</v>
+        <v>0.127190136275146</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.4245810055865922</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4293785310734463</v>
+        <v>0.4375</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9605263157894737</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3719806763285024</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3740458015267176</v>
+        <v>0.3774509803921569</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.782312925170068</v>
+        <v>0.7922077922077922</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4874371859296482</v>
+        <v>0.4832535885167464</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6597938144329897</v>
+        <v>0.6534653465346535</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.21875</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.09045226130653267</v>
+        <v>0.09569377990430622</v>
       </c>
       <c r="GU6" t="n">
         <v>0.5</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2160804020100502</v>
+        <v>0.2248803827751196</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6170212765957447</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3184210526315789</v>
+        <v>0.3131313131313131</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6611570247933884</v>
+        <v>0.6693548387096774</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.09473684210526316</v>
+        <v>0.09848484848484848</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3078947368421053</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3931623931623932</v>
+        <v>0.3884297520661157</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.7306903622693096</v>
+        <v>0.72809863724854</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3719806763285024</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5630874914089347</v>
+        <v>0.5618342139595564</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5617746323529411</v>
+        <v>0.5595962068965518</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5438030913978494</v>
+        <v>0.5434414948453609</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.09394703656998739</v>
+        <v>0.09515260323159784</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1401401401401401</v>
+        <v>0.1425855513307985</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.01533219761499148</v>
+        <v>0.01453957996768982</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.153</v>
+        <v>0.15187470336972</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3035</v>
+        <v>0.2985287138111059</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.624293785310734</v>
+        <v>5.711922663802364</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.20350262697023</v>
+        <v>25.16716417910447</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.2852760736196319</v>
+        <v>0.2828106852497096</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.0111731843575419</v>
+        <v>0.02040816326530612</v>
       </c>
     </row>
     <row r="7">
@@ -7135,67 +7137,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>61080</v>
+        <v>63960</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J10" t="n">
-        <v>2071</v>
+        <v>2164</v>
       </c>
       <c r="K10" t="n">
-        <v>2088</v>
+        <v>2181</v>
       </c>
       <c r="L10" t="n">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="M10" t="n">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="N10" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="O10" t="n">
-        <v>4159</v>
+        <v>4345</v>
       </c>
       <c r="P10" t="n">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="Q10" t="n">
-        <v>597</v>
+        <v>619</v>
       </c>
       <c r="R10" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="S10" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="T10" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="U10" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="V10" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="W10" t="n">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="X10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Y10" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="Z10" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="AA10" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
@@ -7204,239 +7206,239 @@
         <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="AG10" t="n">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AJ10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="AL10" t="n">
+        <v>593</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1114</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>283</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>790</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>460</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2495</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2318</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>87</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>165</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>68</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>322</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>195</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>402</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>84</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>248</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>212</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>854</v>
+      </c>
+      <c r="BE10" t="n">
         <v>574</v>
       </c>
-      <c r="AM10" t="n">
-        <v>1071</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>266</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>747</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>443</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2389</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2211</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>159</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>64</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>67</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>312</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>186</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>385</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>79</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>233</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BF10" t="n">
+        <v>612</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>765</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>84</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>126</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>554</v>
+      </c>
+      <c r="BK10" t="n">
         <v>203</v>
       </c>
-      <c r="BD10" t="n">
-        <v>812</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>558</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>590</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>717</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>81</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>122</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>524</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>194</v>
-      </c>
       <c r="BL10" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="BM10" t="n">
         <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="BO10" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="BP10" t="n">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="BQ10" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="BR10" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="BS10" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="BT10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BU10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>1275</v>
+        <v>1339</v>
       </c>
       <c r="BW10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="BX10" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="BY10" t="n">
         <v>5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="CA10" t="n">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="CB10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="CC10" t="n">
-        <v>806</v>
+        <v>839</v>
       </c>
       <c r="CD10" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="CE10" t="n">
-        <v>1103</v>
+        <v>1151</v>
       </c>
       <c r="CF10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="CG10" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="CH10" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="CI10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="CK10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CL10" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="CM10" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="CN10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CO10" t="n">
         <v>88</v>
       </c>
       <c r="CP10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ10" t="n">
         <v>11</v>
       </c>
       <c r="CR10" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="CS10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CT10" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="CU10" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="CV10" t="n">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="CW10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CX10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="CY10" t="n">
         <v>38</v>
       </c>
       <c r="CZ10" t="n">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DC10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DD10" t="n">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="DE10" t="n">
         <v>49</v>
@@ -7445,280 +7447,280 @@
         <v>3</v>
       </c>
       <c r="DG10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DH10" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="DI10" t="n">
         <v>8</v>
       </c>
       <c r="DJ10" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="DK10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="DL10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="DM10" t="n">
         <v>9</v>
       </c>
       <c r="DN10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="DQ10" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="DR10" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="DS10" t="n">
         <v>7</v>
       </c>
       <c r="DT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DU10" t="n">
-        <v>2077</v>
+        <v>2173</v>
       </c>
       <c r="DV10" t="n">
-        <v>808</v>
+        <v>850</v>
       </c>
       <c r="DW10" t="n">
-        <v>738</v>
+        <v>778</v>
       </c>
       <c r="DX10" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="DY10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4860627177700348</v>
+        <v>0.4839797639123103</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.543859649122807</v>
+        <v>0.5415094339622641</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8984962406015038</v>
+        <v>0.9010600706713781</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.356091030789826</v>
+        <v>0.3582278481012658</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.390625</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3390557939914163</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.356091030789826</v>
+        <v>0.3582278481012658</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5359477124183006</v>
+        <v>0.5323159784560144</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5345911949685535</v>
+        <v>0.5272727272727272</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4831168831168831</v>
+        <v>0.4850746268656717</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5352035203520352</v>
+        <v>0.5344012605042017</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5493273542600897</v>
+        <v>0.5407725321888412</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4927184466019418</v>
+        <v>0.4938461538461538</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5775569558894813</v>
+        <v>0.5761926817971283</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.6003861003861004</v>
+        <v>0.5922509225092251</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5502035278154681</v>
+        <v>0.5503875968992248</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4108910891089109</v>
+        <v>0.4149159663865546</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.008032128514056224</v>
+        <v>0.007594936708860759</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.08029878618113913</v>
+        <v>0.0807899461400359</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09380234505862646</v>
+        <v>0.09369951534733441</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.07977207977207977</v>
+        <v>0.08264462809917356</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01626016260162602</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.005725190839694656</v>
+        <v>0.005415162454873646</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5465838509316771</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.9019607843137255</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6639072847682119</v>
+        <v>0.6656050955414012</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3286004056795132</v>
+        <v>0.3372093023255814</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7223340040241448</v>
+        <v>0.7237354085603113</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2754237288135593</v>
+        <v>0.2670682730923695</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6902815622161671</v>
+        <v>0.691768826619965</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3025906735751295</v>
+        <v>0.3027613412228797</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4</v>
+        <v>0.4099099099099099</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2892156862745098</v>
+        <v>0.2938388625592417</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2405063291139241</v>
+        <v>0.2530120481927711</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2834890965732087</v>
+        <v>0.2719298245614035</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2582781456953642</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.602510460251046</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7798165137614679</v>
+        <v>0.7787610619469026</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.7011494252873564</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7718120805369127</v>
+        <v>0.7721518987341772</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.04805491990846682</v>
+        <v>0.0544069640914037</v>
       </c>
       <c r="FQ10" t="n">
-        <v>98.05108055009823</v>
+        <v>97.82363977485929</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5167785234899329</v>
+        <v>0.5228758169934641</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.30193143408981</v>
+        <v>14.34473197781885</v>
       </c>
       <c r="FT10" t="n">
-        <v>15.06738505747126</v>
+        <v>15.09307657038056</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.73191694833414</v>
+        <v>13.78063770794824</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.32931034482759</v>
+        <v>14.35937643282898</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3283828382838284</v>
+        <v>0.3251050420168067</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6465661641541038</v>
+        <v>0.6397415185783522</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7134935304990758</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5077720207253886</v>
+        <v>0.5025252525252525</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1930693069306931</v>
+        <v>0.1906512605042017</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4131054131054131</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4489164086687307</v>
+        <v>0.4504504504504505</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4551724137931035</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06765676567656766</v>
+        <v>0.06932773109243698</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.3560606060606061</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3553719008264463</v>
+        <v>0.3615384615384615</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.3953488372093023</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1226622662266227</v>
+        <v>0.1239495798319328</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3228699551569507</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3272727272727273</v>
+        <v>0.3433476394849785</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.9861111111111112</v>
+        <v>0.975</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2882288228822882</v>
+        <v>0.2909663865546219</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3702290076335878</v>
+        <v>0.3664259927797834</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3723608445297505</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5067264573991032</v>
+        <v>0.5064377682403434</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5929203539823009</v>
+        <v>0.5847457627118644</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1194029850746269</v>
+        <v>0.1159420289855072</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.07174887892376682</v>
+        <v>0.06866952789699571</v>
       </c>
       <c r="GU10" t="n">
         <v>0.375</v>
@@ -7727,79 +7729,79 @@
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2152466367713005</v>
+        <v>0.2231759656652361</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3300970873786408</v>
+        <v>0.3230769230769231</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5857142857142857</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1051779935275081</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3384615384615385</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2718446601941747</v>
+        <v>0.2738461538461539</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.3370786516853932</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7392739273927392</v>
+        <v>0.7400210084033614</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3702290076335878</v>
+        <v>0.3664259927797834</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.565078602981778</v>
+        <v>0.5648775171323143</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5512853146853146</v>
+        <v>0.5517606666666667</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5520001633986928</v>
+        <v>0.5509492236024846</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.117</v>
+        <v>0.115145723841376</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1824</v>
+        <v>0.1807692307692308</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.008</v>
+        <v>0.007566204287515763</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1305985768103809</v>
+        <v>0.1290581162324649</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.339891167852658</v>
+        <v>0.3422845691382765</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.614285714285714</v>
+        <v>5.640394973070018</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.26185983827493</v>
+        <v>25.24484076433121</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3573153066151618</v>
+        <v>0.3604436229205176</v>
       </c>
       <c r="HS10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="HT10" t="n">
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01345291479820628</v>
+        <v>0.01271186440677966</v>
       </c>
     </row>
     <row r="11">

--- a/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Team_stats.xlsx
@@ -4377,265 +4377,265 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>52140</v>
+        <v>55020</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="J6" t="n">
-        <v>1722</v>
+        <v>1811</v>
       </c>
       <c r="K6" t="n">
-        <v>1743</v>
+        <v>1833</v>
       </c>
       <c r="L6" t="n">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="M6" t="n">
-        <v>589</v>
+        <v>611</v>
       </c>
       <c r="N6" t="n">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="O6" t="n">
-        <v>3465</v>
+        <v>3644</v>
       </c>
       <c r="P6" t="n">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="Q6" t="n">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="R6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S6" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="T6" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U6" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="V6" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="W6" t="n">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="X6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y6" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA6" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="AB6" t="n">
         <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="n">
         <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AF6" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AG6" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AJ6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AK6" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AL6" t="n">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="AM6" t="n">
-        <v>931</v>
+        <v>981</v>
       </c>
       <c r="AN6" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AO6" t="n">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="AP6" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2107</v>
+        <v>2201</v>
       </c>
       <c r="AR6" t="n">
-        <v>1828</v>
+        <v>1918</v>
       </c>
       <c r="AS6" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AT6" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AU6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AW6" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AX6" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="AY6" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="AZ6" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="BA6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BB6" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="BC6" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="BD6" t="n">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="BE6" t="n">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="BF6" t="n">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="BG6" t="n">
-        <v>609</v>
+        <v>636</v>
       </c>
       <c r="BH6" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="BI6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BJ6" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="BK6" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="BL6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN6" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="BO6" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="BP6" t="n">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="BQ6" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="BR6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="BS6" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BT6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BU6" t="n">
         <v>12</v>
       </c>
       <c r="BV6" t="n">
-        <v>1131</v>
+        <v>1168</v>
       </c>
       <c r="BW6" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="BX6" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="CA6" t="n">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="CB6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CC6" t="n">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="CD6" t="n">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="CE6" t="n">
-        <v>929</v>
+        <v>988</v>
       </c>
       <c r="CF6" t="n">
         <v>35</v>
       </c>
       <c r="CG6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="CH6" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="CI6" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="CJ6" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="CK6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CL6" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="CM6" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="CN6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CO6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="CP6" t="n">
         <v>8</v>
@@ -4644,43 +4644,43 @@
         <v>9</v>
       </c>
       <c r="CR6" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="CS6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="CT6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="CU6" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="CV6" t="n">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="CW6" t="n">
         <v>3</v>
       </c>
       <c r="CX6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CY6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CZ6" t="n">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="DA6" t="n">
         <v>6</v>
       </c>
       <c r="DB6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="DC6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="DD6" t="n">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="DE6" t="n">
         <v>29</v>
@@ -4690,16 +4690,16 @@
         <v>6</v>
       </c>
       <c r="DH6" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="DI6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="DJ6" t="n">
+        <v>81</v>
+      </c>
+      <c r="DK6" t="n">
         <v>76</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>72</v>
       </c>
       <c r="DL6" t="n">
         <v>6</v>
@@ -4708,338 +4708,338 @@
         <v>4</v>
       </c>
       <c r="DN6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="DO6" t="n">
         <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="DQ6" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="DR6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="DS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DT6" t="n">
         <v>1</v>
       </c>
       <c r="DU6" t="n">
-        <v>1787</v>
+        <v>1867</v>
       </c>
       <c r="DV6" t="n">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="DW6" t="n">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="DX6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DY6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.4980916030534351</v>
+        <v>0.4898710865561695</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.5373737373737374</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.848</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.3901639344262295</v>
+        <v>0.3863987635239567</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.582089552238806</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.425</v>
+        <v>0.4191616766467066</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.3901639344262295</v>
+        <v>0.3863987635239567</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.5628356605800214</v>
+        <v>0.5535168195718655</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.6056338028169014</v>
+        <v>0.5827814569536424</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.5423728813559322</v>
+        <v>0.532</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.5717066839714471</v>
+        <v>0.5638820638820639</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.6913875598086124</v>
+        <v>0.669683257918552</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5808080808080808</v>
+        <v>0.5707434052757794</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.6013165426445335</v>
+        <v>0.5945287107258939</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.6986899563318777</v>
+        <v>0.6816326530612244</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.6185770750988142</v>
+        <v>0.6106941838649156</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.3958468526930565</v>
+        <v>0.3974201474201474</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.01854714064914992</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07518796992481203</v>
+        <v>0.0764525993883792</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.095703125</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.06389776357827476</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.009433962264150943</v>
+        <v>0.008695652173913044</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.01449275362318841</v>
+        <v>0.01360544217687075</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.5330578512396694</v>
+        <v>0.52734375</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.1754385964912281</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7</v>
+        <v>0.6953316953316954</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.371571072319202</v>
+        <v>0.3781902552204177</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.7610619469026548</v>
+        <v>0.7610062893081762</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2912087912087912</v>
+        <v>0.2912371134020619</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.7331730769230769</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.336996336996337</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.3470588235294118</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2698412698412698</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2755905511811024</v>
+        <v>0.2814814814814815</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.3272727272727273</v>
+        <v>0.3135593220338983</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.6301369863013698</v>
+        <v>0.6305732484076433</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.7528089887640449</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7213114754098361</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.7660818713450293</v>
+        <v>0.7591036414565826</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.05109489051094891</v>
+        <v>0.04781420765027322</v>
       </c>
       <c r="FQ6" t="n">
-        <v>95.69620253164557</v>
+        <v>95.37186477644492</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6463414634146342</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.91149825783972</v>
+        <v>15.9941468801767</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.19414802065405</v>
+        <v>14.21418439716312</v>
       </c>
       <c r="FU6" t="n">
-        <v>15.24819976771196</v>
+        <v>15.29094422970734</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.67343660355709</v>
+        <v>13.66541189307147</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.3322517845554834</v>
+        <v>0.3292383292383292</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.671875</v>
+        <v>0.6585820895522388</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.7429805615550756</v>
+        <v>0.7293388429752066</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.5552325581395349</v>
+        <v>0.546742209631728</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.2031148604802077</v>
+        <v>0.2027027027027027</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.4408945686900959</v>
+        <v>0.4393939393939394</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.4709897610921502</v>
+        <v>0.4707792207792208</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4202898550724637</v>
+        <v>0.4206896551724138</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.06878650227125244</v>
+        <v>0.07063882063882064</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.4</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.127190136275146</v>
+        <v>0.1265356265356265</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4174757281553398</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.4375</v>
+        <v>0.43</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.9651162790697675</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2708845208845209</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3719806763285024</v>
+        <v>0.3718820861678004</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3774509803921569</v>
+        <v>0.3770114942528736</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.7922077922077922</v>
+        <v>0.7865853658536586</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.4832535885167464</v>
+        <v>0.4886877828054298</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.6534653465346535</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2205882352941176</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.09569377990430622</v>
+        <v>0.09502262443438914</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="GV6" t="n">
         <v>0.9</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2248803827751196</v>
+        <v>0.2217194570135747</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3131313131313131</v>
+        <v>0.3141486810551559</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.6693548387096774</v>
+        <v>0.648854961832061</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.09832134292565947</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.302158273381295</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3884297520661157</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.72809863724854</v>
+        <v>0.7266584766584766</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3719806763285024</v>
+        <v>0.3718820861678004</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.5618342139595564</v>
+        <v>0.5600712962962964</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.5595962068965518</v>
+        <v>0.5570471153846154</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.5434414948453609</v>
+        <v>0.5423050122249389</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.09515260323159784</v>
+        <v>0.09405099150141644</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.1425855513307985</v>
+        <v>0.1392405063291139</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.01453957996768982</v>
+        <v>0.01820940819423369</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.15187470336972</v>
+        <v>0.1517492049068605</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.2985287138111059</v>
+        <v>0.2971376646978646</v>
       </c>
       <c r="HP6" t="n">
-        <v>5.711922663802364</v>
+        <v>5.783180428134557</v>
       </c>
       <c r="HQ6" t="n">
-        <v>25.16716417910447</v>
+        <v>25.18421875</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.2828106852497096</v>
+        <v>0.2816123688569851</v>
       </c>
       <c r="HS6" t="n">
         <v>2</v>
       </c>
       <c r="HT6" t="inlineStr"/>
       <c r="HU6" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.02912621359223301</v>
       </c>
     </row>
     <row r="7">
@@ -7137,265 +7137,265 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>63960</v>
+        <v>66840</v>
       </c>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J10" t="n">
-        <v>2164</v>
+        <v>2254</v>
       </c>
       <c r="K10" t="n">
-        <v>2181</v>
+        <v>2270</v>
       </c>
       <c r="L10" t="n">
-        <v>780</v>
+        <v>802</v>
       </c>
       <c r="M10" t="n">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="N10" t="n">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="O10" t="n">
-        <v>4345</v>
+        <v>4524</v>
       </c>
       <c r="P10" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="Q10" t="n">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="R10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="S10" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="T10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="U10" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V10" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="W10" t="n">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="X10" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Y10" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
         <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AF10" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AG10" t="n">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AK10" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AL10" t="n">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="AM10" t="n">
-        <v>1114</v>
+        <v>1163</v>
       </c>
       <c r="AN10" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="AO10" t="n">
-        <v>790</v>
+        <v>828</v>
       </c>
       <c r="AP10" t="n">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2495</v>
+        <v>2585</v>
       </c>
       <c r="AR10" t="n">
-        <v>2318</v>
+        <v>2412</v>
       </c>
       <c r="AS10" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="AT10" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="AU10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV10" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AW10" t="n">
         <v>70</v>
       </c>
       <c r="AX10" t="n">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="AY10" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AZ10" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="BA10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BB10" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="BC10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="BD10" t="n">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="BE10" t="n">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="BF10" t="n">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="BG10" t="n">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="BH10" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="BI10" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="BJ10" t="n">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="BK10" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BL10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BM10" t="n">
         <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="BO10" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="BP10" t="n">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="BQ10" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="BR10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="BS10" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="BT10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BV10" t="n">
-        <v>1339</v>
+        <v>1385</v>
       </c>
       <c r="BW10" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="BX10" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="BY10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="CA10" t="n">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="CB10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="CC10" t="n">
-        <v>839</v>
+        <v>874</v>
       </c>
       <c r="CD10" t="n">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="CE10" t="n">
-        <v>1151</v>
+        <v>1203</v>
       </c>
       <c r="CF10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CG10" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="CH10" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="CI10" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="CJ10" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="CK10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="CL10" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="CM10" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="CN10" t="n">
         <v>21</v>
       </c>
       <c r="CO10" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="CP10" t="n">
         <v>4</v>
@@ -7404,41 +7404,41 @@
         <v>11</v>
       </c>
       <c r="CR10" t="n">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="CS10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="CT10" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="CU10" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="CV10" t="n">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="CW10" t="n">
         <v>14</v>
       </c>
       <c r="CX10" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="CY10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CZ10" t="n">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="DA10" t="inlineStr"/>
       <c r="DB10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="DC10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="DD10" t="n">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="DE10" t="n">
         <v>49</v>
@@ -7450,358 +7450,358 @@
         <v>9</v>
       </c>
       <c r="DH10" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="DI10" t="n">
         <v>8</v>
       </c>
       <c r="DJ10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="DK10" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="DL10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="DM10" t="n">
         <v>9</v>
       </c>
       <c r="DN10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="DO10" t="n">
         <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="DR10" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="DS10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DT10" t="n">
         <v>2</v>
       </c>
       <c r="DU10" t="n">
-        <v>2173</v>
+        <v>2246</v>
       </c>
       <c r="DV10" t="n">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="DW10" t="n">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="DX10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="DY10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4839797639123103</v>
+        <v>0.4804560260586319</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5415094339622641</v>
+        <v>0.5383211678832117</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9010600706713781</v>
+        <v>0.8983050847457628</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3582278481012658</v>
+        <v>0.3562801932367149</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.3802816901408451</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.3307392996108949</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3582278481012658</v>
+        <v>0.3562801932367149</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5323159784560144</v>
+        <v>0.5279449699054171</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5272727272727272</v>
+        <v>0.5310734463276836</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4850746268656717</v>
+        <v>0.4843373493975904</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5344012605042017</v>
+        <v>0.5306378704168759</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5407725321888412</v>
+        <v>0.5423387096774194</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4938461538461538</v>
+        <v>0.4888392857142857</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5761926817971283</v>
+        <v>0.5716186252771619</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5922509225092251</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5503875968992248</v>
+        <v>0.54375</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4149159663865546</v>
+        <v>0.4158714213962832</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.007594936708860759</v>
+        <v>0.007246376811594203</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0807899461400359</v>
+        <v>0.08082545141874463</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09369951534733441</v>
+        <v>0.09175738724727839</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.08264462809917356</v>
+        <v>0.0868421052631579</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01428571428571429</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.005415162454873646</v>
+        <v>0.005199306759098787</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.5465838509316771</v>
+        <v>0.5492537313432836</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8909090909090909</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6656050955414012</v>
+        <v>0.6595744680851063</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3372093023255814</v>
+        <v>0.3388581952117864</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7237354085603113</v>
+        <v>0.7230483271375465</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2670682730923695</v>
+        <v>0.2657743785850861</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.691768826619965</v>
+        <v>0.6881270903010034</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3027613412228797</v>
+        <v>0.3030018761726079</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4099099099099099</v>
+        <v>0.407725321888412</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2938388625592417</v>
+        <v>0.3018018018018018</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2530120481927711</v>
+        <v>0.25</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.2719298245614035</v>
+        <v>0.2773109243697479</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2409638554216867</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.602510460251046</v>
+        <v>0.6062992125984252</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6739130434782609</v>
+        <v>0.6643356643356644</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7787610619469026</v>
+        <v>0.7627118644067796</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.702247191011236</v>
+        <v>0.6989247311827957</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7721518987341772</v>
+        <v>0.7771084337349398</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0544069640914037</v>
+        <v>0.05377456049638056</v>
       </c>
       <c r="FQ10" t="n">
-        <v>97.82363977485929</v>
+        <v>97.46499102333932</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5228758169934641</v>
+        <v>0.525</v>
       </c>
       <c r="FS10" t="n">
-        <v>14.34473197781885</v>
+        <v>14.3550133096717</v>
       </c>
       <c r="FT10" t="n">
-        <v>15.09307657038056</v>
+        <v>15.1911013215859</v>
       </c>
       <c r="FU10" t="n">
-        <v>13.78063770794824</v>
+        <v>13.7698314108252</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.35937643282898</v>
+        <v>14.42832599118943</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.3251050420168067</v>
+        <v>0.3229532898041185</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6397415185783522</v>
+        <v>0.6345256609642301</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6986301369863014</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5025252525252525</v>
+        <v>0.5</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1906512605042017</v>
+        <v>0.1908588648920141</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4132231404958678</v>
+        <v>0.4105263157894737</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.4504504504504505</v>
+        <v>0.4495677233429395</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.4423076923076923</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06932773109243698</v>
+        <v>0.07031642390758412</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3560606060606061</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3615384615384615</v>
+        <v>0.3623188405797101</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.425531914893617</v>
+        <v>0.44</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1239495798319328</v>
+        <v>0.126067302862883</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.3386454183266932</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3433476394849785</v>
+        <v>0.3427419354838709</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.975</v>
+        <v>0.9647058823529412</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2909663865546219</v>
+        <v>0.2898041185334003</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3664259927797834</v>
+        <v>0.3639514731369151</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.8714285714285714</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.5064377682403434</v>
+        <v>0.5120967741935484</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5847457627118644</v>
+        <v>0.5905511811023622</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1159420289855072</v>
+        <v>0.12</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.06866952789699571</v>
+        <v>0.07258064516129033</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="GV10" t="n">
         <v>1</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2231759656652361</v>
+        <v>0.2137096774193548</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3773584905660378</v>
       </c>
       <c r="GY10" t="n">
         <v>0.8</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3230769230769231</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5857142857142857</v>
+        <v>0.5787037037037037</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1076923076923077</v>
+        <v>0.1086309523809524</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2738461538461539</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3370786516853932</v>
+        <v>0.3315217391304348</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7400210084033614</v>
+        <v>0.7388247112004018</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3664259927797834</v>
+        <v>0.3639514731369151</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5648775171323143</v>
+        <v>0.5641150277357539</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5517606666666667</v>
+        <v>0.5509373456790124</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5509492236024846</v>
+        <v>0.5498890977443609</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.115145723841376</v>
+        <v>0.1133973479652492</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1807692307692308</v>
+        <v>0.1784660766961652</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.007566204287515763</v>
+        <v>0.007220216606498195</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1290581162324649</v>
+        <v>0.1311411992263056</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.3422845691382765</v>
+        <v>0.337330754352031</v>
       </c>
       <c r="HP10" t="n">
-        <v>5.640394973070018</v>
+        <v>5.671969045571797</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.24484076433121</v>
+        <v>25.23978102189781</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.3604436229205176</v>
+        <v>0.3558118899733806</v>
       </c>
       <c r="HS10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="HT10" t="n">
         <v>1</v>
       </c>
       <c r="HU10" t="n">
-        <v>0.01271186440677966</v>
+        <v>0.01195219123505976</v>
       </c>
     </row>
     <row r="11">
